--- a/03.QLDA/A320.xlsx
+++ b/03.QLDA/A320.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E14B3B6A-C7ED-497F-8BB5-0F6EA241BB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C2FBCF-67E6-4EB3-A1E6-5D6B685C3BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
@@ -55,9 +55,9 @@
     <definedName name="ㅋㅋㅋㅋㅋㅋㅋㅋㅋ" hidden="1">#REF!</definedName>
     <definedName name="ㅌㅊㅍㅌㅊㅍㅌㅋㅊㅍㅌ" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId2"/>
+    <pivotCache cacheId="93" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="277">
   <si>
     <t>Gá lắp</t>
   </si>
@@ -905,6 +905,12 @@
   <si>
     <t>A320-001</t>
   </si>
+  <si>
+    <t>A320-002</t>
+  </si>
+  <si>
+    <t>A320-M4130-006</t>
+  </si>
 </sst>
 </file>
 
@@ -1603,7 +1609,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46282.457814236113" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46293.337688425927" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA326" sheet="Progress"/>
   </cacheSource>
@@ -1771,19 +1777,19 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày BG" numFmtId="14">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-16T00:00:00" maxDate="2026-09-24T00:00:00"/>
     </cacheField>
     <cacheField name="SL BG" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
     <cacheField name="KL BG" numFmtId="43">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="0"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Đơn vị nhận" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Số biên bản" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsBlank="1"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -10095,11 +10101,11 @@
     <d v="2026-09-16T00:00:00"/>
     <n v="1"/>
     <n v="2369"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-23T00:00:00"/>
+    <n v="1"/>
+    <n v="2369"/>
     <s v="PAC"/>
-    <m/>
+    <s v="A320-002"/>
   </r>
   <r>
     <n v="152"/>
@@ -10150,11 +10156,11 @@
     <d v="2026-09-16T00:00:00"/>
     <n v="1"/>
     <n v="2397.3999999999996"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-23T00:00:00"/>
+    <n v="1"/>
+    <n v="2397.3999999999996"/>
     <s v="PAC"/>
-    <m/>
+    <s v="A320-002"/>
   </r>
   <r>
     <n v="153"/>
@@ -10205,11 +10211,11 @@
     <d v="2026-09-11T00:00:00"/>
     <n v="1"/>
     <n v="6461.7199999999975"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-16T00:00:00"/>
+    <n v="1"/>
+    <n v="6461.7199999999975"/>
     <s v="PAC"/>
-    <m/>
+    <s v="A320-001"/>
   </r>
   <r>
     <n v="154"/>
@@ -10260,11 +10266,11 @@
     <d v="2026-09-11T00:00:00"/>
     <n v="1"/>
     <n v="5173.1000000000004"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-16T00:00:00"/>
+    <n v="1"/>
+    <n v="5173.1000000000004"/>
     <s v="PAC"/>
-    <m/>
+    <s v="A320-001"/>
   </r>
   <r>
     <n v="155"/>
@@ -10315,11 +10321,11 @@
     <d v="2026-09-11T00:00:00"/>
     <n v="1"/>
     <n v="4180.7848000000004"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-09-16T00:00:00"/>
+    <n v="1"/>
+    <n v="4180.7848000000004"/>
     <s v="PAC"/>
-    <m/>
+    <s v="A320-001"/>
   </r>
   <r>
     <n v="156"/>
@@ -19565,7 +19571,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="93" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -20396,7 +20402,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46281</v>
+        <v>46291</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -20452,20 +20458,20 @@
       <c r="AT2" s="17"/>
       <c r="AU2" s="67">
         <f>SUBTOTAL(9,AU4:AU326)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV2" s="68">
         <f>SUBTOTAL(9,AV4:AV326)</f>
-        <v>20582.004799999999</v>
+        <v>22652.604800000001</v>
       </c>
       <c r="AW2" s="16"/>
       <c r="AX2" s="67">
         <f>SUBTOTAL(9,AX4:AX326)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY2" s="67">
         <f>SUBTOTAL(9,AY4:AY326)</f>
-        <v>15815.604799999997</v>
+        <v>20582.004799999999</v>
       </c>
       <c r="AZ2" s="17"/>
       <c r="BA2" s="18" t="str">
@@ -36878,11 +36884,11 @@
       <c r="AD143" s="54"/>
       <c r="AE143" s="31">
         <f t="shared" si="29"/>
-        <v>1863.54</v>
+        <v>2070.6</v>
       </c>
       <c r="AF143" s="32">
         <f t="shared" si="30"/>
-        <v>207.05999999999995</v>
+        <v>0</v>
       </c>
       <c r="AG143" s="30"/>
       <c r="AH143" s="33">
@@ -36918,12 +36924,18 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="AS143" s="27"/>
-      <c r="AT143" s="37"/>
-      <c r="AU143" s="30"/>
+      <c r="AS143" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="AT143" s="37">
+        <v>46291</v>
+      </c>
+      <c r="AU143" s="30">
+        <v>1</v>
+      </c>
       <c r="AV143" s="36">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>2070.6</v>
       </c>
       <c r="AW143" s="35"/>
       <c r="AX143" s="30"/>
@@ -38317,16 +38329,22 @@
         <f t="shared" si="35"/>
         <v>2369</v>
       </c>
-      <c r="AW154" s="35"/>
-      <c r="AX154" s="30"/>
+      <c r="AW154" s="35">
+        <v>46288</v>
+      </c>
+      <c r="AX154" s="30">
+        <v>1</v>
+      </c>
       <c r="AY154" s="32">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2369</v>
       </c>
       <c r="AZ154" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="BA154" s="63"/>
+      <c r="BA154" s="63" t="s">
+        <v>275</v>
+      </c>
       <c r="BB154" s="71"/>
       <c r="BC154" s="71"/>
       <c r="BD154" s="71"/>
@@ -38449,16 +38467,22 @@
         <f t="shared" si="35"/>
         <v>2397.3999999999996</v>
       </c>
-      <c r="AW155" s="35"/>
-      <c r="AX155" s="30"/>
+      <c r="AW155" s="35">
+        <v>46288</v>
+      </c>
+      <c r="AX155" s="30">
+        <v>1</v>
+      </c>
       <c r="AY155" s="32">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2397.3999999999996</v>
       </c>
       <c r="AZ155" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="BA155" s="63"/>
+      <c r="BA155" s="63" t="s">
+        <v>275</v>
+      </c>
       <c r="BB155" s="71"/>
       <c r="BC155" s="71"/>
       <c r="BD155" s="71"/>

--- a/03.QLDA/A320.xlsx
+++ b/03.QLDA/A320.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C2FBCF-67E6-4EB3-A1E6-5D6B685C3BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509E5184-17A5-441F-B3CB-D53A76ADF547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
@@ -55,9 +55,9 @@
     <definedName name="ㅋㅋㅋㅋㅋㅋㅋㅋㅋ" hidden="1">#REF!</definedName>
     <definedName name="ㅌㅊㅍㅌㅊㅍㅌㅋㅊㅍㅌ" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="93" r:id="rId2"/>
+    <pivotCache cacheId="46" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1896" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="278">
   <si>
     <t>Gá lắp</t>
   </si>
@@ -911,6 +911,9 @@
   <si>
     <t>A320-M4130-006</t>
   </si>
+  <si>
+    <t>A320-M4130-007</t>
+  </si>
 </sst>
 </file>
 
@@ -1609,7 +1612,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46293.337688425927" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46297.328421412036" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA326" sheet="Progress"/>
   </cacheSource>
@@ -1768,7 +1771,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Ngày NT" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-11T00:00:00" maxDate="2026-09-17T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-11T00:00:00" maxDate="2026-09-27T00:00:00"/>
     </cacheField>
     <cacheField name="SL NT" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
@@ -9478,8 +9481,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="1863.54"/>
-    <n v="207.05999999999995"/>
+    <n v="2070.6"/>
+    <n v="0"/>
     <m/>
     <n v="0.9"/>
     <n v="1863.54"/>
@@ -9492,10 +9495,10 @@
     <m/>
     <m/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <s v="A320-M4130-006"/>
+    <d v="2026-09-26T00:00:00"/>
+    <n v="1"/>
+    <n v="2070.6"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -19571,7 +19574,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="93" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -20402,7 +20405,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -20458,11 +20461,11 @@
       <c r="AT2" s="17"/>
       <c r="AU2" s="67">
         <f>SUBTOTAL(9,AU4:AU326)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV2" s="68">
         <f>SUBTOTAL(9,AV4:AV326)</f>
-        <v>22652.604800000001</v>
+        <v>24732.604800000001</v>
       </c>
       <c r="AW2" s="16"/>
       <c r="AX2" s="67">
@@ -37016,11 +37019,11 @@
       <c r="AD144" s="54"/>
       <c r="AE144" s="31">
         <f t="shared" si="29"/>
-        <v>1872.0000000000005</v>
+        <v>2080.0000000000005</v>
       </c>
       <c r="AF144" s="32">
         <f t="shared" si="30"/>
-        <v>208</v>
+        <v>0</v>
       </c>
       <c r="AG144" s="30"/>
       <c r="AH144" s="33">
@@ -37056,12 +37059,18 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="AS144" s="27"/>
-      <c r="AT144" s="37"/>
-      <c r="AU144" s="30"/>
+      <c r="AS144" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="AT144" s="37">
+        <v>46296</v>
+      </c>
+      <c r="AU144" s="30">
+        <v>1</v>
+      </c>
       <c r="AV144" s="36">
         <f t="shared" si="35"/>
-        <v>0</v>
+        <v>2080.0000000000005</v>
       </c>
       <c r="AW144" s="35"/>
       <c r="AX144" s="30"/>

--- a/03.QLDA/A320.xlsx
+++ b/03.QLDA/A320.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509E5184-17A5-441F-B3CB-D53A76ADF547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88F7D31-6C71-4EB9-BEFB-823B3B4E9847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="46" r:id="rId2"/>
+    <pivotCache cacheId="6" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -70,8 +70,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -79,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="279">
   <si>
     <t>Gá lắp</t>
   </si>
@@ -914,18 +912,21 @@
   <si>
     <t>A320-M4130-007</t>
   </si>
+  <si>
+    <t>A320-003</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1272,7 +1273,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1360,28 +1361,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1402,19 +1403,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1436,13 +1437,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1470,56 +1471,56 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="26">
+  <dxfs count="27">
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <fill>
@@ -1564,34 +1565,42 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1612,13 +1621,13 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46297.328421412036" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Hiếu Nguyễn" refreshedDate="46298.349438194447" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA326" sheet="Progress"/>
   </cacheSource>
   <cacheFields count="53">
     <cacheField name="TT" numFmtId="0">
-      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="186"/>
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="Số Dự Án" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
@@ -1677,10 +1686,10 @@
     <cacheField name="T'Qty" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="96"/>
     </cacheField>
-    <cacheField name="U.Weight" numFmtId="43">
+    <cacheField name="U.Weight" numFmtId="165">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5000000000000001E-2" maxValue="6730.4139199999981"/>
     </cacheField>
-    <cacheField name="T.Weight" numFmtId="43">
+    <cacheField name="T.Weight" numFmtId="165">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.1" maxValue="6730.4139199999981"/>
     </cacheField>
     <cacheField name="Profile" numFmtId="0">
@@ -1725,10 +1734,10 @@
     <cacheField name="DATE CPCL" numFmtId="14">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Hoàn thiện" numFmtId="164">
+    <cacheField name="Hoàn thiện" numFmtId="166">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
-    <cacheField name="Còn lại" numFmtId="43">
+    <cacheField name="Còn lại" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6730.4139199999981"/>
     </cacheField>
     <cacheField name="Kế hoạch Tháng" numFmtId="0">
@@ -1737,7 +1746,7 @@
     <cacheField name="Nhận Phôi" numFmtId="9">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.9" maxValue="0.9"/>
     </cacheField>
-    <cacheField name="Khối lượng" numFmtId="164">
+    <cacheField name="Khối lượng" numFmtId="166">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="5815.547999999998"/>
     </cacheField>
     <cacheField name="Ngày Gá" numFmtId="14">
@@ -1746,7 +1755,7 @@
     <cacheField name="SL Gá" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Gá" numFmtId="43">
+    <cacheField name="KL Gá" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày Hàn" numFmtId="14">
@@ -1755,7 +1764,7 @@
     <cacheField name="SL Hàn" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Hàn" numFmtId="43">
+    <cacheField name="KL Hàn" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày TH" numFmtId="14">
@@ -1764,28 +1773,28 @@
     <cacheField name="SL TH" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL TH" numFmtId="43">
+    <cacheField name="KL TH" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Số AFI" numFmtId="0">
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="Ngày NT" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-11T00:00:00" maxDate="2026-09-27T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-11T00:00:00" maxDate="2026-10-02T00:00:00"/>
     </cacheField>
     <cacheField name="SL NT" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL NT" numFmtId="43">
+    <cacheField name="KL NT" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày BG" numFmtId="14">
-      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-16T00:00:00" maxDate="2026-09-24T00:00:00"/>
+      <sharedItems containsNonDate="0" containsDate="1" containsString="0" containsBlank="1" minDate="2026-09-16T00:00:00" maxDate="2026-10-03T00:00:00"/>
     </cacheField>
     <cacheField name="SL BG" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL BG" numFmtId="43">
+    <cacheField name="KL BG" numFmtId="165">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Đơn vị nhận" numFmtId="0">
@@ -1806,7 +1815,7 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="323">
   <r>
-    <n v="1"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -1861,7 +1870,7 @@
     <m/>
   </r>
   <r>
-    <n v="2"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -1916,7 +1925,7 @@
     <m/>
   </r>
   <r>
-    <n v="3"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -1971,7 +1980,7 @@
     <m/>
   </r>
   <r>
-    <n v="4"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2026,7 +2035,7 @@
     <m/>
   </r>
   <r>
-    <n v="5"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2081,7 +2090,7 @@
     <m/>
   </r>
   <r>
-    <n v="6"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2136,7 +2145,7 @@
     <m/>
   </r>
   <r>
-    <n v="7"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2191,7 +2200,7 @@
     <m/>
   </r>
   <r>
-    <n v="8"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2246,7 +2255,7 @@
     <m/>
   </r>
   <r>
-    <n v="9"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2301,7 +2310,7 @@
     <m/>
   </r>
   <r>
-    <n v="10"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2356,7 +2365,7 @@
     <m/>
   </r>
   <r>
-    <n v="11"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2411,7 +2420,7 @@
     <m/>
   </r>
   <r>
-    <n v="12"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2466,7 +2475,7 @@
     <m/>
   </r>
   <r>
-    <n v="13"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2521,7 +2530,7 @@
     <m/>
   </r>
   <r>
-    <n v="14"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2576,7 +2585,7 @@
     <m/>
   </r>
   <r>
-    <n v="15"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2631,7 +2640,7 @@
     <m/>
   </r>
   <r>
-    <n v="16"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2686,7 +2695,7 @@
     <m/>
   </r>
   <r>
-    <n v="17"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2741,7 +2750,7 @@
     <m/>
   </r>
   <r>
-    <n v="18"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2796,7 +2805,7 @@
     <m/>
   </r>
   <r>
-    <n v="19"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2851,7 +2860,7 @@
     <m/>
   </r>
   <r>
-    <n v="20"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2906,7 +2915,7 @@
     <m/>
   </r>
   <r>
-    <n v="21"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -2961,7 +2970,7 @@
     <m/>
   </r>
   <r>
-    <n v="22"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3016,7 +3025,7 @@
     <m/>
   </r>
   <r>
-    <n v="23"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3071,7 +3080,7 @@
     <m/>
   </r>
   <r>
-    <n v="24"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3126,7 +3135,7 @@
     <m/>
   </r>
   <r>
-    <n v="25"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3181,7 +3190,7 @@
     <m/>
   </r>
   <r>
-    <n v="26"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3236,7 +3245,7 @@
     <m/>
   </r>
   <r>
-    <n v="27"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3291,7 +3300,7 @@
     <m/>
   </r>
   <r>
-    <n v="28"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3346,7 +3355,7 @@
     <m/>
   </r>
   <r>
-    <n v="29"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3401,7 +3410,7 @@
     <m/>
   </r>
   <r>
-    <n v="30"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3456,7 +3465,7 @@
     <m/>
   </r>
   <r>
-    <n v="31"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3511,7 +3520,7 @@
     <m/>
   </r>
   <r>
-    <n v="32"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3566,7 +3575,7 @@
     <m/>
   </r>
   <r>
-    <n v="33"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3621,7 +3630,7 @@
     <m/>
   </r>
   <r>
-    <n v="34"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3676,7 +3685,7 @@
     <m/>
   </r>
   <r>
-    <n v="35"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3731,7 +3740,7 @@
     <m/>
   </r>
   <r>
-    <n v="36"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3786,7 +3795,7 @@
     <m/>
   </r>
   <r>
-    <n v="37"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3841,7 +3850,7 @@
     <m/>
   </r>
   <r>
-    <n v="38"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3896,7 +3905,7 @@
     <m/>
   </r>
   <r>
-    <n v="39"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 7 SDM-M4130-M4131-L4-ST18"/>
     <x v="0"/>
@@ -3951,7 +3960,7 @@
     <m/>
   </r>
   <r>
-    <n v="40"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4006,7 +4015,7 @@
     <m/>
   </r>
   <r>
-    <n v="41"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4061,7 +4070,7 @@
     <m/>
   </r>
   <r>
-    <n v="42"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4116,7 +4125,7 @@
     <m/>
   </r>
   <r>
-    <n v="43"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4171,7 +4180,7 @@
     <m/>
   </r>
   <r>
-    <n v="44"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4226,7 +4235,7 @@
     <m/>
   </r>
   <r>
-    <n v="45"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4281,7 +4290,7 @@
     <m/>
   </r>
   <r>
-    <n v="46"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4336,7 +4345,7 @@
     <m/>
   </r>
   <r>
-    <n v="47"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4391,7 +4400,7 @@
     <m/>
   </r>
   <r>
-    <n v="48"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4446,7 +4455,7 @@
     <m/>
   </r>
   <r>
-    <n v="49"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4501,7 +4510,7 @@
     <m/>
   </r>
   <r>
-    <n v="50"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4556,7 +4565,7 @@
     <m/>
   </r>
   <r>
-    <n v="51"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4611,7 +4620,7 @@
     <m/>
   </r>
   <r>
-    <n v="52"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4666,7 +4675,7 @@
     <m/>
   </r>
   <r>
-    <n v="53"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4721,7 +4730,7 @@
     <m/>
   </r>
   <r>
-    <n v="54"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4776,7 +4785,7 @@
     <m/>
   </r>
   <r>
-    <n v="55"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4831,7 +4840,7 @@
     <m/>
   </r>
   <r>
-    <n v="56"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4886,7 +4895,7 @@
     <m/>
   </r>
   <r>
-    <n v="57"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4941,7 +4950,7 @@
     <m/>
   </r>
   <r>
-    <n v="58"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -4996,7 +5005,7 @@
     <m/>
   </r>
   <r>
-    <n v="59"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5051,7 +5060,7 @@
     <m/>
   </r>
   <r>
-    <n v="60"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5106,7 +5115,7 @@
     <m/>
   </r>
   <r>
-    <n v="61"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5161,7 +5170,7 @@
     <m/>
   </r>
   <r>
-    <n v="62"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5216,7 +5225,7 @@
     <m/>
   </r>
   <r>
-    <n v="63"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5271,7 +5280,7 @@
     <m/>
   </r>
   <r>
-    <n v="64"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5326,7 +5335,7 @@
     <m/>
   </r>
   <r>
-    <n v="65"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5381,7 +5390,7 @@
     <m/>
   </r>
   <r>
-    <n v="66"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5436,7 +5445,7 @@
     <m/>
   </r>
   <r>
-    <n v="67"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5491,7 +5500,7 @@
     <m/>
   </r>
   <r>
-    <n v="68"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5546,7 +5555,7 @@
     <m/>
   </r>
   <r>
-    <n v="69"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5601,7 +5610,7 @@
     <m/>
   </r>
   <r>
-    <n v="70"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5656,7 +5665,7 @@
     <m/>
   </r>
   <r>
-    <n v="71"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5711,7 +5720,7 @@
     <m/>
   </r>
   <r>
-    <n v="72"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5766,7 +5775,7 @@
     <m/>
   </r>
   <r>
-    <n v="73"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5821,7 +5830,7 @@
     <m/>
   </r>
   <r>
-    <n v="74"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5876,7 +5885,7 @@
     <m/>
   </r>
   <r>
-    <n v="75"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5931,7 +5940,7 @@
     <m/>
   </r>
   <r>
-    <n v="76"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -5986,7 +5995,7 @@
     <m/>
   </r>
   <r>
-    <n v="77"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6041,7 +6050,7 @@
     <m/>
   </r>
   <r>
-    <n v="78"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6096,7 +6105,7 @@
     <m/>
   </r>
   <r>
-    <n v="79"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6151,7 +6160,7 @@
     <m/>
   </r>
   <r>
-    <n v="80"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6206,7 +6215,7 @@
     <m/>
   </r>
   <r>
-    <n v="81"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6261,7 +6270,7 @@
     <m/>
   </r>
   <r>
-    <n v="82"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6316,7 +6325,7 @@
     <m/>
   </r>
   <r>
-    <n v="83"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6371,7 +6380,7 @@
     <m/>
   </r>
   <r>
-    <n v="84"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6426,7 +6435,7 @@
     <m/>
   </r>
   <r>
-    <n v="85"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6481,7 +6490,7 @@
     <m/>
   </r>
   <r>
-    <n v="86"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6536,7 +6545,7 @@
     <m/>
   </r>
   <r>
-    <n v="87"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6591,7 +6600,7 @@
     <m/>
   </r>
   <r>
-    <n v="88"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 5 SDM-M4130-M4131-L3-ST15"/>
     <x v="1"/>
@@ -6646,7 +6655,7 @@
     <m/>
   </r>
   <r>
-    <n v="89"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -6701,7 +6710,7 @@
     <m/>
   </r>
   <r>
-    <n v="90"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -6756,7 +6765,7 @@
     <m/>
   </r>
   <r>
-    <n v="91"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -6811,7 +6820,7 @@
     <m/>
   </r>
   <r>
-    <n v="92"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -6866,7 +6875,7 @@
     <m/>
   </r>
   <r>
-    <n v="93"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -6921,7 +6930,7 @@
     <m/>
   </r>
   <r>
-    <n v="94"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -6976,7 +6985,7 @@
     <m/>
   </r>
   <r>
-    <n v="95"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7031,7 +7040,7 @@
     <m/>
   </r>
   <r>
-    <n v="96"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7086,7 +7095,7 @@
     <m/>
   </r>
   <r>
-    <n v="97"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7141,7 +7150,7 @@
     <m/>
   </r>
   <r>
-    <n v="98"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7196,7 +7205,7 @@
     <m/>
   </r>
   <r>
-    <n v="99"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7251,7 +7260,7 @@
     <m/>
   </r>
   <r>
-    <n v="100"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7306,7 +7315,7 @@
     <m/>
   </r>
   <r>
-    <n v="101"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7361,7 +7370,7 @@
     <m/>
   </r>
   <r>
-    <n v="102"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7416,7 +7425,7 @@
     <m/>
   </r>
   <r>
-    <n v="103"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7471,7 +7480,7 @@
     <m/>
   </r>
   <r>
-    <n v="104"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7526,7 +7535,7 @@
     <m/>
   </r>
   <r>
-    <n v="105"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7581,7 +7590,7 @@
     <m/>
   </r>
   <r>
-    <n v="106"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7636,7 +7645,7 @@
     <m/>
   </r>
   <r>
-    <n v="107"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7691,7 +7700,7 @@
     <m/>
   </r>
   <r>
-    <n v="108"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7746,7 +7755,7 @@
     <m/>
   </r>
   <r>
-    <n v="109"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7801,7 +7810,7 @@
     <m/>
   </r>
   <r>
-    <n v="110"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7856,7 +7865,7 @@
     <m/>
   </r>
   <r>
-    <n v="111"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7911,7 +7920,7 @@
     <m/>
   </r>
   <r>
-    <n v="112"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -7966,7 +7975,7 @@
     <m/>
   </r>
   <r>
-    <n v="113"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8021,7 +8030,7 @@
     <m/>
   </r>
   <r>
-    <n v="114"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8076,7 +8085,7 @@
     <m/>
   </r>
   <r>
-    <n v="115"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8131,7 +8140,7 @@
     <m/>
   </r>
   <r>
-    <n v="116"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8186,7 +8195,7 @@
     <m/>
   </r>
   <r>
-    <n v="117"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8241,7 +8250,7 @@
     <m/>
   </r>
   <r>
-    <n v="118"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8296,7 +8305,7 @@
     <m/>
   </r>
   <r>
-    <n v="119"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8351,7 +8360,7 @@
     <m/>
   </r>
   <r>
-    <n v="120"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8406,7 +8415,7 @@
     <m/>
   </r>
   <r>
-    <n v="121"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8461,7 +8470,7 @@
     <m/>
   </r>
   <r>
-    <n v="122"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8516,7 +8525,7 @@
     <m/>
   </r>
   <r>
-    <n v="123"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8571,7 +8580,7 @@
     <m/>
   </r>
   <r>
-    <n v="124"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8626,7 +8635,7 @@
     <m/>
   </r>
   <r>
-    <n v="125"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8681,7 +8690,7 @@
     <m/>
   </r>
   <r>
-    <n v="126"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8736,7 +8745,7 @@
     <m/>
   </r>
   <r>
-    <n v="127"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8791,7 +8800,7 @@
     <m/>
   </r>
   <r>
-    <n v="128"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8846,7 +8855,7 @@
     <m/>
   </r>
   <r>
-    <n v="129"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8901,7 +8910,7 @@
     <m/>
   </r>
   <r>
-    <n v="130"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -8956,7 +8965,7 @@
     <m/>
   </r>
   <r>
-    <n v="131"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9011,7 +9020,7 @@
     <m/>
   </r>
   <r>
-    <n v="132"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9066,7 +9075,7 @@
     <m/>
   </r>
   <r>
-    <n v="133"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9121,7 +9130,7 @@
     <m/>
   </r>
   <r>
-    <n v="134"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9176,7 +9185,7 @@
     <m/>
   </r>
   <r>
-    <n v="135"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9231,7 +9240,7 @@
     <m/>
   </r>
   <r>
-    <n v="136"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9286,7 +9295,7 @@
     <m/>
   </r>
   <r>
-    <n v="137"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 3 SDM-M4130-M4131-L2-ST13"/>
     <x v="2"/>
@@ -9341,7 +9350,7 @@
     <m/>
   </r>
   <r>
-    <n v="138"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9396,7 +9405,7 @@
     <m/>
   </r>
   <r>
-    <n v="139"/>
+    <n v="0"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9451,7 +9460,7 @@
     <m/>
   </r>
   <r>
-    <n v="140"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9499,14 +9508,14 @@
     <d v="2026-09-26T00:00:00"/>
     <n v="1"/>
     <n v="2070.6"/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <d v="2026-10-02T00:00:00"/>
+    <n v="1"/>
+    <n v="2070.6"/>
     <s v="PAC"/>
-    <m/>
+    <s v="A290-003"/>
   </r>
   <r>
-    <n v="141"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9536,8 +9545,8 @@
     <m/>
     <m/>
     <m/>
-    <n v="1872.0000000000005"/>
-    <n v="208"/>
+    <n v="2080.0000000000005"/>
+    <n v="0"/>
     <m/>
     <n v="0.9"/>
     <n v="1872.0000000000005"/>
@@ -9550,10 +9559,10 @@
     <m/>
     <m/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0"/>
+    <s v="A320-M4130-007"/>
+    <d v="2026-10-01T00:00:00"/>
+    <n v="1"/>
+    <n v="2080.0000000000005"/>
     <m/>
     <m/>
     <n v="0"/>
@@ -9561,7 +9570,7 @@
     <m/>
   </r>
   <r>
-    <n v="142"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9616,7 +9625,7 @@
     <m/>
   </r>
   <r>
-    <n v="143"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9671,7 +9680,7 @@
     <m/>
   </r>
   <r>
-    <n v="144"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9726,7 +9735,7 @@
     <m/>
   </r>
   <r>
-    <n v="145"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9781,7 +9790,7 @@
     <m/>
   </r>
   <r>
-    <n v="146"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9836,7 +9845,7 @@
     <m/>
   </r>
   <r>
-    <n v="147"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9891,7 +9900,7 @@
     <m/>
   </r>
   <r>
-    <n v="148"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -9946,7 +9955,7 @@
     <m/>
   </r>
   <r>
-    <n v="149"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10001,7 +10010,7 @@
     <m/>
   </r>
   <r>
-    <n v="150"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10056,7 +10065,7 @@
     <m/>
   </r>
   <r>
-    <n v="151"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10111,7 +10120,7 @@
     <s v="A320-002"/>
   </r>
   <r>
-    <n v="152"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10166,7 +10175,7 @@
     <s v="A320-002"/>
   </r>
   <r>
-    <n v="153"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10221,7 +10230,7 @@
     <s v="A320-001"/>
   </r>
   <r>
-    <n v="154"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10276,7 +10285,7 @@
     <s v="A320-001"/>
   </r>
   <r>
-    <n v="155"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10331,7 +10340,7 @@
     <s v="A320-001"/>
   </r>
   <r>
-    <n v="156"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10386,7 +10395,7 @@
     <m/>
   </r>
   <r>
-    <n v="157"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10441,7 +10450,7 @@
     <m/>
   </r>
   <r>
-    <n v="158"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10496,7 +10505,7 @@
     <m/>
   </r>
   <r>
-    <n v="159"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10551,7 +10560,7 @@
     <m/>
   </r>
   <r>
-    <n v="160"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10606,7 +10615,7 @@
     <m/>
   </r>
   <r>
-    <n v="161"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10661,7 +10670,7 @@
     <m/>
   </r>
   <r>
-    <n v="162"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10716,7 +10725,7 @@
     <m/>
   </r>
   <r>
-    <n v="163"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10771,7 +10780,7 @@
     <m/>
   </r>
   <r>
-    <n v="164"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10826,7 +10835,7 @@
     <m/>
   </r>
   <r>
-    <n v="165"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10881,7 +10890,7 @@
     <m/>
   </r>
   <r>
-    <n v="166"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10936,7 +10945,7 @@
     <m/>
   </r>
   <r>
-    <n v="167"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -10991,7 +11000,7 @@
     <m/>
   </r>
   <r>
-    <n v="168"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11046,7 +11055,7 @@
     <m/>
   </r>
   <r>
-    <n v="169"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11101,7 +11110,7 @@
     <m/>
   </r>
   <r>
-    <n v="170"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11156,7 +11165,7 @@
     <m/>
   </r>
   <r>
-    <n v="171"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11211,7 +11220,7 @@
     <m/>
   </r>
   <r>
-    <n v="172"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11266,7 +11275,7 @@
     <m/>
   </r>
   <r>
-    <n v="173"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11321,7 +11330,7 @@
     <m/>
   </r>
   <r>
-    <n v="174"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11376,7 +11385,7 @@
     <m/>
   </r>
   <r>
-    <n v="175"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11431,7 +11440,7 @@
     <m/>
   </r>
   <r>
-    <n v="176"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11486,7 +11495,7 @@
     <m/>
   </r>
   <r>
-    <n v="177"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11541,7 +11550,7 @@
     <m/>
   </r>
   <r>
-    <n v="178"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11596,7 +11605,7 @@
     <m/>
   </r>
   <r>
-    <n v="179"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11651,7 +11660,7 @@
     <m/>
   </r>
   <r>
-    <n v="180"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11706,7 +11715,7 @@
     <m/>
   </r>
   <r>
-    <n v="181"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11761,7 +11770,7 @@
     <m/>
   </r>
   <r>
-    <n v="182"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11816,7 +11825,7 @@
     <m/>
   </r>
   <r>
-    <n v="183"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11871,7 +11880,7 @@
     <m/>
   </r>
   <r>
-    <n v="184"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11926,7 +11935,7 @@
     <m/>
   </r>
   <r>
-    <n v="185"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -11981,7 +11990,7 @@
     <m/>
   </r>
   <r>
-    <n v="186"/>
+    <n v="1"/>
     <x v="0"/>
     <s v="Shipment 1 SDM-M4130-M4131-L1-ST11"/>
     <x v="3"/>
@@ -19574,7 +19583,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="46" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -19634,27 +19643,27 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="166" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="43" showAll="0"/>
+    <pivotField dataField="1" numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="43" showAll="0"/>
+    <pivotField numFmtId="165" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -19708,7 +19717,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="Sum of T.Weight" fld="15" baseField="1" baseItem="0"/>
-    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="43"/>
+    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="165"/>
   </dataFields>
   <formats count="10">
     <format dxfId="25">
@@ -20257,9 +20266,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:BH327"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
+  <sheetPr codeName="Sheet1" filterMode="1"/>
+  <dimension ref="A1:BH326"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -20309,7 +20318,7 @@
     <col min="60" max="60" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1">
       <c r="A1" s="1" t="str">
         <f>"DỰ ÁN:"&amp;B4</f>
         <v>DỰ ÁN:A320</v>
@@ -20380,7 +20389,7 @@
       <c r="BC1" s="48"/>
       <c r="BD1" s="48"/>
     </row>
-    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -20405,7 +20414,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -20430,29 +20439,29 @@
       <c r="AJ2" s="15"/>
       <c r="AK2" s="67">
         <f>SUBTOTAL(9,AK4:AK326)</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AL2" s="68">
         <f>SUBTOTAL(9,AL4:AL326)</f>
-        <v>51008.607039999988</v>
+        <v>2070.6</v>
       </c>
       <c r="AM2" s="15"/>
       <c r="AN2" s="67">
         <f>SUBTOTAL(9,AN4:AN326)</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="AO2" s="68">
         <f>SUBTOTAL(9,AO4:AO326)</f>
-        <v>51008.607039999988</v>
+        <v>2070.6</v>
       </c>
       <c r="AP2" s="15"/>
       <c r="AQ2" s="67">
         <f>SUBTOTAL(9,AQ4:AQ326)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR2" s="68">
         <f>SUBTOTAL(9,AR4:AR326)</f>
-        <v>15815.604799999997</v>
+        <v>0</v>
       </c>
       <c r="AS2" s="16" t="str">
         <f>SUBSTITUTE(A1,"DỰ ÁN:","")&amp;"-"</f>
@@ -20461,20 +20470,20 @@
       <c r="AT2" s="17"/>
       <c r="AU2" s="67">
         <f>SUBTOTAL(9,AU4:AU326)</f>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AV2" s="68">
         <f>SUBTOTAL(9,AV4:AV326)</f>
-        <v>24732.604800000001</v>
+        <v>2070.6</v>
       </c>
       <c r="AW2" s="16"/>
       <c r="AX2" s="67">
         <f>SUBTOTAL(9,AX4:AX326)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AY2" s="67">
         <f>SUBTOTAL(9,AY4:AY326)</f>
-        <v>20582.004799999999</v>
+        <v>2070.6</v>
       </c>
       <c r="AZ2" s="17"/>
       <c r="BA2" s="18" t="str">
@@ -20485,7 +20494,7 @@
       <c r="BC2" s="48"/>
       <c r="BD2" s="48"/>
     </row>
-    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1">
       <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
@@ -20664,10 +20673,10 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:60" hidden="1">
       <c r="A4" s="24">
         <f>IF(B4="","",SUBTOTAL(3,$B$4:B4))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>174</v>
@@ -20787,10 +20796,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:60" hidden="1">
       <c r="A5" s="24">
         <f>IF(B5="","",SUBTOTAL(3,$B$4:B5))</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>174</v>
@@ -20910,10 +20919,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:60" hidden="1">
       <c r="A6" s="24">
         <f>IF(B6="","",SUBTOTAL(3,$B$4:B6))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>174</v>
@@ -21033,10 +21042,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:60" hidden="1">
       <c r="A7" s="24">
         <f>IF(B7="","",SUBTOTAL(3,$B$4:B7))</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>174</v>
@@ -21156,10 +21165,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:60" hidden="1">
       <c r="A8" s="24">
         <f>IF(B8="","",SUBTOTAL(3,$B$4:B8))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>174</v>
@@ -21279,10 +21288,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:60" hidden="1">
       <c r="A9" s="24">
         <f>IF(B9="","",SUBTOTAL(3,$B$4:B9))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>174</v>
@@ -21402,10 +21411,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:60" hidden="1">
       <c r="A10" s="24">
         <f>IF(B10="","",SUBTOTAL(3,$B$4:B10))</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>174</v>
@@ -21525,10 +21534,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:60" hidden="1">
       <c r="A11" s="24">
         <f>IF(B11="","",SUBTOTAL(3,$B$4:B11))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>174</v>
@@ -21648,10 +21657,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:60" hidden="1">
       <c r="A12" s="24">
         <f>IF(B12="","",SUBTOTAL(3,$B$4:B12))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>174</v>
@@ -21773,10 +21782,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:60" hidden="1">
       <c r="A13" s="24">
         <f>IF(B13="","",SUBTOTAL(3,$B$4:B13))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>174</v>
@@ -21898,10 +21907,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:60" hidden="1">
       <c r="A14" s="24">
         <f>IF(B14="","",SUBTOTAL(3,$B$4:B14))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>174</v>
@@ -22014,10 +22023,10 @@
       <c r="BC14" s="71"/>
       <c r="BD14" s="71"/>
     </row>
-    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:60" hidden="1">
       <c r="A15" s="24">
         <f>IF(B15="","",SUBTOTAL(3,$B$4:B15))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>174</v>
@@ -22130,10 +22139,10 @@
       <c r="BC15" s="71"/>
       <c r="BD15" s="71"/>
     </row>
-    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:60" hidden="1">
       <c r="A16" s="24">
         <f>IF(B16="","",SUBTOTAL(3,$B$4:B16))</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>174</v>
@@ -22246,10 +22255,10 @@
       <c r="BC16" s="71"/>
       <c r="BD16" s="71"/>
     </row>
-    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:56" hidden="1">
       <c r="A17" s="24">
         <f>IF(B17="","",SUBTOTAL(3,$B$4:B17))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>174</v>
@@ -22362,10 +22371,10 @@
       <c r="BC17" s="71"/>
       <c r="BD17" s="71"/>
     </row>
-    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:56" hidden="1">
       <c r="A18" s="24">
         <f>IF(B18="","",SUBTOTAL(3,$B$4:B18))</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>174</v>
@@ -22478,10 +22487,10 @@
       <c r="BC18" s="71"/>
       <c r="BD18" s="71"/>
     </row>
-    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:56" hidden="1">
       <c r="A19" s="24">
         <f>IF(B19="","",SUBTOTAL(3,$B$4:B19))</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>174</v>
@@ -22594,10 +22603,10 @@
       <c r="BC19" s="71"/>
       <c r="BD19" s="71"/>
     </row>
-    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:56" hidden="1">
       <c r="A20" s="24">
         <f>IF(B20="","",SUBTOTAL(3,$B$4:B20))</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>174</v>
@@ -22710,10 +22719,10 @@
       <c r="BC20" s="71"/>
       <c r="BD20" s="71"/>
     </row>
-    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:56" hidden="1">
       <c r="A21" s="24">
         <f>IF(B21="","",SUBTOTAL(3,$B$4:B21))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>174</v>
@@ -22826,10 +22835,10 @@
       <c r="BC21" s="71"/>
       <c r="BD21" s="71"/>
     </row>
-    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:56" hidden="1">
       <c r="A22" s="24">
         <f>IF(B22="","",SUBTOTAL(3,$B$4:B22))</f>
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>174</v>
@@ -22942,10 +22951,10 @@
       <c r="BC22" s="71"/>
       <c r="BD22" s="71"/>
     </row>
-    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:56" hidden="1">
       <c r="A23" s="24">
         <f>IF(B23="","",SUBTOTAL(3,$B$4:B23))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>174</v>
@@ -23058,10 +23067,10 @@
       <c r="BC23" s="71"/>
       <c r="BD23" s="71"/>
     </row>
-    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:56" hidden="1">
       <c r="A24" s="24">
         <f>IF(B24="","",SUBTOTAL(3,$B$4:B24))</f>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="B24" s="25" t="s">
         <v>174</v>
@@ -23174,10 +23183,10 @@
       <c r="BC24" s="71"/>
       <c r="BD24" s="71"/>
     </row>
-    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:56" hidden="1">
       <c r="A25" s="24">
         <f>IF(B25="","",SUBTOTAL(3,$B$4:B25))</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="B25" s="25" t="s">
         <v>174</v>
@@ -23290,10 +23299,10 @@
       <c r="BC25" s="71"/>
       <c r="BD25" s="71"/>
     </row>
-    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:56" hidden="1">
       <c r="A26" s="24">
         <f>IF(B26="","",SUBTOTAL(3,$B$4:B26))</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B26" s="25" t="s">
         <v>174</v>
@@ -23406,10 +23415,10 @@
       <c r="BC26" s="71"/>
       <c r="BD26" s="71"/>
     </row>
-    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:56" hidden="1">
       <c r="A27" s="24">
         <f>IF(B27="","",SUBTOTAL(3,$B$4:B27))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B27" s="25" t="s">
         <v>174</v>
@@ -23522,10 +23531,10 @@
       <c r="BC27" s="71"/>
       <c r="BD27" s="71"/>
     </row>
-    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:56" hidden="1">
       <c r="A28" s="24">
         <f>IF(B28="","",SUBTOTAL(3,$B$4:B28))</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="B28" s="25" t="s">
         <v>174</v>
@@ -23638,10 +23647,10 @@
       <c r="BC28" s="71"/>
       <c r="BD28" s="71"/>
     </row>
-    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:56" hidden="1">
       <c r="A29" s="24">
         <f>IF(B29="","",SUBTOTAL(3,$B$4:B29))</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="B29" s="25" t="s">
         <v>174</v>
@@ -23754,10 +23763,10 @@
       <c r="BC29" s="71"/>
       <c r="BD29" s="71"/>
     </row>
-    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:56" hidden="1">
       <c r="A30" s="24">
         <f>IF(B30="","",SUBTOTAL(3,$B$4:B30))</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B30" s="25" t="s">
         <v>174</v>
@@ -23870,10 +23879,10 @@
       <c r="BC30" s="71"/>
       <c r="BD30" s="71"/>
     </row>
-    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:56" hidden="1">
       <c r="A31" s="24">
         <f>IF(B31="","",SUBTOTAL(3,$B$4:B31))</f>
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B31" s="25" t="s">
         <v>174</v>
@@ -23986,10 +23995,10 @@
       <c r="BC31" s="71"/>
       <c r="BD31" s="71"/>
     </row>
-    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:56" hidden="1">
       <c r="A32" s="24">
         <f>IF(B32="","",SUBTOTAL(3,$B$4:B32))</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="B32" s="25" t="s">
         <v>174</v>
@@ -24102,10 +24111,10 @@
       <c r="BC32" s="71"/>
       <c r="BD32" s="71"/>
     </row>
-    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:56" hidden="1">
       <c r="A33" s="24">
         <f>IF(B33="","",SUBTOTAL(3,$B$4:B33))</f>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>174</v>
@@ -24218,10 +24227,10 @@
       <c r="BC33" s="71"/>
       <c r="BD33" s="71"/>
     </row>
-    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:56" hidden="1">
       <c r="A34" s="24">
         <f>IF(B34="","",SUBTOTAL(3,$B$4:B34))</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>174</v>
@@ -24334,10 +24343,10 @@
       <c r="BC34" s="71"/>
       <c r="BD34" s="71"/>
     </row>
-    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:56" hidden="1">
       <c r="A35" s="24">
         <f>IF(B35="","",SUBTOTAL(3,$B$4:B35))</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>174</v>
@@ -24450,10 +24459,10 @@
       <c r="BC35" s="71"/>
       <c r="BD35" s="71"/>
     </row>
-    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:56" hidden="1">
       <c r="A36" s="24">
         <f>IF(B36="","",SUBTOTAL(3,$B$4:B36))</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>174</v>
@@ -24566,10 +24575,10 @@
       <c r="BC36" s="71"/>
       <c r="BD36" s="71"/>
     </row>
-    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:56" hidden="1">
       <c r="A37" s="24">
         <f>IF(B37="","",SUBTOTAL(3,$B$4:B37))</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="B37" s="25" t="s">
         <v>174</v>
@@ -24682,10 +24691,10 @@
       <c r="BC37" s="71"/>
       <c r="BD37" s="71"/>
     </row>
-    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:56" hidden="1">
       <c r="A38" s="24">
         <f>IF(B38="","",SUBTOTAL(3,$B$4:B38))</f>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>174</v>
@@ -24798,10 +24807,10 @@
       <c r="BC38" s="71"/>
       <c r="BD38" s="71"/>
     </row>
-    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:56" hidden="1">
       <c r="A39" s="24">
         <f>IF(B39="","",SUBTOTAL(3,$B$4:B39))</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>174</v>
@@ -24914,10 +24923,10 @@
       <c r="BC39" s="71"/>
       <c r="BD39" s="71"/>
     </row>
-    <row r="40" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:56" hidden="1">
       <c r="A40" s="24">
         <f>IF(B40="","",SUBTOTAL(3,$B$4:B40))</f>
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="B40" s="25" t="s">
         <v>174</v>
@@ -25030,10 +25039,10 @@
       <c r="BC40" s="71"/>
       <c r="BD40" s="71"/>
     </row>
-    <row r="41" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:56" hidden="1">
       <c r="A41" s="24">
         <f>IF(B41="","",SUBTOTAL(3,$B$4:B41))</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>174</v>
@@ -25146,10 +25155,10 @@
       <c r="BC41" s="71"/>
       <c r="BD41" s="71"/>
     </row>
-    <row r="42" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:56" hidden="1">
       <c r="A42" s="24">
         <f>IF(B42="","",SUBTOTAL(3,$B$4:B42))</f>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B42" s="25" t="s">
         <v>174</v>
@@ -25262,10 +25271,10 @@
       <c r="BC42" s="71"/>
       <c r="BD42" s="71"/>
     </row>
-    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:56" hidden="1">
       <c r="A43" s="24">
         <f>IF(B43="","",SUBTOTAL(3,$B$4:B43))</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>174</v>
@@ -25376,10 +25385,10 @@
       <c r="BC43" s="71"/>
       <c r="BD43" s="71"/>
     </row>
-    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:56" hidden="1">
       <c r="A44" s="24">
         <f>IF(B44="","",SUBTOTAL(3,$B$4:B44))</f>
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="B44" s="25" t="s">
         <v>174</v>
@@ -25490,10 +25499,10 @@
       <c r="BC44" s="71"/>
       <c r="BD44" s="71"/>
     </row>
-    <row r="45" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:56" hidden="1">
       <c r="A45" s="24">
         <f>IF(B45="","",SUBTOTAL(3,$B$4:B45))</f>
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>174</v>
@@ -25604,10 +25613,10 @@
       <c r="BC45" s="71"/>
       <c r="BD45" s="71"/>
     </row>
-    <row r="46" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:56" hidden="1">
       <c r="A46" s="24">
         <f>IF(B46="","",SUBTOTAL(3,$B$4:B46))</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>174</v>
@@ -25718,10 +25727,10 @@
       <c r="BC46" s="71"/>
       <c r="BD46" s="71"/>
     </row>
-    <row r="47" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:56" hidden="1">
       <c r="A47" s="24">
         <f>IF(B47="","",SUBTOTAL(3,$B$4:B47))</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B47" s="25" t="s">
         <v>174</v>
@@ -25832,10 +25841,10 @@
       <c r="BC47" s="71"/>
       <c r="BD47" s="71"/>
     </row>
-    <row r="48" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:56" hidden="1">
       <c r="A48" s="24">
         <f>IF(B48="","",SUBTOTAL(3,$B$4:B48))</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="B48" s="25" t="s">
         <v>174</v>
@@ -25946,10 +25955,10 @@
       <c r="BC48" s="71"/>
       <c r="BD48" s="71"/>
     </row>
-    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:56" hidden="1">
       <c r="A49" s="24">
         <f>IF(B49="","",SUBTOTAL(3,$B$4:B49))</f>
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>174</v>
@@ -26060,10 +26069,10 @@
       <c r="BC49" s="71"/>
       <c r="BD49" s="71"/>
     </row>
-    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:56" hidden="1">
       <c r="A50" s="24">
         <f>IF(B50="","",SUBTOTAL(3,$B$4:B50))</f>
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>174</v>
@@ -26174,10 +26183,10 @@
       <c r="BC50" s="71"/>
       <c r="BD50" s="71"/>
     </row>
-    <row r="51" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:56" hidden="1">
       <c r="A51" s="24">
         <f>IF(B51="","",SUBTOTAL(3,$B$4:B51))</f>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="B51" s="25" t="s">
         <v>174</v>
@@ -26288,10 +26297,10 @@
       <c r="BC51" s="71"/>
       <c r="BD51" s="71"/>
     </row>
-    <row r="52" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:56" hidden="1">
       <c r="A52" s="24">
         <f>IF(B52="","",SUBTOTAL(3,$B$4:B52))</f>
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="B52" s="25" t="s">
         <v>174</v>
@@ -26402,10 +26411,10 @@
       <c r="BC52" s="71"/>
       <c r="BD52" s="71"/>
     </row>
-    <row r="53" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:56" hidden="1">
       <c r="A53" s="24">
         <f>IF(B53="","",SUBTOTAL(3,$B$4:B53))</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="B53" s="25" t="s">
         <v>174</v>
@@ -26516,10 +26525,10 @@
       <c r="BC53" s="71"/>
       <c r="BD53" s="71"/>
     </row>
-    <row r="54" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:56" hidden="1">
       <c r="A54" s="24">
         <f>IF(B54="","",SUBTOTAL(3,$B$4:B54))</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="B54" s="25" t="s">
         <v>174</v>
@@ -26630,10 +26639,10 @@
       <c r="BC54" s="71"/>
       <c r="BD54" s="71"/>
     </row>
-    <row r="55" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:56" hidden="1">
       <c r="A55" s="24">
         <f>IF(B55="","",SUBTOTAL(3,$B$4:B55))</f>
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="B55" s="25" t="s">
         <v>174</v>
@@ -26744,10 +26753,10 @@
       <c r="BC55" s="71"/>
       <c r="BD55" s="71"/>
     </row>
-    <row r="56" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:56" hidden="1">
       <c r="A56" s="24">
         <f>IF(B56="","",SUBTOTAL(3,$B$4:B56))</f>
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="B56" s="25" t="s">
         <v>174</v>
@@ -26858,10 +26867,10 @@
       <c r="BC56" s="71"/>
       <c r="BD56" s="71"/>
     </row>
-    <row r="57" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:56" hidden="1">
       <c r="A57" s="24">
         <f>IF(B57="","",SUBTOTAL(3,$B$4:B57))</f>
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B57" s="25" t="s">
         <v>174</v>
@@ -26972,10 +26981,10 @@
       <c r="BC57" s="71"/>
       <c r="BD57" s="71"/>
     </row>
-    <row r="58" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:56" hidden="1">
       <c r="A58" s="24">
         <f>IF(B58="","",SUBTOTAL(3,$B$4:B58))</f>
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="B58" s="25" t="s">
         <v>174</v>
@@ -27088,10 +27097,10 @@
       <c r="BC58" s="71"/>
       <c r="BD58" s="71"/>
     </row>
-    <row r="59" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:56" hidden="1">
       <c r="A59" s="24">
         <f>IF(B59="","",SUBTOTAL(3,$B$4:B59))</f>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="B59" s="25" t="s">
         <v>174</v>
@@ -27204,10 +27213,10 @@
       <c r="BC59" s="71"/>
       <c r="BD59" s="71"/>
     </row>
-    <row r="60" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:56" hidden="1">
       <c r="A60" s="24">
         <f>IF(B60="","",SUBTOTAL(3,$B$4:B60))</f>
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="B60" s="25" t="s">
         <v>174</v>
@@ -27320,10 +27329,10 @@
       <c r="BC60" s="71"/>
       <c r="BD60" s="71"/>
     </row>
-    <row r="61" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:56" hidden="1">
       <c r="A61" s="24">
         <f>IF(B61="","",SUBTOTAL(3,$B$4:B61))</f>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B61" s="25" t="s">
         <v>174</v>
@@ -27436,10 +27445,10 @@
       <c r="BC61" s="71"/>
       <c r="BD61" s="71"/>
     </row>
-    <row r="62" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:56" hidden="1">
       <c r="A62" s="24">
         <f>IF(B62="","",SUBTOTAL(3,$B$4:B62))</f>
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>174</v>
@@ -27552,10 +27561,10 @@
       <c r="BC62" s="71"/>
       <c r="BD62" s="71"/>
     </row>
-    <row r="63" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:56" hidden="1">
       <c r="A63" s="24">
         <f>IF(B63="","",SUBTOTAL(3,$B$4:B63))</f>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B63" s="25" t="s">
         <v>174</v>
@@ -27668,10 +27677,10 @@
       <c r="BC63" s="71"/>
       <c r="BD63" s="71"/>
     </row>
-    <row r="64" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:56" hidden="1">
       <c r="A64" s="24">
         <f>IF(B64="","",SUBTOTAL(3,$B$4:B64))</f>
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="B64" s="25" t="s">
         <v>174</v>
@@ -27784,10 +27793,10 @@
       <c r="BC64" s="71"/>
       <c r="BD64" s="71"/>
     </row>
-    <row r="65" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:56" hidden="1">
       <c r="A65" s="24">
         <f>IF(B65="","",SUBTOTAL(3,$B$4:B65))</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B65" s="25" t="s">
         <v>174</v>
@@ -27900,10 +27909,10 @@
       <c r="BC65" s="71"/>
       <c r="BD65" s="71"/>
     </row>
-    <row r="66" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:56" hidden="1">
       <c r="A66" s="24">
         <f>IF(B66="","",SUBTOTAL(3,$B$4:B66))</f>
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B66" s="25" t="s">
         <v>174</v>
@@ -28016,10 +28025,10 @@
       <c r="BC66" s="71"/>
       <c r="BD66" s="71"/>
     </row>
-    <row r="67" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:56" hidden="1">
       <c r="A67" s="24">
         <f>IF(B67="","",SUBTOTAL(3,$B$4:B67))</f>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>174</v>
@@ -28132,10 +28141,10 @@
       <c r="BC67" s="71"/>
       <c r="BD67" s="71"/>
     </row>
-    <row r="68" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:56" hidden="1">
       <c r="A68" s="24">
         <f>IF(B68="","",SUBTOTAL(3,$B$4:B68))</f>
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="B68" s="25" t="s">
         <v>174</v>
@@ -28248,10 +28257,10 @@
       <c r="BC68" s="71"/>
       <c r="BD68" s="71"/>
     </row>
-    <row r="69" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:56" hidden="1">
       <c r="A69" s="24">
         <f>IF(B69="","",SUBTOTAL(3,$B$4:B69))</f>
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="B69" s="25" t="s">
         <v>174</v>
@@ -28364,10 +28373,10 @@
       <c r="BC69" s="71"/>
       <c r="BD69" s="71"/>
     </row>
-    <row r="70" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:56" hidden="1">
       <c r="A70" s="24">
         <f>IF(B70="","",SUBTOTAL(3,$B$4:B70))</f>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="B70" s="25" t="s">
         <v>174</v>
@@ -28480,10 +28489,10 @@
       <c r="BC70" s="71"/>
       <c r="BD70" s="71"/>
     </row>
-    <row r="71" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:56" hidden="1">
       <c r="A71" s="24">
         <f>IF(B71="","",SUBTOTAL(3,$B$4:B71))</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="B71" s="25" t="s">
         <v>174</v>
@@ -28596,10 +28605,10 @@
       <c r="BC71" s="71"/>
       <c r="BD71" s="71"/>
     </row>
-    <row r="72" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:56" hidden="1">
       <c r="A72" s="24">
         <f>IF(B72="","",SUBTOTAL(3,$B$4:B72))</f>
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="B72" s="25" t="s">
         <v>174</v>
@@ -28712,10 +28721,10 @@
       <c r="BC72" s="71"/>
       <c r="BD72" s="71"/>
     </row>
-    <row r="73" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:56" hidden="1">
       <c r="A73" s="24">
         <f>IF(B73="","",SUBTOTAL(3,$B$4:B73))</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="B73" s="25" t="s">
         <v>174</v>
@@ -28828,10 +28837,10 @@
       <c r="BC73" s="71"/>
       <c r="BD73" s="71"/>
     </row>
-    <row r="74" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:56" hidden="1">
       <c r="A74" s="24">
         <f>IF(B74="","",SUBTOTAL(3,$B$4:B74))</f>
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="B74" s="25" t="s">
         <v>174</v>
@@ -28944,10 +28953,10 @@
       <c r="BC74" s="71"/>
       <c r="BD74" s="71"/>
     </row>
-    <row r="75" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:56" hidden="1">
       <c r="A75" s="24">
         <f>IF(B75="","",SUBTOTAL(3,$B$4:B75))</f>
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="B75" s="25" t="s">
         <v>174</v>
@@ -29060,10 +29069,10 @@
       <c r="BC75" s="71"/>
       <c r="BD75" s="71"/>
     </row>
-    <row r="76" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:56" hidden="1">
       <c r="A76" s="24">
         <f>IF(B76="","",SUBTOTAL(3,$B$4:B76))</f>
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="B76" s="25" t="s">
         <v>174</v>
@@ -29176,10 +29185,10 @@
       <c r="BC76" s="71"/>
       <c r="BD76" s="71"/>
     </row>
-    <row r="77" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:56" hidden="1">
       <c r="A77" s="24">
         <f>IF(B77="","",SUBTOTAL(3,$B$4:B77))</f>
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="B77" s="25" t="s">
         <v>174</v>
@@ -29292,10 +29301,10 @@
       <c r="BC77" s="71"/>
       <c r="BD77" s="71"/>
     </row>
-    <row r="78" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:56" hidden="1">
       <c r="A78" s="24">
         <f>IF(B78="","",SUBTOTAL(3,$B$4:B78))</f>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="B78" s="25" t="s">
         <v>174</v>
@@ -29408,10 +29417,10 @@
       <c r="BC78" s="71"/>
       <c r="BD78" s="71"/>
     </row>
-    <row r="79" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:56" hidden="1">
       <c r="A79" s="24">
         <f>IF(B79="","",SUBTOTAL(3,$B$4:B79))</f>
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="B79" s="25" t="s">
         <v>174</v>
@@ -29524,10 +29533,10 @@
       <c r="BC79" s="71"/>
       <c r="BD79" s="71"/>
     </row>
-    <row r="80" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:56" hidden="1">
       <c r="A80" s="24">
         <f>IF(B80="","",SUBTOTAL(3,$B$4:B80))</f>
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -29640,10 +29649,10 @@
       <c r="BC80" s="71"/>
       <c r="BD80" s="71"/>
     </row>
-    <row r="81" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:56" hidden="1">
       <c r="A81" s="24">
         <f>IF(B81="","",SUBTOTAL(3,$B$4:B81))</f>
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="B81" s="25" t="s">
         <v>174</v>
@@ -29756,10 +29765,10 @@
       <c r="BC81" s="71"/>
       <c r="BD81" s="71"/>
     </row>
-    <row r="82" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:56" hidden="1">
       <c r="A82" s="24">
         <f>IF(B82="","",SUBTOTAL(3,$B$4:B82))</f>
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="B82" s="25" t="s">
         <v>174</v>
@@ -29872,10 +29881,10 @@
       <c r="BC82" s="71"/>
       <c r="BD82" s="71"/>
     </row>
-    <row r="83" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:56" hidden="1">
       <c r="A83" s="24">
         <f>IF(B83="","",SUBTOTAL(3,$B$4:B83))</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="B83" s="25" t="s">
         <v>174</v>
@@ -29988,10 +29997,10 @@
       <c r="BC83" s="71"/>
       <c r="BD83" s="71"/>
     </row>
-    <row r="84" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:56" hidden="1">
       <c r="A84" s="24">
         <f>IF(B84="","",SUBTOTAL(3,$B$4:B84))</f>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="B84" s="25" t="s">
         <v>174</v>
@@ -30104,10 +30113,10 @@
       <c r="BC84" s="71"/>
       <c r="BD84" s="71"/>
     </row>
-    <row r="85" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:56" hidden="1">
       <c r="A85" s="24">
         <f>IF(B85="","",SUBTOTAL(3,$B$4:B85))</f>
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="B85" s="25" t="s">
         <v>174</v>
@@ -30220,10 +30229,10 @@
       <c r="BC85" s="71"/>
       <c r="BD85" s="71"/>
     </row>
-    <row r="86" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:56" hidden="1">
       <c r="A86" s="24">
         <f>IF(B86="","",SUBTOTAL(3,$B$4:B86))</f>
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="B86" s="25" t="s">
         <v>174</v>
@@ -30336,10 +30345,10 @@
       <c r="BC86" s="71"/>
       <c r="BD86" s="71"/>
     </row>
-    <row r="87" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:56" hidden="1">
       <c r="A87" s="24">
         <f>IF(B87="","",SUBTOTAL(3,$B$4:B87))</f>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="B87" s="25" t="s">
         <v>174</v>
@@ -30452,10 +30461,10 @@
       <c r="BC87" s="71"/>
       <c r="BD87" s="71"/>
     </row>
-    <row r="88" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:56" hidden="1">
       <c r="A88" s="24">
         <f>IF(B88="","",SUBTOTAL(3,$B$4:B88))</f>
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="B88" s="25" t="s">
         <v>174</v>
@@ -30568,10 +30577,10 @@
       <c r="BC88" s="71"/>
       <c r="BD88" s="71"/>
     </row>
-    <row r="89" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:56" hidden="1">
       <c r="A89" s="24">
         <f>IF(B89="","",SUBTOTAL(3,$B$4:B89))</f>
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="B89" s="25" t="s">
         <v>174</v>
@@ -30684,10 +30693,10 @@
       <c r="BC89" s="71"/>
       <c r="BD89" s="71"/>
     </row>
-    <row r="90" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:56" hidden="1">
       <c r="A90" s="24">
         <f>IF(B90="","",SUBTOTAL(3,$B$4:B90))</f>
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="B90" s="25" t="s">
         <v>174</v>
@@ -30800,10 +30809,10 @@
       <c r="BC90" s="71"/>
       <c r="BD90" s="71"/>
     </row>
-    <row r="91" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:56" hidden="1">
       <c r="A91" s="24">
         <f>IF(B91="","",SUBTOTAL(3,$B$4:B91))</f>
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="B91" s="25" t="s">
         <v>174</v>
@@ -30916,10 +30925,10 @@
       <c r="BC91" s="71"/>
       <c r="BD91" s="71"/>
     </row>
-    <row r="92" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:56" hidden="1">
       <c r="A92" s="24">
         <f>IF(B92="","",SUBTOTAL(3,$B$4:B92))</f>
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="B92" s="25" t="s">
         <v>174</v>
@@ -31030,10 +31039,10 @@
       <c r="BC92" s="71"/>
       <c r="BD92" s="71"/>
     </row>
-    <row r="93" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:56" hidden="1">
       <c r="A93" s="24">
         <f>IF(B93="","",SUBTOTAL(3,$B$4:B93))</f>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="B93" s="25" t="s">
         <v>174</v>
@@ -31144,10 +31153,10 @@
       <c r="BC93" s="71"/>
       <c r="BD93" s="71"/>
     </row>
-    <row r="94" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:56" hidden="1">
       <c r="A94" s="24">
         <f>IF(B94="","",SUBTOTAL(3,$B$4:B94))</f>
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="B94" s="25" t="s">
         <v>174</v>
@@ -31258,10 +31267,10 @@
       <c r="BC94" s="71"/>
       <c r="BD94" s="71"/>
     </row>
-    <row r="95" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:56" hidden="1">
       <c r="A95" s="24">
         <f>IF(B95="","",SUBTOTAL(3,$B$4:B95))</f>
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="B95" s="25" t="s">
         <v>174</v>
@@ -31372,10 +31381,10 @@
       <c r="BC95" s="71"/>
       <c r="BD95" s="71"/>
     </row>
-    <row r="96" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:56" hidden="1">
       <c r="A96" s="24">
         <f>IF(B96="","",SUBTOTAL(3,$B$4:B96))</f>
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="B96" s="25" t="s">
         <v>174</v>
@@ -31486,10 +31495,10 @@
       <c r="BC96" s="71"/>
       <c r="BD96" s="71"/>
     </row>
-    <row r="97" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:56" hidden="1">
       <c r="A97" s="24">
         <f>IF(B97="","",SUBTOTAL(3,$B$4:B97))</f>
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="B97" s="25" t="s">
         <v>174</v>
@@ -31600,10 +31609,10 @@
       <c r="BC97" s="71"/>
       <c r="BD97" s="71"/>
     </row>
-    <row r="98" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:56" hidden="1">
       <c r="A98" s="24">
         <f>IF(B98="","",SUBTOTAL(3,$B$4:B98))</f>
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="B98" s="25" t="s">
         <v>174</v>
@@ -31714,10 +31723,10 @@
       <c r="BC98" s="71"/>
       <c r="BD98" s="71"/>
     </row>
-    <row r="99" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:56" hidden="1">
       <c r="A99" s="24">
         <f>IF(B99="","",SUBTOTAL(3,$B$4:B99))</f>
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="B99" s="25" t="s">
         <v>174</v>
@@ -31828,10 +31837,10 @@
       <c r="BC99" s="71"/>
       <c r="BD99" s="71"/>
     </row>
-    <row r="100" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:56" hidden="1">
       <c r="A100" s="24">
         <f>IF(B100="","",SUBTOTAL(3,$B$4:B100))</f>
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="B100" s="25" t="s">
         <v>174</v>
@@ -31942,10 +31951,10 @@
       <c r="BC100" s="71"/>
       <c r="BD100" s="71"/>
     </row>
-    <row r="101" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:56" hidden="1">
       <c r="A101" s="24">
         <f>IF(B101="","",SUBTOTAL(3,$B$4:B101))</f>
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="B101" s="25" t="s">
         <v>174</v>
@@ -32056,10 +32065,10 @@
       <c r="BC101" s="71"/>
       <c r="BD101" s="71"/>
     </row>
-    <row r="102" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:56" hidden="1">
       <c r="A102" s="24">
         <f>IF(B102="","",SUBTOTAL(3,$B$4:B102))</f>
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>174</v>
@@ -32170,10 +32179,10 @@
       <c r="BC102" s="71"/>
       <c r="BD102" s="71"/>
     </row>
-    <row r="103" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:56" hidden="1">
       <c r="A103" s="24">
         <f>IF(B103="","",SUBTOTAL(3,$B$4:B103))</f>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B103" s="25" t="s">
         <v>174</v>
@@ -32284,10 +32293,10 @@
       <c r="BC103" s="71"/>
       <c r="BD103" s="71"/>
     </row>
-    <row r="104" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:56" hidden="1">
       <c r="A104" s="24">
         <f>IF(B104="","",SUBTOTAL(3,$B$4:B104))</f>
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="B104" s="25" t="s">
         <v>174</v>
@@ -32398,10 +32407,10 @@
       <c r="BC104" s="71"/>
       <c r="BD104" s="71"/>
     </row>
-    <row r="105" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:56" hidden="1">
       <c r="A105" s="24">
         <f>IF(B105="","",SUBTOTAL(3,$B$4:B105))</f>
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="B105" s="25" t="s">
         <v>174</v>
@@ -32512,10 +32521,10 @@
       <c r="BC105" s="71"/>
       <c r="BD105" s="71"/>
     </row>
-    <row r="106" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:56" hidden="1">
       <c r="A106" s="24">
         <f>IF(B106="","",SUBTOTAL(3,$B$4:B106))</f>
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="B106" s="25" t="s">
         <v>174</v>
@@ -32626,10 +32635,10 @@
       <c r="BC106" s="71"/>
       <c r="BD106" s="71"/>
     </row>
-    <row r="107" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:56" hidden="1">
       <c r="A107" s="24">
         <f>IF(B107="","",SUBTOTAL(3,$B$4:B107))</f>
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="B107" s="25" t="s">
         <v>174</v>
@@ -32742,10 +32751,10 @@
       <c r="BC107" s="71"/>
       <c r="BD107" s="71"/>
     </row>
-    <row r="108" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:56" hidden="1">
       <c r="A108" s="24">
         <f>IF(B108="","",SUBTOTAL(3,$B$4:B108))</f>
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="B108" s="25" t="s">
         <v>174</v>
@@ -32858,10 +32867,10 @@
       <c r="BC108" s="71"/>
       <c r="BD108" s="71"/>
     </row>
-    <row r="109" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:56" hidden="1">
       <c r="A109" s="24">
         <f>IF(B109="","",SUBTOTAL(3,$B$4:B109))</f>
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="B109" s="25" t="s">
         <v>174</v>
@@ -32974,10 +32983,10 @@
       <c r="BC109" s="71"/>
       <c r="BD109" s="71"/>
     </row>
-    <row r="110" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:56" hidden="1">
       <c r="A110" s="24">
         <f>IF(B110="","",SUBTOTAL(3,$B$4:B110))</f>
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="B110" s="25" t="s">
         <v>174</v>
@@ -33090,10 +33099,10 @@
       <c r="BC110" s="71"/>
       <c r="BD110" s="71"/>
     </row>
-    <row r="111" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:56" hidden="1">
       <c r="A111" s="24">
         <f>IF(B111="","",SUBTOTAL(3,$B$4:B111))</f>
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="B111" s="25" t="s">
         <v>174</v>
@@ -33206,10 +33215,10 @@
       <c r="BC111" s="71"/>
       <c r="BD111" s="71"/>
     </row>
-    <row r="112" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:56" hidden="1">
       <c r="A112" s="24">
         <f>IF(B112="","",SUBTOTAL(3,$B$4:B112))</f>
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="B112" s="25" t="s">
         <v>174</v>
@@ -33322,10 +33331,10 @@
       <c r="BC112" s="71"/>
       <c r="BD112" s="71"/>
     </row>
-    <row r="113" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:56" hidden="1">
       <c r="A113" s="24">
         <f>IF(B113="","",SUBTOTAL(3,$B$4:B113))</f>
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="B113" s="25" t="s">
         <v>174</v>
@@ -33438,10 +33447,10 @@
       <c r="BC113" s="71"/>
       <c r="BD113" s="71"/>
     </row>
-    <row r="114" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:56" hidden="1">
       <c r="A114" s="24">
         <f>IF(B114="","",SUBTOTAL(3,$B$4:B114))</f>
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>174</v>
@@ -33554,10 +33563,10 @@
       <c r="BC114" s="71"/>
       <c r="BD114" s="71"/>
     </row>
-    <row r="115" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:56" hidden="1">
       <c r="A115" s="24">
         <f>IF(B115="","",SUBTOTAL(3,$B$4:B115))</f>
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="B115" s="25" t="s">
         <v>174</v>
@@ -33670,10 +33679,10 @@
       <c r="BC115" s="71"/>
       <c r="BD115" s="71"/>
     </row>
-    <row r="116" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:56" hidden="1">
       <c r="A116" s="24">
         <f>IF(B116="","",SUBTOTAL(3,$B$4:B116))</f>
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>174</v>
@@ -33786,10 +33795,10 @@
       <c r="BC116" s="71"/>
       <c r="BD116" s="71"/>
     </row>
-    <row r="117" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:56" hidden="1">
       <c r="A117" s="24">
         <f>IF(B117="","",SUBTOTAL(3,$B$4:B117))</f>
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="B117" s="25" t="s">
         <v>174</v>
@@ -33902,10 +33911,10 @@
       <c r="BC117" s="71"/>
       <c r="BD117" s="71"/>
     </row>
-    <row r="118" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:56" hidden="1">
       <c r="A118" s="24">
         <f>IF(B118="","",SUBTOTAL(3,$B$4:B118))</f>
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="B118" s="25" t="s">
         <v>174</v>
@@ -34018,10 +34027,10 @@
       <c r="BC118" s="71"/>
       <c r="BD118" s="71"/>
     </row>
-    <row r="119" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:56" hidden="1">
       <c r="A119" s="24">
         <f>IF(B119="","",SUBTOTAL(3,$B$4:B119))</f>
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="B119" s="25" t="s">
         <v>174</v>
@@ -34134,10 +34143,10 @@
       <c r="BC119" s="71"/>
       <c r="BD119" s="71"/>
     </row>
-    <row r="120" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:56" hidden="1">
       <c r="A120" s="24">
         <f>IF(B120="","",SUBTOTAL(3,$B$4:B120))</f>
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="B120" s="25" t="s">
         <v>174</v>
@@ -34250,10 +34259,10 @@
       <c r="BC120" s="71"/>
       <c r="BD120" s="71"/>
     </row>
-    <row r="121" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:56" hidden="1">
       <c r="A121" s="24">
         <f>IF(B121="","",SUBTOTAL(3,$B$4:B121))</f>
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="B121" s="25" t="s">
         <v>174</v>
@@ -34366,10 +34375,10 @@
       <c r="BC121" s="71"/>
       <c r="BD121" s="71"/>
     </row>
-    <row r="122" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:56" hidden="1">
       <c r="A122" s="24">
         <f>IF(B122="","",SUBTOTAL(3,$B$4:B122))</f>
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="B122" s="25" t="s">
         <v>174</v>
@@ -34482,10 +34491,10 @@
       <c r="BC122" s="71"/>
       <c r="BD122" s="71"/>
     </row>
-    <row r="123" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:56" hidden="1">
       <c r="A123" s="24">
         <f>IF(B123="","",SUBTOTAL(3,$B$4:B123))</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="B123" s="25" t="s">
         <v>174</v>
@@ -34598,10 +34607,10 @@
       <c r="BC123" s="71"/>
       <c r="BD123" s="71"/>
     </row>
-    <row r="124" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:56" hidden="1">
       <c r="A124" s="24">
         <f>IF(B124="","",SUBTOTAL(3,$B$4:B124))</f>
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="B124" s="25" t="s">
         <v>174</v>
@@ -34714,10 +34723,10 @@
       <c r="BC124" s="71"/>
       <c r="BD124" s="71"/>
     </row>
-    <row r="125" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:56" hidden="1">
       <c r="A125" s="24">
         <f>IF(B125="","",SUBTOTAL(3,$B$4:B125))</f>
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="B125" s="25" t="s">
         <v>174</v>
@@ -34830,10 +34839,10 @@
       <c r="BC125" s="71"/>
       <c r="BD125" s="71"/>
     </row>
-    <row r="126" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:56" hidden="1">
       <c r="A126" s="24">
         <f>IF(B126="","",SUBTOTAL(3,$B$4:B126))</f>
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="B126" s="25" t="s">
         <v>174</v>
@@ -34946,10 +34955,10 @@
       <c r="BC126" s="71"/>
       <c r="BD126" s="71"/>
     </row>
-    <row r="127" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:56" hidden="1">
       <c r="A127" s="24">
         <f>IF(B127="","",SUBTOTAL(3,$B$4:B127))</f>
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="B127" s="25" t="s">
         <v>174</v>
@@ -35062,10 +35071,10 @@
       <c r="BC127" s="71"/>
       <c r="BD127" s="71"/>
     </row>
-    <row r="128" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:56" hidden="1">
       <c r="A128" s="24">
         <f>IF(B128="","",SUBTOTAL(3,$B$4:B128))</f>
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="B128" s="25" t="s">
         <v>174</v>
@@ -35178,10 +35187,10 @@
       <c r="BC128" s="71"/>
       <c r="BD128" s="71"/>
     </row>
-    <row r="129" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:56" hidden="1">
       <c r="A129" s="24">
         <f>IF(B129="","",SUBTOTAL(3,$B$4:B129))</f>
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="B129" s="25" t="s">
         <v>174</v>
@@ -35294,10 +35303,10 @@
       <c r="BC129" s="71"/>
       <c r="BD129" s="71"/>
     </row>
-    <row r="130" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:56" hidden="1">
       <c r="A130" s="24">
         <f>IF(B130="","",SUBTOTAL(3,$B$4:B130))</f>
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="B130" s="25" t="s">
         <v>174</v>
@@ -35410,10 +35419,10 @@
       <c r="BC130" s="71"/>
       <c r="BD130" s="71"/>
     </row>
-    <row r="131" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:56" hidden="1">
       <c r="A131" s="24">
         <f>IF(B131="","",SUBTOTAL(3,$B$4:B131))</f>
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="B131" s="25" t="s">
         <v>174</v>
@@ -35526,10 +35535,10 @@
       <c r="BC131" s="71"/>
       <c r="BD131" s="71"/>
     </row>
-    <row r="132" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:56" hidden="1">
       <c r="A132" s="24">
         <f>IF(B132="","",SUBTOTAL(3,$B$4:B132))</f>
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="B132" s="25" t="s">
         <v>174</v>
@@ -35642,10 +35651,10 @@
       <c r="BC132" s="71"/>
       <c r="BD132" s="71"/>
     </row>
-    <row r="133" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:56" hidden="1">
       <c r="A133" s="24">
         <f>IF(B133="","",SUBTOTAL(3,$B$4:B133))</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="B133" s="25" t="s">
         <v>174</v>
@@ -35758,10 +35767,10 @@
       <c r="BC133" s="71"/>
       <c r="BD133" s="71"/>
     </row>
-    <row r="134" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:56" hidden="1">
       <c r="A134" s="24">
         <f>IF(B134="","",SUBTOTAL(3,$B$4:B134))</f>
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="B134" s="25" t="s">
         <v>174</v>
@@ -35874,10 +35883,10 @@
       <c r="BC134" s="71"/>
       <c r="BD134" s="71"/>
     </row>
-    <row r="135" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:56" hidden="1">
       <c r="A135" s="24">
         <f>IF(B135="","",SUBTOTAL(3,$B$4:B135))</f>
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="B135" s="25" t="s">
         <v>174</v>
@@ -35990,10 +35999,10 @@
       <c r="BC135" s="71"/>
       <c r="BD135" s="71"/>
     </row>
-    <row r="136" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:56" hidden="1">
       <c r="A136" s="24">
         <f>IF(B136="","",SUBTOTAL(3,$B$4:B136))</f>
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="B136" s="25" t="s">
         <v>174</v>
@@ -36106,10 +36115,10 @@
       <c r="BC136" s="71"/>
       <c r="BD136" s="71"/>
     </row>
-    <row r="137" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:56" hidden="1">
       <c r="A137" s="24">
         <f>IF(B137="","",SUBTOTAL(3,$B$4:B137))</f>
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="B137" s="25" t="s">
         <v>174</v>
@@ -36222,10 +36231,10 @@
       <c r="BC137" s="71"/>
       <c r="BD137" s="71"/>
     </row>
-    <row r="138" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:56" hidden="1">
       <c r="A138" s="24">
         <f>IF(B138="","",SUBTOTAL(3,$B$4:B138))</f>
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B138" s="25" t="s">
         <v>174</v>
@@ -36338,10 +36347,10 @@
       <c r="BC138" s="71"/>
       <c r="BD138" s="71"/>
     </row>
-    <row r="139" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:56" hidden="1">
       <c r="A139" s="24">
         <f>IF(B139="","",SUBTOTAL(3,$B$4:B139))</f>
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="B139" s="25" t="s">
         <v>174</v>
@@ -36454,10 +36463,10 @@
       <c r="BC139" s="71"/>
       <c r="BD139" s="71"/>
     </row>
-    <row r="140" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:56" hidden="1">
       <c r="A140" s="24">
         <f>IF(B140="","",SUBTOTAL(3,$B$4:B140))</f>
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="B140" s="25" t="s">
         <v>174</v>
@@ -36570,10 +36579,10 @@
       <c r="BC140" s="71"/>
       <c r="BD140" s="71"/>
     </row>
-    <row r="141" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:56" hidden="1">
       <c r="A141" s="24">
         <f>IF(B141="","",SUBTOTAL(3,$B$4:B141))</f>
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="B141" s="25" t="s">
         <v>174</v>
@@ -36696,10 +36705,10 @@
       <c r="BC141" s="71"/>
       <c r="BD141" s="71"/>
     </row>
-    <row r="142" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:56" hidden="1">
       <c r="A142" s="24">
         <f>IF(B142="","",SUBTOTAL(3,$B$4:B142))</f>
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="B142" s="25" t="s">
         <v>174</v>
@@ -36822,10 +36831,10 @@
       <c r="BC142" s="71"/>
       <c r="BD142" s="71"/>
     </row>
-    <row r="143" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:56">
       <c r="A143" s="24">
         <f>IF(B143="","",SUBTOTAL(3,$B$4:B143))</f>
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="B143" s="25" t="s">
         <v>174</v>
@@ -36940,24 +36949,30 @@
         <f t="shared" si="35"/>
         <v>2070.6</v>
       </c>
-      <c r="AW143" s="35"/>
-      <c r="AX143" s="30"/>
+      <c r="AW143" s="35">
+        <v>46297</v>
+      </c>
+      <c r="AX143" s="30">
+        <v>1</v>
+      </c>
       <c r="AY143" s="32">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>2070.6</v>
       </c>
       <c r="AZ143" s="30" t="s">
         <v>265</v>
       </c>
-      <c r="BA143" s="63"/>
+      <c r="BA143" s="63" t="s">
+        <v>278</v>
+      </c>
       <c r="BB143" s="71"/>
       <c r="BC143" s="71"/>
       <c r="BD143" s="71"/>
     </row>
-    <row r="144" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:56" hidden="1">
       <c r="A144" s="24">
         <f>IF(B144="","",SUBTOTAL(3,$B$4:B144))</f>
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="B144" s="25" t="s">
         <v>174</v>
@@ -37086,10 +37101,10 @@
       <c r="BC144" s="71"/>
       <c r="BD144" s="71"/>
     </row>
-    <row r="145" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:56" hidden="1">
       <c r="A145" s="24">
         <f>IF(B145="","",SUBTOTAL(3,$B$4:B145))</f>
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="B145" s="25" t="s">
         <v>174</v>
@@ -37212,10 +37227,10 @@
       <c r="BC145" s="71"/>
       <c r="BD145" s="71"/>
     </row>
-    <row r="146" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:56" hidden="1">
       <c r="A146" s="24">
         <f>IF(B146="","",SUBTOTAL(3,$B$4:B146))</f>
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="B146" s="25" t="s">
         <v>174</v>
@@ -37338,10 +37353,10 @@
       <c r="BC146" s="71"/>
       <c r="BD146" s="71"/>
     </row>
-    <row r="147" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:56" hidden="1">
       <c r="A147" s="24">
         <f>IF(B147="","",SUBTOTAL(3,$B$4:B147))</f>
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="B147" s="25" t="s">
         <v>174</v>
@@ -37464,10 +37479,10 @@
       <c r="BC147" s="71"/>
       <c r="BD147" s="71"/>
     </row>
-    <row r="148" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:56" hidden="1">
       <c r="A148" s="24">
         <f>IF(B148="","",SUBTOTAL(3,$B$4:B148))</f>
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="B148" s="25" t="s">
         <v>174</v>
@@ -37590,10 +37605,10 @@
       <c r="BC148" s="71"/>
       <c r="BD148" s="71"/>
     </row>
-    <row r="149" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:56" hidden="1">
       <c r="A149" s="24">
         <f>IF(B149="","",SUBTOTAL(3,$B$4:B149))</f>
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="B149" s="25" t="s">
         <v>174</v>
@@ -37716,10 +37731,10 @@
       <c r="BC149" s="71"/>
       <c r="BD149" s="71"/>
     </row>
-    <row r="150" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:56" hidden="1">
       <c r="A150" s="24">
         <f>IF(B150="","",SUBTOTAL(3,$B$4:B150))</f>
-        <v>147</v>
+        <v>1</v>
       </c>
       <c r="B150" s="25" t="s">
         <v>174</v>
@@ -37842,10 +37857,10 @@
       <c r="BC150" s="71"/>
       <c r="BD150" s="71"/>
     </row>
-    <row r="151" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:56" hidden="1">
       <c r="A151" s="24">
         <f>IF(B151="","",SUBTOTAL(3,$B$4:B151))</f>
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="B151" s="25" t="s">
         <v>174</v>
@@ -37968,10 +37983,10 @@
       <c r="BC151" s="71"/>
       <c r="BD151" s="71"/>
     </row>
-    <row r="152" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:56" hidden="1">
       <c r="A152" s="24">
         <f>IF(B152="","",SUBTOTAL(3,$B$4:B152))</f>
-        <v>149</v>
+        <v>1</v>
       </c>
       <c r="B152" s="25" t="s">
         <v>174</v>
@@ -38094,10 +38109,10 @@
       <c r="BC152" s="71"/>
       <c r="BD152" s="71"/>
     </row>
-    <row r="153" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:56" hidden="1">
       <c r="A153" s="24">
         <f>IF(B153="","",SUBTOTAL(3,$B$4:B153))</f>
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="B153" s="25" t="s">
         <v>174</v>
@@ -38220,10 +38235,10 @@
       <c r="BC153" s="71"/>
       <c r="BD153" s="71"/>
     </row>
-    <row r="154" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:56" hidden="1">
       <c r="A154" s="24">
         <f>IF(B154="","",SUBTOTAL(3,$B$4:B154))</f>
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="B154" s="25" t="s">
         <v>174</v>
@@ -38358,10 +38373,10 @@
       <c r="BC154" s="71"/>
       <c r="BD154" s="71"/>
     </row>
-    <row r="155" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:56" hidden="1">
       <c r="A155" s="24">
         <f>IF(B155="","",SUBTOTAL(3,$B$4:B155))</f>
-        <v>152</v>
+        <v>1</v>
       </c>
       <c r="B155" s="25" t="s">
         <v>174</v>
@@ -38496,10 +38511,10 @@
       <c r="BC155" s="71"/>
       <c r="BD155" s="71"/>
     </row>
-    <row r="156" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:56" hidden="1">
       <c r="A156" s="24">
         <f>IF(B156="","",SUBTOTAL(3,$B$4:B156))</f>
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="B156" s="25" t="s">
         <v>174</v>
@@ -38640,10 +38655,10 @@
       <c r="BC156" s="71"/>
       <c r="BD156" s="71"/>
     </row>
-    <row r="157" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:56" hidden="1">
       <c r="A157" s="24">
         <f>IF(B157="","",SUBTOTAL(3,$B$4:B157))</f>
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="B157" s="25" t="s">
         <v>174</v>
@@ -38784,10 +38799,10 @@
       <c r="BC157" s="71"/>
       <c r="BD157" s="71"/>
     </row>
-    <row r="158" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:56" hidden="1">
       <c r="A158" s="24">
         <f>IF(B158="","",SUBTOTAL(3,$B$4:B158))</f>
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="B158" s="25" t="s">
         <v>174</v>
@@ -38928,10 +38943,10 @@
       <c r="BC158" s="71"/>
       <c r="BD158" s="71"/>
     </row>
-    <row r="159" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:56" hidden="1">
       <c r="A159" s="24">
         <f>IF(B159="","",SUBTOTAL(3,$B$4:B159))</f>
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="B159" s="25" t="s">
         <v>174</v>
@@ -39046,10 +39061,10 @@
       <c r="BC159" s="71"/>
       <c r="BD159" s="71"/>
     </row>
-    <row r="160" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:56" hidden="1">
       <c r="A160" s="24">
         <f>IF(B160="","",SUBTOTAL(3,$B$4:B160))</f>
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="B160" s="25" t="s">
         <v>174</v>
@@ -39164,10 +39179,10 @@
       <c r="BC160" s="71"/>
       <c r="BD160" s="71"/>
     </row>
-    <row r="161" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:56" hidden="1">
       <c r="A161" s="24">
         <f>IF(B161="","",SUBTOTAL(3,$B$4:B161))</f>
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="B161" s="25" t="s">
         <v>174</v>
@@ -39282,10 +39297,10 @@
       <c r="BC161" s="71"/>
       <c r="BD161" s="71"/>
     </row>
-    <row r="162" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:56" hidden="1">
       <c r="A162" s="24">
         <f>IF(B162="","",SUBTOTAL(3,$B$4:B162))</f>
-        <v>159</v>
+        <v>1</v>
       </c>
       <c r="B162" s="25" t="s">
         <v>174</v>
@@ -39400,10 +39415,10 @@
       <c r="BC162" s="71"/>
       <c r="BD162" s="71"/>
     </row>
-    <row r="163" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:56" hidden="1">
       <c r="A163" s="24">
         <f>IF(B163="","",SUBTOTAL(3,$B$4:B163))</f>
-        <v>160</v>
+        <v>1</v>
       </c>
       <c r="B163" s="25" t="s">
         <v>174</v>
@@ -39518,10 +39533,10 @@
       <c r="BC163" s="71"/>
       <c r="BD163" s="71"/>
     </row>
-    <row r="164" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:56" hidden="1">
       <c r="A164" s="24">
         <f>IF(B164="","",SUBTOTAL(3,$B$4:B164))</f>
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="B164" s="25" t="s">
         <v>174</v>
@@ -39636,10 +39651,10 @@
       <c r="BC164" s="71"/>
       <c r="BD164" s="71"/>
     </row>
-    <row r="165" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:56" hidden="1">
       <c r="A165" s="24">
         <f>IF(B165="","",SUBTOTAL(3,$B$4:B165))</f>
-        <v>162</v>
+        <v>1</v>
       </c>
       <c r="B165" s="25" t="s">
         <v>174</v>
@@ -39754,10 +39769,10 @@
       <c r="BC165" s="71"/>
       <c r="BD165" s="71"/>
     </row>
-    <row r="166" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:56" hidden="1">
       <c r="A166" s="24">
         <f>IF(B166="","",SUBTOTAL(3,$B$4:B166))</f>
-        <v>163</v>
+        <v>1</v>
       </c>
       <c r="B166" s="25" t="s">
         <v>174</v>
@@ -39872,10 +39887,10 @@
       <c r="BC166" s="71"/>
       <c r="BD166" s="71"/>
     </row>
-    <row r="167" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:56" hidden="1">
       <c r="A167" s="24">
         <f>IF(B167="","",SUBTOTAL(3,$B$4:B167))</f>
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="B167" s="25" t="s">
         <v>174</v>
@@ -39990,10 +40005,10 @@
       <c r="BC167" s="71"/>
       <c r="BD167" s="71"/>
     </row>
-    <row r="168" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:56" hidden="1">
       <c r="A168" s="24">
         <f>IF(B168="","",SUBTOTAL(3,$B$4:B168))</f>
-        <v>165</v>
+        <v>1</v>
       </c>
       <c r="B168" s="25" t="s">
         <v>174</v>
@@ -40108,10 +40123,10 @@
       <c r="BC168" s="71"/>
       <c r="BD168" s="71"/>
     </row>
-    <row r="169" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:56" hidden="1">
       <c r="A169" s="24">
         <f>IF(B169="","",SUBTOTAL(3,$B$4:B169))</f>
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="B169" s="25" t="s">
         <v>174</v>
@@ -40226,10 +40241,10 @@
       <c r="BC169" s="71"/>
       <c r="BD169" s="71"/>
     </row>
-    <row r="170" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:56" hidden="1">
       <c r="A170" s="24">
         <f>IF(B170="","",SUBTOTAL(3,$B$4:B170))</f>
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="B170" s="25" t="s">
         <v>174</v>
@@ -40344,10 +40359,10 @@
       <c r="BC170" s="71"/>
       <c r="BD170" s="71"/>
     </row>
-    <row r="171" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:56" hidden="1">
       <c r="A171" s="24">
         <f>IF(B171="","",SUBTOTAL(3,$B$4:B171))</f>
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="B171" s="25" t="s">
         <v>174</v>
@@ -40462,10 +40477,10 @@
       <c r="BC171" s="71"/>
       <c r="BD171" s="71"/>
     </row>
-    <row r="172" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:56" hidden="1">
       <c r="A172" s="24">
         <f>IF(B172="","",SUBTOTAL(3,$B$4:B172))</f>
-        <v>169</v>
+        <v>1</v>
       </c>
       <c r="B172" s="25" t="s">
         <v>174</v>
@@ -40580,10 +40595,10 @@
       <c r="BC172" s="71"/>
       <c r="BD172" s="71"/>
     </row>
-    <row r="173" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:56" hidden="1">
       <c r="A173" s="24">
         <f>IF(B173="","",SUBTOTAL(3,$B$4:B173))</f>
-        <v>170</v>
+        <v>1</v>
       </c>
       <c r="B173" s="25" t="s">
         <v>174</v>
@@ -40698,10 +40713,10 @@
       <c r="BC173" s="71"/>
       <c r="BD173" s="71"/>
     </row>
-    <row r="174" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:56" hidden="1">
       <c r="A174" s="24">
         <f>IF(B174="","",SUBTOTAL(3,$B$4:B174))</f>
-        <v>171</v>
+        <v>1</v>
       </c>
       <c r="B174" s="25" t="s">
         <v>174</v>
@@ -40816,10 +40831,10 @@
       <c r="BC174" s="71"/>
       <c r="BD174" s="71"/>
     </row>
-    <row r="175" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:56" hidden="1">
       <c r="A175" s="24">
         <f>IF(B175="","",SUBTOTAL(3,$B$4:B175))</f>
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="B175" s="25" t="s">
         <v>174</v>
@@ -40934,10 +40949,10 @@
       <c r="BC175" s="71"/>
       <c r="BD175" s="71"/>
     </row>
-    <row r="176" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:56" hidden="1">
       <c r="A176" s="24">
         <f>IF(B176="","",SUBTOTAL(3,$B$4:B176))</f>
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="B176" s="25" t="s">
         <v>174</v>
@@ -41052,10 +41067,10 @@
       <c r="BC176" s="71"/>
       <c r="BD176" s="71"/>
     </row>
-    <row r="177" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:56" hidden="1">
       <c r="A177" s="24">
         <f>IF(B177="","",SUBTOTAL(3,$B$4:B177))</f>
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="B177" s="25" t="s">
         <v>174</v>
@@ -41170,10 +41185,10 @@
       <c r="BC177" s="71"/>
       <c r="BD177" s="71"/>
     </row>
-    <row r="178" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:56" hidden="1">
       <c r="A178" s="24">
         <f>IF(B178="","",SUBTOTAL(3,$B$4:B178))</f>
-        <v>175</v>
+        <v>1</v>
       </c>
       <c r="B178" s="25" t="s">
         <v>174</v>
@@ -41288,10 +41303,10 @@
       <c r="BC178" s="71"/>
       <c r="BD178" s="71"/>
     </row>
-    <row r="179" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:56" hidden="1">
       <c r="A179" s="24">
         <f>IF(B179="","",SUBTOTAL(3,$B$4:B179))</f>
-        <v>176</v>
+        <v>1</v>
       </c>
       <c r="B179" s="25" t="s">
         <v>174</v>
@@ -41406,10 +41421,10 @@
       <c r="BC179" s="71"/>
       <c r="BD179" s="71"/>
     </row>
-    <row r="180" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:56" hidden="1">
       <c r="A180" s="24">
         <f>IF(B180="","",SUBTOTAL(3,$B$4:B180))</f>
-        <v>177</v>
+        <v>1</v>
       </c>
       <c r="B180" s="25" t="s">
         <v>174</v>
@@ -41524,10 +41539,10 @@
       <c r="BC180" s="71"/>
       <c r="BD180" s="71"/>
     </row>
-    <row r="181" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:56" hidden="1">
       <c r="A181" s="24">
         <f>IF(B181="","",SUBTOTAL(3,$B$4:B181))</f>
-        <v>178</v>
+        <v>1</v>
       </c>
       <c r="B181" s="25" t="s">
         <v>174</v>
@@ -41642,10 +41657,10 @@
       <c r="BC181" s="71"/>
       <c r="BD181" s="71"/>
     </row>
-    <row r="182" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:56" hidden="1">
       <c r="A182" s="24">
         <f>IF(B182="","",SUBTOTAL(3,$B$4:B182))</f>
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="B182" s="25" t="s">
         <v>174</v>
@@ -41760,10 +41775,10 @@
       <c r="BC182" s="71"/>
       <c r="BD182" s="71"/>
     </row>
-    <row r="183" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:56" hidden="1">
       <c r="A183" s="24">
         <f>IF(B183="","",SUBTOTAL(3,$B$4:B183))</f>
-        <v>180</v>
+        <v>1</v>
       </c>
       <c r="B183" s="25" t="s">
         <v>174</v>
@@ -41878,10 +41893,10 @@
       <c r="BC183" s="71"/>
       <c r="BD183" s="71"/>
     </row>
-    <row r="184" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:56" hidden="1">
       <c r="A184" s="24">
         <f>IF(B184="","",SUBTOTAL(3,$B$4:B184))</f>
-        <v>181</v>
+        <v>1</v>
       </c>
       <c r="B184" s="25" t="s">
         <v>174</v>
@@ -41996,10 +42011,10 @@
       <c r="BC184" s="71"/>
       <c r="BD184" s="71"/>
     </row>
-    <row r="185" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:56" hidden="1">
       <c r="A185" s="24">
         <f>IF(B185="","",SUBTOTAL(3,$B$4:B185))</f>
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="B185" s="25" t="s">
         <v>174</v>
@@ -42114,10 +42129,10 @@
       <c r="BC185" s="71"/>
       <c r="BD185" s="71"/>
     </row>
-    <row r="186" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:56" hidden="1">
       <c r="A186" s="24">
         <f>IF(B186="","",SUBTOTAL(3,$B$4:B186))</f>
-        <v>183</v>
+        <v>1</v>
       </c>
       <c r="B186" s="25" t="s">
         <v>174</v>
@@ -42232,10 +42247,10 @@
       <c r="BC186" s="71"/>
       <c r="BD186" s="71"/>
     </row>
-    <row r="187" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:56" hidden="1">
       <c r="A187" s="24">
         <f>IF(B187="","",SUBTOTAL(3,$B$4:B187))</f>
-        <v>184</v>
+        <v>1</v>
       </c>
       <c r="B187" s="25" t="s">
         <v>174</v>
@@ -42350,10 +42365,10 @@
       <c r="BC187" s="71"/>
       <c r="BD187" s="71"/>
     </row>
-    <row r="188" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:56" hidden="1">
       <c r="A188" s="24">
         <f>IF(B188="","",SUBTOTAL(3,$B$4:B188))</f>
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>174</v>
@@ -42468,10 +42483,10 @@
       <c r="BC188" s="71"/>
       <c r="BD188" s="71"/>
     </row>
-    <row r="189" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:56" hidden="1">
       <c r="A189" s="24">
         <f>IF(B189="","",SUBTOTAL(3,$B$4:B189))</f>
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="B189" s="25" t="s">
         <v>174</v>
@@ -42586,7 +42601,7 @@
       <c r="BC189" s="71"/>
       <c r="BD189" s="71"/>
     </row>
-    <row r="190" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:56" hidden="1">
       <c r="A190" s="24" t="str">
         <f>IF(B190="","",SUBTOTAL(3,$B$4:B190))</f>
         <v/>
@@ -42674,7 +42689,7 @@
       <c r="BC190" s="71"/>
       <c r="BD190" s="71"/>
     </row>
-    <row r="191" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:56" hidden="1">
       <c r="A191" s="24" t="str">
         <f>IF(B191="","",SUBTOTAL(3,$B$4:B191))</f>
         <v/>
@@ -42762,7 +42777,7 @@
       <c r="BC191" s="71"/>
       <c r="BD191" s="71"/>
     </row>
-    <row r="192" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:56" hidden="1">
       <c r="A192" s="24" t="str">
         <f>IF(B192="","",SUBTOTAL(3,$B$4:B192))</f>
         <v/>
@@ -42850,7 +42865,7 @@
       <c r="BC192" s="71"/>
       <c r="BD192" s="71"/>
     </row>
-    <row r="193" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:56" hidden="1">
       <c r="A193" s="24" t="str">
         <f>IF(B193="","",SUBTOTAL(3,$B$4:B193))</f>
         <v/>
@@ -42938,7 +42953,7 @@
       <c r="BC193" s="71"/>
       <c r="BD193" s="71"/>
     </row>
-    <row r="194" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:56" hidden="1">
       <c r="A194" s="24" t="str">
         <f>IF(B194="","",SUBTOTAL(3,$B$4:B194))</f>
         <v/>
@@ -43026,7 +43041,7 @@
       <c r="BC194" s="71"/>
       <c r="BD194" s="71"/>
     </row>
-    <row r="195" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:56" hidden="1">
       <c r="A195" s="24" t="str">
         <f>IF(B195="","",SUBTOTAL(3,$B$4:B195))</f>
         <v/>
@@ -43114,7 +43129,7 @@
       <c r="BC195" s="71"/>
       <c r="BD195" s="71"/>
     </row>
-    <row r="196" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:56" hidden="1">
       <c r="A196" s="24" t="str">
         <f>IF(B196="","",SUBTOTAL(3,$B$4:B196))</f>
         <v/>
@@ -43202,7 +43217,7 @@
       <c r="BC196" s="71"/>
       <c r="BD196" s="71"/>
     </row>
-    <row r="197" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:56" hidden="1">
       <c r="A197" s="24" t="str">
         <f>IF(B197="","",SUBTOTAL(3,$B$4:B197))</f>
         <v/>
@@ -43290,7 +43305,7 @@
       <c r="BC197" s="71"/>
       <c r="BD197" s="71"/>
     </row>
-    <row r="198" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:56" hidden="1">
       <c r="A198" s="24" t="str">
         <f>IF(B198="","",SUBTOTAL(3,$B$4:B198))</f>
         <v/>
@@ -43378,7 +43393,7 @@
       <c r="BC198" s="71"/>
       <c r="BD198" s="71"/>
     </row>
-    <row r="199" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:56" hidden="1">
       <c r="A199" s="24" t="str">
         <f>IF(B199="","",SUBTOTAL(3,$B$4:B199))</f>
         <v/>
@@ -43466,7 +43481,7 @@
       <c r="BC199" s="71"/>
       <c r="BD199" s="71"/>
     </row>
-    <row r="200" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:56" hidden="1">
       <c r="A200" s="24" t="str">
         <f>IF(B200="","",SUBTOTAL(3,$B$4:B200))</f>
         <v/>
@@ -43554,7 +43569,7 @@
       <c r="BC200" s="71"/>
       <c r="BD200" s="71"/>
     </row>
-    <row r="201" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:56" hidden="1">
       <c r="A201" s="24" t="str">
         <f>IF(B201="","",SUBTOTAL(3,$B$4:B201))</f>
         <v/>
@@ -43642,7 +43657,7 @@
       <c r="BC201" s="71"/>
       <c r="BD201" s="71"/>
     </row>
-    <row r="202" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:56" hidden="1">
       <c r="A202" s="24" t="str">
         <f>IF(B202="","",SUBTOTAL(3,$B$4:B202))</f>
         <v/>
@@ -43730,7 +43745,7 @@
       <c r="BC202" s="71"/>
       <c r="BD202" s="71"/>
     </row>
-    <row r="203" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:56" hidden="1">
       <c r="A203" s="24" t="str">
         <f>IF(B203="","",SUBTOTAL(3,$B$4:B203))</f>
         <v/>
@@ -43818,7 +43833,7 @@
       <c r="BC203" s="71"/>
       <c r="BD203" s="71"/>
     </row>
-    <row r="204" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:56" hidden="1">
       <c r="A204" s="24" t="str">
         <f>IF(B204="","",SUBTOTAL(3,$B$4:B204))</f>
         <v/>
@@ -43906,7 +43921,7 @@
       <c r="BC204" s="71"/>
       <c r="BD204" s="71"/>
     </row>
-    <row r="205" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:56" hidden="1">
       <c r="A205" s="24" t="str">
         <f>IF(B205="","",SUBTOTAL(3,$B$4:B205))</f>
         <v/>
@@ -43994,7 +44009,7 @@
       <c r="BC205" s="71"/>
       <c r="BD205" s="71"/>
     </row>
-    <row r="206" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:56" hidden="1">
       <c r="A206" s="24" t="str">
         <f>IF(B206="","",SUBTOTAL(3,$B$4:B206))</f>
         <v/>
@@ -44082,7 +44097,7 @@
       <c r="BC206" s="71"/>
       <c r="BD206" s="71"/>
     </row>
-    <row r="207" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:56" hidden="1">
       <c r="A207" s="24" t="str">
         <f>IF(B207="","",SUBTOTAL(3,$B$4:B207))</f>
         <v/>
@@ -44170,7 +44185,7 @@
       <c r="BC207" s="71"/>
       <c r="BD207" s="71"/>
     </row>
-    <row r="208" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:56" hidden="1">
       <c r="A208" s="24" t="str">
         <f>IF(B208="","",SUBTOTAL(3,$B$4:B208))</f>
         <v/>
@@ -44258,7 +44273,7 @@
       <c r="BC208" s="71"/>
       <c r="BD208" s="71"/>
     </row>
-    <row r="209" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:56" hidden="1">
       <c r="A209" s="24" t="str">
         <f>IF(B209="","",SUBTOTAL(3,$B$4:B209))</f>
         <v/>
@@ -44346,7 +44361,7 @@
       <c r="BC209" s="71"/>
       <c r="BD209" s="71"/>
     </row>
-    <row r="210" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:56" hidden="1">
       <c r="A210" s="24" t="str">
         <f>IF(B210="","",SUBTOTAL(3,$B$4:B210))</f>
         <v/>
@@ -44434,7 +44449,7 @@
       <c r="BC210" s="71"/>
       <c r="BD210" s="71"/>
     </row>
-    <row r="211" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:56" hidden="1">
       <c r="A211" s="24" t="str">
         <f>IF(B211="","",SUBTOTAL(3,$B$4:B211))</f>
         <v/>
@@ -44522,7 +44537,7 @@
       <c r="BC211" s="71"/>
       <c r="BD211" s="71"/>
     </row>
-    <row r="212" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:56" hidden="1">
       <c r="A212" s="24" t="str">
         <f>IF(B212="","",SUBTOTAL(3,$B$4:B212))</f>
         <v/>
@@ -44610,7 +44625,7 @@
       <c r="BC212" s="71"/>
       <c r="BD212" s="71"/>
     </row>
-    <row r="213" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:56" hidden="1">
       <c r="A213" s="24" t="str">
         <f>IF(B213="","",SUBTOTAL(3,$B$4:B213))</f>
         <v/>
@@ -44698,7 +44713,7 @@
       <c r="BC213" s="71"/>
       <c r="BD213" s="71"/>
     </row>
-    <row r="214" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:56" hidden="1">
       <c r="A214" s="24" t="str">
         <f>IF(B214="","",SUBTOTAL(3,$B$4:B214))</f>
         <v/>
@@ -44786,7 +44801,7 @@
       <c r="BC214" s="71"/>
       <c r="BD214" s="71"/>
     </row>
-    <row r="215" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:56" hidden="1">
       <c r="A215" s="24" t="str">
         <f>IF(B215="","",SUBTOTAL(3,$B$4:B215))</f>
         <v/>
@@ -44874,7 +44889,7 @@
       <c r="BC215" s="71"/>
       <c r="BD215" s="71"/>
     </row>
-    <row r="216" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:56" hidden="1">
       <c r="A216" s="24" t="str">
         <f>IF(B216="","",SUBTOTAL(3,$B$4:B216))</f>
         <v/>
@@ -44962,7 +44977,7 @@
       <c r="BC216" s="71"/>
       <c r="BD216" s="71"/>
     </row>
-    <row r="217" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:56" hidden="1">
       <c r="A217" s="24" t="str">
         <f>IF(B217="","",SUBTOTAL(3,$B$4:B217))</f>
         <v/>
@@ -45050,7 +45065,7 @@
       <c r="BC217" s="71"/>
       <c r="BD217" s="71"/>
     </row>
-    <row r="218" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:56" hidden="1">
       <c r="A218" s="24" t="str">
         <f>IF(B218="","",SUBTOTAL(3,$B$4:B218))</f>
         <v/>
@@ -45138,7 +45153,7 @@
       <c r="BC218" s="71"/>
       <c r="BD218" s="71"/>
     </row>
-    <row r="219" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:56" hidden="1">
       <c r="A219" s="24" t="str">
         <f>IF(B219="","",SUBTOTAL(3,$B$4:B219))</f>
         <v/>
@@ -45226,7 +45241,7 @@
       <c r="BC219" s="71"/>
       <c r="BD219" s="71"/>
     </row>
-    <row r="220" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:56" hidden="1">
       <c r="A220" s="24" t="str">
         <f>IF(B220="","",SUBTOTAL(3,$B$4:B220))</f>
         <v/>
@@ -45314,7 +45329,7 @@
       <c r="BC220" s="71"/>
       <c r="BD220" s="71"/>
     </row>
-    <row r="221" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:56" hidden="1">
       <c r="A221" s="24" t="str">
         <f>IF(B221="","",SUBTOTAL(3,$B$4:B221))</f>
         <v/>
@@ -45402,7 +45417,7 @@
       <c r="BC221" s="71"/>
       <c r="BD221" s="71"/>
     </row>
-    <row r="222" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:56" hidden="1">
       <c r="A222" s="24" t="str">
         <f>IF(B222="","",SUBTOTAL(3,$B$4:B222))</f>
         <v/>
@@ -45490,7 +45505,7 @@
       <c r="BC222" s="71"/>
       <c r="BD222" s="71"/>
     </row>
-    <row r="223" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:56" hidden="1">
       <c r="A223" s="24" t="str">
         <f>IF(B223="","",SUBTOTAL(3,$B$4:B223))</f>
         <v/>
@@ -45578,7 +45593,7 @@
       <c r="BC223" s="71"/>
       <c r="BD223" s="71"/>
     </row>
-    <row r="224" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:56" hidden="1">
       <c r="A224" s="24" t="str">
         <f>IF(B224="","",SUBTOTAL(3,$B$4:B224))</f>
         <v/>
@@ -45666,7 +45681,7 @@
       <c r="BC224" s="71"/>
       <c r="BD224" s="71"/>
     </row>
-    <row r="225" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:56" hidden="1">
       <c r="A225" s="24" t="str">
         <f>IF(B225="","",SUBTOTAL(3,$B$4:B225))</f>
         <v/>
@@ -45754,7 +45769,7 @@
       <c r="BC225" s="71"/>
       <c r="BD225" s="71"/>
     </row>
-    <row r="226" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:56" hidden="1">
       <c r="A226" s="24" t="str">
         <f>IF(B226="","",SUBTOTAL(3,$B$4:B226))</f>
         <v/>
@@ -45842,7 +45857,7 @@
       <c r="BC226" s="71"/>
       <c r="BD226" s="71"/>
     </row>
-    <row r="227" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:56" hidden="1">
       <c r="A227" s="24" t="str">
         <f>IF(B227="","",SUBTOTAL(3,$B$4:B227))</f>
         <v/>
@@ -45930,7 +45945,7 @@
       <c r="BC227" s="71"/>
       <c r="BD227" s="71"/>
     </row>
-    <row r="228" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:56" hidden="1">
       <c r="A228" s="24" t="str">
         <f>IF(B228="","",SUBTOTAL(3,$B$4:B228))</f>
         <v/>
@@ -46018,7 +46033,7 @@
       <c r="BC228" s="71"/>
       <c r="BD228" s="71"/>
     </row>
-    <row r="229" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:56" hidden="1">
       <c r="A229" s="24" t="str">
         <f>IF(B229="","",SUBTOTAL(3,$B$4:B229))</f>
         <v/>
@@ -46106,7 +46121,7 @@
       <c r="BC229" s="71"/>
       <c r="BD229" s="71"/>
     </row>
-    <row r="230" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:56" hidden="1">
       <c r="A230" s="24" t="str">
         <f>IF(B230="","",SUBTOTAL(3,$B$4:B230))</f>
         <v/>
@@ -46194,7 +46209,7 @@
       <c r="BC230" s="71"/>
       <c r="BD230" s="71"/>
     </row>
-    <row r="231" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:56" hidden="1">
       <c r="A231" s="24" t="str">
         <f>IF(B231="","",SUBTOTAL(3,$B$4:B231))</f>
         <v/>
@@ -46282,7 +46297,7 @@
       <c r="BC231" s="71"/>
       <c r="BD231" s="71"/>
     </row>
-    <row r="232" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:56" hidden="1">
       <c r="A232" s="24" t="str">
         <f>IF(B232="","",SUBTOTAL(3,$B$4:B232))</f>
         <v/>
@@ -46370,7 +46385,7 @@
       <c r="BC232" s="71"/>
       <c r="BD232" s="71"/>
     </row>
-    <row r="233" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:56" hidden="1">
       <c r="A233" s="24" t="str">
         <f>IF(B233="","",SUBTOTAL(3,$B$4:B233))</f>
         <v/>
@@ -46458,7 +46473,7 @@
       <c r="BC233" s="71"/>
       <c r="BD233" s="71"/>
     </row>
-    <row r="234" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:56" hidden="1">
       <c r="A234" s="24" t="str">
         <f>IF(B234="","",SUBTOTAL(3,$B$4:B234))</f>
         <v/>
@@ -46546,7 +46561,7 @@
       <c r="BC234" s="71"/>
       <c r="BD234" s="71"/>
     </row>
-    <row r="235" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:56" hidden="1">
       <c r="A235" s="24" t="str">
         <f>IF(B235="","",SUBTOTAL(3,$B$4:B235))</f>
         <v/>
@@ -46634,7 +46649,7 @@
       <c r="BC235" s="71"/>
       <c r="BD235" s="71"/>
     </row>
-    <row r="236" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:56" hidden="1">
       <c r="A236" s="24" t="str">
         <f>IF(B236="","",SUBTOTAL(3,$B$4:B236))</f>
         <v/>
@@ -46722,7 +46737,7 @@
       <c r="BC236" s="71"/>
       <c r="BD236" s="71"/>
     </row>
-    <row r="237" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:56" hidden="1">
       <c r="A237" s="24" t="str">
         <f>IF(B237="","",SUBTOTAL(3,$B$4:B237))</f>
         <v/>
@@ -46810,7 +46825,7 @@
       <c r="BC237" s="71"/>
       <c r="BD237" s="71"/>
     </row>
-    <row r="238" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:56" hidden="1">
       <c r="A238" s="24" t="str">
         <f>IF(B238="","",SUBTOTAL(3,$B$4:B238))</f>
         <v/>
@@ -46898,7 +46913,7 @@
       <c r="BC238" s="71"/>
       <c r="BD238" s="71"/>
     </row>
-    <row r="239" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:56" hidden="1">
       <c r="A239" s="24" t="str">
         <f>IF(B239="","",SUBTOTAL(3,$B$4:B239))</f>
         <v/>
@@ -46986,7 +47001,7 @@
       <c r="BC239" s="71"/>
       <c r="BD239" s="71"/>
     </row>
-    <row r="240" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:56" hidden="1">
       <c r="A240" s="24" t="str">
         <f>IF(B240="","",SUBTOTAL(3,$B$4:B240))</f>
         <v/>
@@ -47074,7 +47089,7 @@
       <c r="BC240" s="71"/>
       <c r="BD240" s="71"/>
     </row>
-    <row r="241" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:56" hidden="1">
       <c r="A241" s="24" t="str">
         <f>IF(B241="","",SUBTOTAL(3,$B$4:B241))</f>
         <v/>
@@ -47162,7 +47177,7 @@
       <c r="BC241" s="71"/>
       <c r="BD241" s="71"/>
     </row>
-    <row r="242" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:56" hidden="1">
       <c r="A242" s="24" t="str">
         <f>IF(B242="","",SUBTOTAL(3,$B$4:B242))</f>
         <v/>
@@ -47250,7 +47265,7 @@
       <c r="BC242" s="71"/>
       <c r="BD242" s="71"/>
     </row>
-    <row r="243" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:56" hidden="1">
       <c r="A243" s="24" t="str">
         <f>IF(B243="","",SUBTOTAL(3,$B$4:B243))</f>
         <v/>
@@ -47338,7 +47353,7 @@
       <c r="BC243" s="71"/>
       <c r="BD243" s="71"/>
     </row>
-    <row r="244" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:56" hidden="1">
       <c r="A244" s="24" t="str">
         <f>IF(B244="","",SUBTOTAL(3,$B$4:B244))</f>
         <v/>
@@ -47426,7 +47441,7 @@
       <c r="BC244" s="71"/>
       <c r="BD244" s="71"/>
     </row>
-    <row r="245" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:56" hidden="1">
       <c r="A245" s="24" t="str">
         <f>IF(B245="","",SUBTOTAL(3,$B$4:B245))</f>
         <v/>
@@ -47514,7 +47529,7 @@
       <c r="BC245" s="71"/>
       <c r="BD245" s="71"/>
     </row>
-    <row r="246" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:56" hidden="1">
       <c r="A246" s="24" t="str">
         <f>IF(B246="","",SUBTOTAL(3,$B$4:B246))</f>
         <v/>
@@ -47602,7 +47617,7 @@
       <c r="BC246" s="71"/>
       <c r="BD246" s="71"/>
     </row>
-    <row r="247" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:56" hidden="1">
       <c r="A247" s="24" t="str">
         <f>IF(B247="","",SUBTOTAL(3,$B$4:B247))</f>
         <v/>
@@ -47690,7 +47705,7 @@
       <c r="BC247" s="71"/>
       <c r="BD247" s="71"/>
     </row>
-    <row r="248" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:56" hidden="1">
       <c r="A248" s="24" t="str">
         <f>IF(B248="","",SUBTOTAL(3,$B$4:B248))</f>
         <v/>
@@ -47778,7 +47793,7 @@
       <c r="BC248" s="71"/>
       <c r="BD248" s="71"/>
     </row>
-    <row r="249" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:56" hidden="1">
       <c r="A249" s="24" t="str">
         <f>IF(B249="","",SUBTOTAL(3,$B$4:B249))</f>
         <v/>
@@ -47866,7 +47881,7 @@
       <c r="BC249" s="71"/>
       <c r="BD249" s="71"/>
     </row>
-    <row r="250" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:56" hidden="1">
       <c r="A250" s="24" t="str">
         <f>IF(B250="","",SUBTOTAL(3,$B$4:B250))</f>
         <v/>
@@ -47954,7 +47969,7 @@
       <c r="BC250" s="71"/>
       <c r="BD250" s="71"/>
     </row>
-    <row r="251" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:56" hidden="1">
       <c r="A251" s="24" t="str">
         <f>IF(B251="","",SUBTOTAL(3,$B$4:B251))</f>
         <v/>
@@ -48042,7 +48057,7 @@
       <c r="BC251" s="71"/>
       <c r="BD251" s="71"/>
     </row>
-    <row r="252" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:56" hidden="1">
       <c r="A252" s="24" t="str">
         <f>IF(B252="","",SUBTOTAL(3,$B$4:B252))</f>
         <v/>
@@ -48130,7 +48145,7 @@
       <c r="BC252" s="71"/>
       <c r="BD252" s="71"/>
     </row>
-    <row r="253" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:56" hidden="1">
       <c r="A253" s="24" t="str">
         <f>IF(B253="","",SUBTOTAL(3,$B$4:B253))</f>
         <v/>
@@ -48218,7 +48233,7 @@
       <c r="BC253" s="71"/>
       <c r="BD253" s="71"/>
     </row>
-    <row r="254" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:56" hidden="1">
       <c r="A254" s="24" t="str">
         <f>IF(B254="","",SUBTOTAL(3,$B$4:B254))</f>
         <v/>
@@ -48306,7 +48321,7 @@
       <c r="BC254" s="71"/>
       <c r="BD254" s="71"/>
     </row>
-    <row r="255" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:56" hidden="1">
       <c r="A255" s="24" t="str">
         <f>IF(B255="","",SUBTOTAL(3,$B$4:B255))</f>
         <v/>
@@ -48394,7 +48409,7 @@
       <c r="BC255" s="71"/>
       <c r="BD255" s="71"/>
     </row>
-    <row r="256" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:56" hidden="1">
       <c r="A256" s="24" t="str">
         <f>IF(B256="","",SUBTOTAL(3,$B$4:B256))</f>
         <v/>
@@ -48482,7 +48497,7 @@
       <c r="BC256" s="71"/>
       <c r="BD256" s="71"/>
     </row>
-    <row r="257" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:56" hidden="1">
       <c r="A257" s="24" t="str">
         <f>IF(B257="","",SUBTOTAL(3,$B$4:B257))</f>
         <v/>
@@ -48570,7 +48585,7 @@
       <c r="BC257" s="71"/>
       <c r="BD257" s="71"/>
     </row>
-    <row r="258" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:56" hidden="1">
       <c r="A258" s="24" t="str">
         <f>IF(B258="","",SUBTOTAL(3,$B$4:B258))</f>
         <v/>
@@ -48658,7 +48673,7 @@
       <c r="BC258" s="71"/>
       <c r="BD258" s="71"/>
     </row>
-    <row r="259" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:56" hidden="1">
       <c r="A259" s="24" t="str">
         <f>IF(B259="","",SUBTOTAL(3,$B$4:B259))</f>
         <v/>
@@ -48746,7 +48761,7 @@
       <c r="BC259" s="71"/>
       <c r="BD259" s="71"/>
     </row>
-    <row r="260" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:56" hidden="1">
       <c r="A260" s="24" t="str">
         <f>IF(B260="","",SUBTOTAL(3,$B$4:B260))</f>
         <v/>
@@ -48834,7 +48849,7 @@
       <c r="BC260" s="71"/>
       <c r="BD260" s="71"/>
     </row>
-    <row r="261" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:56" hidden="1">
       <c r="A261" s="24" t="str">
         <f>IF(B261="","",SUBTOTAL(3,$B$4:B261))</f>
         <v/>
@@ -48922,7 +48937,7 @@
       <c r="BC261" s="71"/>
       <c r="BD261" s="71"/>
     </row>
-    <row r="262" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:56" hidden="1">
       <c r="A262" s="24" t="str">
         <f>IF(B262="","",SUBTOTAL(3,$B$4:B262))</f>
         <v/>
@@ -49010,7 +49025,7 @@
       <c r="BC262" s="71"/>
       <c r="BD262" s="71"/>
     </row>
-    <row r="263" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:56" hidden="1">
       <c r="A263" s="24" t="str">
         <f>IF(B263="","",SUBTOTAL(3,$B$4:B263))</f>
         <v/>
@@ -49098,7 +49113,7 @@
       <c r="BC263" s="71"/>
       <c r="BD263" s="71"/>
     </row>
-    <row r="264" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:56" hidden="1">
       <c r="A264" s="24" t="str">
         <f>IF(B264="","",SUBTOTAL(3,$B$4:B264))</f>
         <v/>
@@ -49186,7 +49201,7 @@
       <c r="BC264" s="71"/>
       <c r="BD264" s="71"/>
     </row>
-    <row r="265" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:56" hidden="1">
       <c r="A265" s="24" t="str">
         <f>IF(B265="","",SUBTOTAL(3,$B$4:B265))</f>
         <v/>
@@ -49274,7 +49289,7 @@
       <c r="BC265" s="71"/>
       <c r="BD265" s="71"/>
     </row>
-    <row r="266" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:56" hidden="1">
       <c r="A266" s="24" t="str">
         <f>IF(B266="","",SUBTOTAL(3,$B$4:B266))</f>
         <v/>
@@ -49362,7 +49377,7 @@
       <c r="BC266" s="71"/>
       <c r="BD266" s="71"/>
     </row>
-    <row r="267" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:56" hidden="1">
       <c r="A267" s="24" t="str">
         <f>IF(B267="","",SUBTOTAL(3,$B$4:B267))</f>
         <v/>
@@ -49450,7 +49465,7 @@
       <c r="BC267" s="71"/>
       <c r="BD267" s="71"/>
     </row>
-    <row r="268" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:56" hidden="1">
       <c r="A268" s="24" t="str">
         <f>IF(B268="","",SUBTOTAL(3,$B$4:B268))</f>
         <v/>
@@ -49538,7 +49553,7 @@
       <c r="BC268" s="71"/>
       <c r="BD268" s="71"/>
     </row>
-    <row r="269" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:56" hidden="1">
       <c r="A269" s="24" t="str">
         <f>IF(B269="","",SUBTOTAL(3,$B$4:B269))</f>
         <v/>
@@ -49626,7 +49641,7 @@
       <c r="BC269" s="71"/>
       <c r="BD269" s="71"/>
     </row>
-    <row r="270" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:56" hidden="1">
       <c r="A270" s="24" t="str">
         <f>IF(B270="","",SUBTOTAL(3,$B$4:B270))</f>
         <v/>
@@ -49714,7 +49729,7 @@
       <c r="BC270" s="71"/>
       <c r="BD270" s="71"/>
     </row>
-    <row r="271" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:56" hidden="1">
       <c r="A271" s="24" t="str">
         <f>IF(B271="","",SUBTOTAL(3,$B$4:B271))</f>
         <v/>
@@ -49802,7 +49817,7 @@
       <c r="BC271" s="71"/>
       <c r="BD271" s="71"/>
     </row>
-    <row r="272" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:56" hidden="1">
       <c r="A272" s="24" t="str">
         <f>IF(B272="","",SUBTOTAL(3,$B$4:B272))</f>
         <v/>
@@ -49890,7 +49905,7 @@
       <c r="BC272" s="71"/>
       <c r="BD272" s="71"/>
     </row>
-    <row r="273" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:56" hidden="1">
       <c r="A273" s="24" t="str">
         <f>IF(B273="","",SUBTOTAL(3,$B$4:B273))</f>
         <v/>
@@ -49978,7 +49993,7 @@
       <c r="BC273" s="71"/>
       <c r="BD273" s="71"/>
     </row>
-    <row r="274" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:56" hidden="1">
       <c r="A274" s="24" t="str">
         <f>IF(B274="","",SUBTOTAL(3,$B$4:B274))</f>
         <v/>
@@ -50066,7 +50081,7 @@
       <c r="BC274" s="71"/>
       <c r="BD274" s="71"/>
     </row>
-    <row r="275" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:56" hidden="1">
       <c r="A275" s="24" t="str">
         <f>IF(B275="","",SUBTOTAL(3,$B$4:B275))</f>
         <v/>
@@ -50154,7 +50169,7 @@
       <c r="BC275" s="71"/>
       <c r="BD275" s="71"/>
     </row>
-    <row r="276" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:56" hidden="1">
       <c r="A276" s="24" t="str">
         <f>IF(B276="","",SUBTOTAL(3,$B$4:B276))</f>
         <v/>
@@ -50242,7 +50257,7 @@
       <c r="BC276" s="71"/>
       <c r="BD276" s="71"/>
     </row>
-    <row r="277" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:56" hidden="1">
       <c r="A277" s="24" t="str">
         <f>IF(B277="","",SUBTOTAL(3,$B$4:B277))</f>
         <v/>
@@ -50330,7 +50345,7 @@
       <c r="BC277" s="71"/>
       <c r="BD277" s="71"/>
     </row>
-    <row r="278" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:56" hidden="1">
       <c r="A278" s="24" t="str">
         <f>IF(B278="","",SUBTOTAL(3,$B$4:B278))</f>
         <v/>
@@ -50418,7 +50433,7 @@
       <c r="BC278" s="71"/>
       <c r="BD278" s="71"/>
     </row>
-    <row r="279" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:56" hidden="1">
       <c r="A279" s="24" t="str">
         <f>IF(B279="","",SUBTOTAL(3,$B$4:B279))</f>
         <v/>
@@ -50506,7 +50521,7 @@
       <c r="BC279" s="71"/>
       <c r="BD279" s="71"/>
     </row>
-    <row r="280" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:56" hidden="1">
       <c r="A280" s="24" t="str">
         <f>IF(B280="","",SUBTOTAL(3,$B$4:B280))</f>
         <v/>
@@ -50594,7 +50609,7 @@
       <c r="BC280" s="71"/>
       <c r="BD280" s="71"/>
     </row>
-    <row r="281" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:56" hidden="1">
       <c r="A281" s="24" t="str">
         <f>IF(B281="","",SUBTOTAL(3,$B$4:B281))</f>
         <v/>
@@ -50682,7 +50697,7 @@
       <c r="BC281" s="71"/>
       <c r="BD281" s="71"/>
     </row>
-    <row r="282" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:56" hidden="1">
       <c r="A282" s="24" t="str">
         <f>IF(B282="","",SUBTOTAL(3,$B$4:B282))</f>
         <v/>
@@ -50770,7 +50785,7 @@
       <c r="BC282" s="71"/>
       <c r="BD282" s="71"/>
     </row>
-    <row r="283" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:56" hidden="1">
       <c r="A283" s="24" t="str">
         <f>IF(B283="","",SUBTOTAL(3,$B$4:B283))</f>
         <v/>
@@ -50858,7 +50873,7 @@
       <c r="BC283" s="71"/>
       <c r="BD283" s="71"/>
     </row>
-    <row r="284" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:56" hidden="1">
       <c r="A284" s="24" t="str">
         <f>IF(B284="","",SUBTOTAL(3,$B$4:B284))</f>
         <v/>
@@ -50946,7 +50961,7 @@
       <c r="BC284" s="71"/>
       <c r="BD284" s="71"/>
     </row>
-    <row r="285" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:56" hidden="1">
       <c r="A285" s="24" t="str">
         <f>IF(B285="","",SUBTOTAL(3,$B$4:B285))</f>
         <v/>
@@ -51034,7 +51049,7 @@
       <c r="BC285" s="71"/>
       <c r="BD285" s="71"/>
     </row>
-    <row r="286" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:56" hidden="1">
       <c r="A286" s="24" t="str">
         <f>IF(B286="","",SUBTOTAL(3,$B$4:B286))</f>
         <v/>
@@ -51122,7 +51137,7 @@
       <c r="BC286" s="71"/>
       <c r="BD286" s="71"/>
     </row>
-    <row r="287" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:56" hidden="1">
       <c r="A287" s="24" t="str">
         <f>IF(B287="","",SUBTOTAL(3,$B$4:B287))</f>
         <v/>
@@ -51210,7 +51225,7 @@
       <c r="BC287" s="71"/>
       <c r="BD287" s="71"/>
     </row>
-    <row r="288" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:56" hidden="1">
       <c r="A288" s="24" t="str">
         <f>IF(B288="","",SUBTOTAL(3,$B$4:B288))</f>
         <v/>
@@ -51298,7 +51313,7 @@
       <c r="BC288" s="71"/>
       <c r="BD288" s="71"/>
     </row>
-    <row r="289" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:56" hidden="1">
       <c r="A289" s="24" t="str">
         <f>IF(B289="","",SUBTOTAL(3,$B$4:B289))</f>
         <v/>
@@ -51386,7 +51401,7 @@
       <c r="BC289" s="71"/>
       <c r="BD289" s="71"/>
     </row>
-    <row r="290" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:56" hidden="1">
       <c r="A290" s="24" t="str">
         <f>IF(B290="","",SUBTOTAL(3,$B$4:B290))</f>
         <v/>
@@ -51474,7 +51489,7 @@
       <c r="BC290" s="71"/>
       <c r="BD290" s="71"/>
     </row>
-    <row r="291" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:56" hidden="1">
       <c r="A291" s="24" t="str">
         <f>IF(B291="","",SUBTOTAL(3,$B$4:B291))</f>
         <v/>
@@ -51562,7 +51577,7 @@
       <c r="BC291" s="71"/>
       <c r="BD291" s="71"/>
     </row>
-    <row r="292" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:56" hidden="1">
       <c r="A292" s="24" t="str">
         <f>IF(B292="","",SUBTOTAL(3,$B$4:B292))</f>
         <v/>
@@ -51650,7 +51665,7 @@
       <c r="BC292" s="71"/>
       <c r="BD292" s="71"/>
     </row>
-    <row r="293" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:56" hidden="1">
       <c r="A293" s="24" t="str">
         <f>IF(B293="","",SUBTOTAL(3,$B$4:B293))</f>
         <v/>
@@ -51738,7 +51753,7 @@
       <c r="BC293" s="71"/>
       <c r="BD293" s="71"/>
     </row>
-    <row r="294" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:56" hidden="1">
       <c r="A294" s="24" t="str">
         <f>IF(B294="","",SUBTOTAL(3,$B$4:B294))</f>
         <v/>
@@ -51826,7 +51841,7 @@
       <c r="BC294" s="71"/>
       <c r="BD294" s="71"/>
     </row>
-    <row r="295" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:56" hidden="1">
       <c r="A295" s="24" t="str">
         <f>IF(B295="","",SUBTOTAL(3,$B$4:B295))</f>
         <v/>
@@ -51914,7 +51929,7 @@
       <c r="BC295" s="71"/>
       <c r="BD295" s="71"/>
     </row>
-    <row r="296" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:56" hidden="1">
       <c r="A296" s="24" t="str">
         <f>IF(B296="","",SUBTOTAL(3,$B$4:B296))</f>
         <v/>
@@ -52002,7 +52017,7 @@
       <c r="BC296" s="71"/>
       <c r="BD296" s="71"/>
     </row>
-    <row r="297" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:56" hidden="1">
       <c r="A297" s="24" t="str">
         <f>IF(B297="","",SUBTOTAL(3,$B$4:B297))</f>
         <v/>
@@ -52090,7 +52105,7 @@
       <c r="BC297" s="71"/>
       <c r="BD297" s="71"/>
     </row>
-    <row r="298" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:56" hidden="1">
       <c r="A298" s="24" t="str">
         <f>IF(B298="","",SUBTOTAL(3,$B$4:B298))</f>
         <v/>
@@ -52178,7 +52193,7 @@
       <c r="BC298" s="71"/>
       <c r="BD298" s="71"/>
     </row>
-    <row r="299" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:56" hidden="1">
       <c r="A299" s="24" t="str">
         <f>IF(B299="","",SUBTOTAL(3,$B$4:B299))</f>
         <v/>
@@ -52266,7 +52281,7 @@
       <c r="BC299" s="71"/>
       <c r="BD299" s="71"/>
     </row>
-    <row r="300" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:56" hidden="1">
       <c r="A300" s="24" t="str">
         <f>IF(B300="","",SUBTOTAL(3,$B$4:B300))</f>
         <v/>
@@ -52354,7 +52369,7 @@
       <c r="BC300" s="71"/>
       <c r="BD300" s="71"/>
     </row>
-    <row r="301" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:56" hidden="1">
       <c r="A301" s="24" t="str">
         <f>IF(B301="","",SUBTOTAL(3,$B$4:B301))</f>
         <v/>
@@ -52442,7 +52457,7 @@
       <c r="BC301" s="71"/>
       <c r="BD301" s="71"/>
     </row>
-    <row r="302" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:56" hidden="1">
       <c r="A302" s="24" t="str">
         <f>IF(B302="","",SUBTOTAL(3,$B$4:B302))</f>
         <v/>
@@ -52530,7 +52545,7 @@
       <c r="BC302" s="71"/>
       <c r="BD302" s="71"/>
     </row>
-    <row r="303" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:56" hidden="1">
       <c r="A303" s="24" t="str">
         <f>IF(B303="","",SUBTOTAL(3,$B$4:B303))</f>
         <v/>
@@ -52618,7 +52633,7 @@
       <c r="BC303" s="71"/>
       <c r="BD303" s="71"/>
     </row>
-    <row r="304" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:56" hidden="1">
       <c r="A304" s="24" t="str">
         <f>IF(B304="","",SUBTOTAL(3,$B$4:B304))</f>
         <v/>
@@ -52706,7 +52721,7 @@
       <c r="BC304" s="71"/>
       <c r="BD304" s="71"/>
     </row>
-    <row r="305" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:56" hidden="1">
       <c r="A305" s="24" t="str">
         <f>IF(B305="","",SUBTOTAL(3,$B$4:B305))</f>
         <v/>
@@ -52794,7 +52809,7 @@
       <c r="BC305" s="71"/>
       <c r="BD305" s="71"/>
     </row>
-    <row r="306" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:56" hidden="1">
       <c r="A306" s="24" t="str">
         <f>IF(B306="","",SUBTOTAL(3,$B$4:B306))</f>
         <v/>
@@ -52882,7 +52897,7 @@
       <c r="BC306" s="71"/>
       <c r="BD306" s="71"/>
     </row>
-    <row r="307" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:56" hidden="1">
       <c r="A307" s="24" t="str">
         <f>IF(B307="","",SUBTOTAL(3,$B$4:B307))</f>
         <v/>
@@ -52970,7 +52985,7 @@
       <c r="BC307" s="71"/>
       <c r="BD307" s="71"/>
     </row>
-    <row r="308" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:56" hidden="1">
       <c r="A308" s="24" t="str">
         <f>IF(B308="","",SUBTOTAL(3,$B$4:B308))</f>
         <v/>
@@ -53058,7 +53073,7 @@
       <c r="BC308" s="71"/>
       <c r="BD308" s="71"/>
     </row>
-    <row r="309" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:56" hidden="1">
       <c r="A309" s="24" t="str">
         <f>IF(B309="","",SUBTOTAL(3,$B$4:B309))</f>
         <v/>
@@ -53146,7 +53161,7 @@
       <c r="BC309" s="71"/>
       <c r="BD309" s="71"/>
     </row>
-    <row r="310" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:56" hidden="1">
       <c r="A310" s="24" t="str">
         <f>IF(B310="","",SUBTOTAL(3,$B$4:B310))</f>
         <v/>
@@ -53234,7 +53249,7 @@
       <c r="BC310" s="71"/>
       <c r="BD310" s="71"/>
     </row>
-    <row r="311" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:56" hidden="1">
       <c r="A311" s="24" t="str">
         <f>IF(B311="","",SUBTOTAL(3,$B$4:B311))</f>
         <v/>
@@ -53322,7 +53337,7 @@
       <c r="BC311" s="71"/>
       <c r="BD311" s="71"/>
     </row>
-    <row r="312" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:56" hidden="1">
       <c r="A312" s="24" t="str">
         <f>IF(B312="","",SUBTOTAL(3,$B$4:B312))</f>
         <v/>
@@ -53410,7 +53425,7 @@
       <c r="BC312" s="71"/>
       <c r="BD312" s="71"/>
     </row>
-    <row r="313" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:56" hidden="1">
       <c r="A313" s="24" t="str">
         <f>IF(B313="","",SUBTOTAL(3,$B$4:B313))</f>
         <v/>
@@ -53498,7 +53513,7 @@
       <c r="BC313" s="71"/>
       <c r="BD313" s="71"/>
     </row>
-    <row r="314" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:56" hidden="1">
       <c r="A314" s="24" t="str">
         <f>IF(B314="","",SUBTOTAL(3,$B$4:B314))</f>
         <v/>
@@ -53586,7 +53601,7 @@
       <c r="BC314" s="71"/>
       <c r="BD314" s="71"/>
     </row>
-    <row r="315" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:56" hidden="1">
       <c r="A315" s="24" t="str">
         <f>IF(B315="","",SUBTOTAL(3,$B$4:B315))</f>
         <v/>
@@ -53674,7 +53689,7 @@
       <c r="BC315" s="71"/>
       <c r="BD315" s="71"/>
     </row>
-    <row r="316" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:56" hidden="1">
       <c r="A316" s="24" t="str">
         <f>IF(B316="","",SUBTOTAL(3,$B$4:B316))</f>
         <v/>
@@ -53762,7 +53777,7 @@
       <c r="BC316" s="71"/>
       <c r="BD316" s="71"/>
     </row>
-    <row r="317" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:56" hidden="1">
       <c r="A317" s="24" t="str">
         <f>IF(B317="","",SUBTOTAL(3,$B$4:B317))</f>
         <v/>
@@ -53850,7 +53865,7 @@
       <c r="BC317" s="71"/>
       <c r="BD317" s="71"/>
     </row>
-    <row r="318" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:56" hidden="1">
       <c r="A318" s="24" t="str">
         <f>IF(B318="","",SUBTOTAL(3,$B$4:B318))</f>
         <v/>
@@ -53938,7 +53953,7 @@
       <c r="BC318" s="71"/>
       <c r="BD318" s="71"/>
     </row>
-    <row r="319" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:56" hidden="1">
       <c r="A319" s="24" t="str">
         <f>IF(B319="","",SUBTOTAL(3,$B$4:B319))</f>
         <v/>
@@ -54026,7 +54041,7 @@
       <c r="BC319" s="71"/>
       <c r="BD319" s="71"/>
     </row>
-    <row r="320" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:56" hidden="1">
       <c r="A320" s="24" t="str">
         <f>IF(B320="","",SUBTOTAL(3,$B$4:B320))</f>
         <v/>
@@ -54114,7 +54129,7 @@
       <c r="BC320" s="71"/>
       <c r="BD320" s="71"/>
     </row>
-    <row r="321" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:56" hidden="1">
       <c r="A321" s="24" t="str">
         <f>IF(B321="","",SUBTOTAL(3,$B$4:B321))</f>
         <v/>
@@ -54202,7 +54217,7 @@
       <c r="BC321" s="71"/>
       <c r="BD321" s="71"/>
     </row>
-    <row r="322" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:56" hidden="1">
       <c r="A322" s="24" t="str">
         <f>IF(B322="","",SUBTOTAL(3,$B$4:B322))</f>
         <v/>
@@ -54290,7 +54305,7 @@
       <c r="BC322" s="71"/>
       <c r="BD322" s="71"/>
     </row>
-    <row r="323" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:56" hidden="1">
       <c r="A323" s="24" t="str">
         <f>IF(B323="","",SUBTOTAL(3,$B$4:B323))</f>
         <v/>
@@ -54378,7 +54393,7 @@
       <c r="BC323" s="71"/>
       <c r="BD323" s="71"/>
     </row>
-    <row r="324" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:56" hidden="1">
       <c r="A324" s="24" t="str">
         <f>IF(B324="","",SUBTOTAL(3,$B$4:B324))</f>
         <v/>
@@ -54466,7 +54481,7 @@
       <c r="BC324" s="71"/>
       <c r="BD324" s="71"/>
     </row>
-    <row r="325" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:56" hidden="1">
       <c r="A325" s="24" t="str">
         <f>IF(B325="","",SUBTOTAL(3,$B$4:B325))</f>
         <v/>
@@ -54554,7 +54569,7 @@
       <c r="BC325" s="71"/>
       <c r="BD325" s="71"/>
     </row>
-    <row r="326" spans="1:56" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:56" ht="16.5" hidden="1" thickBot="1">
       <c r="A326" s="38" t="str">
         <f>IF(B326="","",SUBTOTAL(3,$B$4:B326))</f>
         <v/>
@@ -54642,9 +54657,17 @@
       <c r="BC326" s="71"/>
       <c r="BD326" s="71"/>
     </row>
-    <row r="327" spans="1:56" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:BD326" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}"/>
+  <autoFilter ref="A3:BD326" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
+    <filterColumn colId="44">
+      <filters>
+        <filter val="A320-M4130-006"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="49">
+      <colorFilter dxfId="26"/>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A4:AG326 AJ4:AL326">
     <cfRule type="expression" dxfId="15" priority="2">
       <formula>$AK4=$N4</formula>

--- a/03.QLDA/A320.xlsx
+++ b/03.QLDA/A320.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AMECC JSC\Amecc 2\00. Overall Report\03.QLDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88F7D31-6C71-4EB9-BEFB-823B3B4E9847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED36D6F-0C54-42A1-BE52-6E5898037896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB65E7D8-5C33-4F00-97F9-F6CAD846FF50}"/>
   </bookViews>
   <sheets>
     <sheet name="Progress" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId2"/>
+    <pivotCache cacheId="12" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -921,12 +921,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1273,7 +1273,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1361,28 +1361,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1403,19 +1403,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1437,13 +1437,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1471,56 +1471,56 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="26">
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
       <fill>
@@ -1565,42 +1565,34 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="33" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1621,7 +1613,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="Hiếu Nguyễn" refreshedDate="46298.349438194447" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="DELL" refreshedDate="46301.675595833331" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="323" xr:uid="{4067F58C-28E2-44CB-8FA2-A8EFFD878FFB}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A3:BA326" sheet="Progress"/>
   </cacheSource>
@@ -1686,10 +1678,10 @@
     <cacheField name="T'Qty" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="96"/>
     </cacheField>
-    <cacheField name="U.Weight" numFmtId="165">
+    <cacheField name="U.Weight" numFmtId="43">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="2.5000000000000001E-2" maxValue="6730.4139199999981"/>
     </cacheField>
-    <cacheField name="T.Weight" numFmtId="165">
+    <cacheField name="T.Weight" numFmtId="43">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.1" maxValue="6730.4139199999981"/>
     </cacheField>
     <cacheField name="Profile" numFmtId="0">
@@ -1734,10 +1726,10 @@
     <cacheField name="DATE CPCL" numFmtId="14">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
-    <cacheField name="Hoàn thiện" numFmtId="166">
+    <cacheField name="Hoàn thiện" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
-    <cacheField name="Còn lại" numFmtId="165">
+    <cacheField name="Còn lại" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6730.4139199999981"/>
     </cacheField>
     <cacheField name="Kế hoạch Tháng" numFmtId="0">
@@ -1746,7 +1738,7 @@
     <cacheField name="Nhận Phôi" numFmtId="9">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0.9" maxValue="0.9"/>
     </cacheField>
-    <cacheField name="Khối lượng" numFmtId="166">
+    <cacheField name="Khối lượng" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="5815.547999999998"/>
     </cacheField>
     <cacheField name="Ngày Gá" numFmtId="14">
@@ -1755,7 +1747,7 @@
     <cacheField name="SL Gá" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Gá" numFmtId="165">
+    <cacheField name="KL Gá" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày Hàn" numFmtId="14">
@@ -1764,7 +1756,7 @@
     <cacheField name="SL Hàn" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL Hàn" numFmtId="165">
+    <cacheField name="KL Hàn" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày TH" numFmtId="14">
@@ -1773,7 +1765,7 @@
     <cacheField name="SL TH" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL TH" numFmtId="165">
+    <cacheField name="KL TH" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Số AFI" numFmtId="0">
@@ -1785,7 +1777,7 @@
     <cacheField name="SL NT" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL NT" numFmtId="165">
+    <cacheField name="KL NT" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Ngày BG" numFmtId="14">
@@ -1794,7 +1786,7 @@
     <cacheField name="SL BG" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
-    <cacheField name="KL BG" numFmtId="165">
+    <cacheField name="KL BG" numFmtId="43">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="6461.7199999999975"/>
     </cacheField>
     <cacheField name="Đơn vị nhận" numFmtId="0">
@@ -9512,7 +9504,7 @@
     <n v="1"/>
     <n v="2070.6"/>
     <s v="PAC"/>
-    <s v="A290-003"/>
+    <s v="A320-003"/>
   </r>
   <r>
     <n v="1"/>
@@ -19583,7 +19575,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{85CD8DED-1024-4DD7-B7B9-B699E3BC5DA2}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="BF3:BH13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="53">
     <pivotField showAll="0"/>
@@ -19643,27 +19635,27 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="166" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="165" showAll="0"/>
+    <pivotField dataField="1" numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField numFmtId="165" showAll="0"/>
+    <pivotField numFmtId="43" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -19717,7 +19709,7 @@
   </colItems>
   <dataFields count="2">
     <dataField name="Sum of T.Weight" fld="15" baseField="1" baseItem="0"/>
-    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="165"/>
+    <dataField name="Sum of KL Gá" fld="37" baseField="0" baseItem="0" numFmtId="43"/>
   </dataFields>
   <formats count="10">
     <format dxfId="25">
@@ -20266,9 +20258,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
-  <sheetPr codeName="Sheet1" filterMode="1"/>
-  <dimension ref="A1:BH326"/>
-  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:BH327"/>
+  <sheetFormatPr defaultRowHeight="15.75" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -20318,7 +20310,7 @@
     <col min="60" max="60" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1">
+    <row r="1" spans="1:60" ht="25.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="str">
         <f>"DỰ ÁN:"&amp;B4</f>
         <v>DỰ ÁN:A320</v>
@@ -20389,7 +20381,7 @@
       <c r="BC1" s="48"/>
       <c r="BD1" s="48"/>
     </row>
-    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:60" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -20414,7 +20406,7 @@
       <c r="R2" s="5"/>
       <c r="S2" s="51">
         <f ca="1">IF(WEEKDAY(TODAY()-1)=1,TODAY()-2,TODAY()-1)</f>
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="T2" s="13" t="s">
         <v>40</v>
@@ -20439,29 +20431,29 @@
       <c r="AJ2" s="15"/>
       <c r="AK2" s="67">
         <f>SUBTOTAL(9,AK4:AK326)</f>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AL2" s="68">
         <f>SUBTOTAL(9,AL4:AL326)</f>
-        <v>2070.6</v>
+        <v>51008.607039999988</v>
       </c>
       <c r="AM2" s="15"/>
       <c r="AN2" s="67">
         <f>SUBTOTAL(9,AN4:AN326)</f>
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AO2" s="68">
         <f>SUBTOTAL(9,AO4:AO326)</f>
-        <v>2070.6</v>
+        <v>51008.607039999988</v>
       </c>
       <c r="AP2" s="15"/>
       <c r="AQ2" s="67">
         <f>SUBTOTAL(9,AQ4:AQ326)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR2" s="68">
         <f>SUBTOTAL(9,AR4:AR326)</f>
-        <v>0</v>
+        <v>15815.604799999997</v>
       </c>
       <c r="AS2" s="16" t="str">
         <f>SUBSTITUTE(A1,"DỰ ÁN:","")&amp;"-"</f>
@@ -20470,20 +20462,20 @@
       <c r="AT2" s="17"/>
       <c r="AU2" s="67">
         <f>SUBTOTAL(9,AU4:AU326)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AV2" s="68">
         <f>SUBTOTAL(9,AV4:AV326)</f>
-        <v>2070.6</v>
+        <v>24732.604800000001</v>
       </c>
       <c r="AW2" s="16"/>
       <c r="AX2" s="67">
         <f>SUBTOTAL(9,AX4:AX326)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AY2" s="67">
         <f>SUBTOTAL(9,AY4:AY326)</f>
-        <v>2070.6</v>
+        <v>22652.604800000001</v>
       </c>
       <c r="AZ2" s="17"/>
       <c r="BA2" s="18" t="str">
@@ -20494,7 +20486,7 @@
       <c r="BC2" s="48"/>
       <c r="BD2" s="48"/>
     </row>
-    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1">
+    <row r="3" spans="1:60" ht="27" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>7</v>
       </c>
@@ -20673,10 +20665,10 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:60" hidden="1">
+    <row r="4" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A4" s="24">
         <f>IF(B4="","",SUBTOTAL(3,$B$4:B4))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>174</v>
@@ -20796,10 +20788,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="5" spans="1:60" hidden="1">
+    <row r="5" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
         <f>IF(B5="","",SUBTOTAL(3,$B$4:B5))</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B5" s="25" t="s">
         <v>174</v>
@@ -20919,10 +20911,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:60" hidden="1">
+    <row r="6" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A6" s="24">
         <f>IF(B6="","",SUBTOTAL(3,$B$4:B6))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B6" s="25" t="s">
         <v>174</v>
@@ -21042,10 +21034,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:60" hidden="1">
+    <row r="7" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A7" s="24">
         <f>IF(B7="","",SUBTOTAL(3,$B$4:B7))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B7" s="25" t="s">
         <v>174</v>
@@ -21165,10 +21157,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="8" spans="1:60" hidden="1">
+    <row r="8" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A8" s="24">
         <f>IF(B8="","",SUBTOTAL(3,$B$4:B8))</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B8" s="25" t="s">
         <v>174</v>
@@ -21288,10 +21280,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="9" spans="1:60" hidden="1">
+    <row r="9" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A9" s="24">
         <f>IF(B9="","",SUBTOTAL(3,$B$4:B9))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B9" s="25" t="s">
         <v>174</v>
@@ -21411,10 +21403,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:60" hidden="1">
+    <row r="10" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A10" s="24">
         <f>IF(B10="","",SUBTOTAL(3,$B$4:B10))</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B10" s="25" t="s">
         <v>174</v>
@@ -21534,10 +21526,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:60" hidden="1">
+    <row r="11" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A11" s="24">
         <f>IF(B11="","",SUBTOTAL(3,$B$4:B11))</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>174</v>
@@ -21657,10 +21649,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:60" hidden="1">
+    <row r="12" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A12" s="24">
         <f>IF(B12="","",SUBTOTAL(3,$B$4:B12))</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>174</v>
@@ -21782,10 +21774,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:60" hidden="1">
+    <row r="13" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A13" s="24">
         <f>IF(B13="","",SUBTOTAL(3,$B$4:B13))</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B13" s="25" t="s">
         <v>174</v>
@@ -21907,10 +21899,10 @@
         <v>51008.607039999988</v>
       </c>
     </row>
-    <row r="14" spans="1:60" hidden="1">
+    <row r="14" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <f>IF(B14="","",SUBTOTAL(3,$B$4:B14))</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B14" s="25" t="s">
         <v>174</v>
@@ -22023,10 +22015,10 @@
       <c r="BC14" s="71"/>
       <c r="BD14" s="71"/>
     </row>
-    <row r="15" spans="1:60" hidden="1">
+    <row r="15" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A15" s="24">
         <f>IF(B15="","",SUBTOTAL(3,$B$4:B15))</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B15" s="25" t="s">
         <v>174</v>
@@ -22139,10 +22131,10 @@
       <c r="BC15" s="71"/>
       <c r="BD15" s="71"/>
     </row>
-    <row r="16" spans="1:60" hidden="1">
+    <row r="16" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <f>IF(B16="","",SUBTOTAL(3,$B$4:B16))</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B16" s="25" t="s">
         <v>174</v>
@@ -22255,10 +22247,10 @@
       <c r="BC16" s="71"/>
       <c r="BD16" s="71"/>
     </row>
-    <row r="17" spans="1:56" hidden="1">
+    <row r="17" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A17" s="24">
         <f>IF(B17="","",SUBTOTAL(3,$B$4:B17))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>174</v>
@@ -22371,10 +22363,10 @@
       <c r="BC17" s="71"/>
       <c r="BD17" s="71"/>
     </row>
-    <row r="18" spans="1:56" hidden="1">
+    <row r="18" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A18" s="24">
         <f>IF(B18="","",SUBTOTAL(3,$B$4:B18))</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>174</v>
@@ -22487,10 +22479,10 @@
       <c r="BC18" s="71"/>
       <c r="BD18" s="71"/>
     </row>
-    <row r="19" spans="1:56" hidden="1">
+    <row r="19" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A19" s="24">
         <f>IF(B19="","",SUBTOTAL(3,$B$4:B19))</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>174</v>
@@ -22603,10 +22595,10 @@
       <c r="BC19" s="71"/>
       <c r="BD19" s="71"/>
     </row>
-    <row r="20" spans="1:56" hidden="1">
+    <row r="20" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A20" s="24">
         <f>IF(B20="","",SUBTOTAL(3,$B$4:B20))</f>
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>174</v>
@@ -22719,10 +22711,10 @@
       <c r="BC20" s="71"/>
       <c r="BD20" s="71"/>
     </row>
-    <row r="21" spans="1:56" hidden="1">
+    <row r="21" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A21" s="24">
         <f>IF(B21="","",SUBTOTAL(3,$B$4:B21))</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>174</v>
@@ -22835,10 +22827,10 @@
       <c r="BC21" s="71"/>
       <c r="BD21" s="71"/>
     </row>
-    <row r="22" spans="1:56" hidden="1">
+    <row r="22" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A22" s="24">
         <f>IF(B22="","",SUBTOTAL(3,$B$4:B22))</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>174</v>
@@ -22951,10 +22943,10 @@
       <c r="BC22" s="71"/>
       <c r="BD22" s="71"/>
     </row>
-    <row r="23" spans="1:56" hidden="1">
+    <row r="23" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A23" s="24">
         <f>IF(B23="","",SUBTOTAL(3,$B$4:B23))</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>174</v>
@@ -23067,10 +23059,10 @@
       <c r="BC23" s="71"/>
       <c r="BD23" s="71"/>
     </row>
-    <row r="24" spans="1:56" hidden="1">
+    <row r="24" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A24" s="24">
         <f>IF(B24="","",SUBTOTAL(3,$B$4:B24))</f>
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B24" s="25" t="s">
         <v>174</v>
@@ -23183,10 +23175,10 @@
       <c r="BC24" s="71"/>
       <c r="BD24" s="71"/>
     </row>
-    <row r="25" spans="1:56" hidden="1">
+    <row r="25" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A25" s="24">
         <f>IF(B25="","",SUBTOTAL(3,$B$4:B25))</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="B25" s="25" t="s">
         <v>174</v>
@@ -23299,10 +23291,10 @@
       <c r="BC25" s="71"/>
       <c r="BD25" s="71"/>
     </row>
-    <row r="26" spans="1:56" hidden="1">
+    <row r="26" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A26" s="24">
         <f>IF(B26="","",SUBTOTAL(3,$B$4:B26))</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B26" s="25" t="s">
         <v>174</v>
@@ -23415,10 +23407,10 @@
       <c r="BC26" s="71"/>
       <c r="BD26" s="71"/>
     </row>
-    <row r="27" spans="1:56" hidden="1">
+    <row r="27" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A27" s="24">
         <f>IF(B27="","",SUBTOTAL(3,$B$4:B27))</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B27" s="25" t="s">
         <v>174</v>
@@ -23531,10 +23523,10 @@
       <c r="BC27" s="71"/>
       <c r="BD27" s="71"/>
     </row>
-    <row r="28" spans="1:56" hidden="1">
+    <row r="28" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A28" s="24">
         <f>IF(B28="","",SUBTOTAL(3,$B$4:B28))</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="B28" s="25" t="s">
         <v>174</v>
@@ -23647,10 +23639,10 @@
       <c r="BC28" s="71"/>
       <c r="BD28" s="71"/>
     </row>
-    <row r="29" spans="1:56" hidden="1">
+    <row r="29" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A29" s="24">
         <f>IF(B29="","",SUBTOTAL(3,$B$4:B29))</f>
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="B29" s="25" t="s">
         <v>174</v>
@@ -23763,10 +23755,10 @@
       <c r="BC29" s="71"/>
       <c r="BD29" s="71"/>
     </row>
-    <row r="30" spans="1:56" hidden="1">
+    <row r="30" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A30" s="24">
         <f>IF(B30="","",SUBTOTAL(3,$B$4:B30))</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B30" s="25" t="s">
         <v>174</v>
@@ -23879,10 +23871,10 @@
       <c r="BC30" s="71"/>
       <c r="BD30" s="71"/>
     </row>
-    <row r="31" spans="1:56" hidden="1">
+    <row r="31" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A31" s="24">
         <f>IF(B31="","",SUBTOTAL(3,$B$4:B31))</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B31" s="25" t="s">
         <v>174</v>
@@ -23995,10 +23987,10 @@
       <c r="BC31" s="71"/>
       <c r="BD31" s="71"/>
     </row>
-    <row r="32" spans="1:56" hidden="1">
+    <row r="32" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A32" s="24">
         <f>IF(B32="","",SUBTOTAL(3,$B$4:B32))</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="B32" s="25" t="s">
         <v>174</v>
@@ -24111,10 +24103,10 @@
       <c r="BC32" s="71"/>
       <c r="BD32" s="71"/>
     </row>
-    <row r="33" spans="1:56" hidden="1">
+    <row r="33" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A33" s="24">
         <f>IF(B33="","",SUBTOTAL(3,$B$4:B33))</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="B33" s="25" t="s">
         <v>174</v>
@@ -24227,10 +24219,10 @@
       <c r="BC33" s="71"/>
       <c r="BD33" s="71"/>
     </row>
-    <row r="34" spans="1:56" hidden="1">
+    <row r="34" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A34" s="24">
         <f>IF(B34="","",SUBTOTAL(3,$B$4:B34))</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>174</v>
@@ -24343,10 +24335,10 @@
       <c r="BC34" s="71"/>
       <c r="BD34" s="71"/>
     </row>
-    <row r="35" spans="1:56" hidden="1">
+    <row r="35" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A35" s="24">
         <f>IF(B35="","",SUBTOTAL(3,$B$4:B35))</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>174</v>
@@ -24459,10 +24451,10 @@
       <c r="BC35" s="71"/>
       <c r="BD35" s="71"/>
     </row>
-    <row r="36" spans="1:56" hidden="1">
+    <row r="36" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A36" s="24">
         <f>IF(B36="","",SUBTOTAL(3,$B$4:B36))</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>174</v>
@@ -24575,10 +24567,10 @@
       <c r="BC36" s="71"/>
       <c r="BD36" s="71"/>
     </row>
-    <row r="37" spans="1:56" hidden="1">
+    <row r="37" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A37" s="24">
         <f>IF(B37="","",SUBTOTAL(3,$B$4:B37))</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B37" s="25" t="s">
         <v>174</v>
@@ -24691,10 +24683,10 @@
       <c r="BC37" s="71"/>
       <c r="BD37" s="71"/>
     </row>
-    <row r="38" spans="1:56" hidden="1">
+    <row r="38" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A38" s="24">
         <f>IF(B38="","",SUBTOTAL(3,$B$4:B38))</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>174</v>
@@ -24807,10 +24799,10 @@
       <c r="BC38" s="71"/>
       <c r="BD38" s="71"/>
     </row>
-    <row r="39" spans="1:56" hidden="1">
+    <row r="39" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A39" s="24">
         <f>IF(B39="","",SUBTOTAL(3,$B$4:B39))</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>174</v>
@@ -24923,10 +24915,10 @@
       <c r="BC39" s="71"/>
       <c r="BD39" s="71"/>
     </row>
-    <row r="40" spans="1:56" hidden="1">
+    <row r="40" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A40" s="24">
         <f>IF(B40="","",SUBTOTAL(3,$B$4:B40))</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B40" s="25" t="s">
         <v>174</v>
@@ -25039,10 +25031,10 @@
       <c r="BC40" s="71"/>
       <c r="BD40" s="71"/>
     </row>
-    <row r="41" spans="1:56" hidden="1">
+    <row r="41" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A41" s="24">
         <f>IF(B41="","",SUBTOTAL(3,$B$4:B41))</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>174</v>
@@ -25155,10 +25147,10 @@
       <c r="BC41" s="71"/>
       <c r="BD41" s="71"/>
     </row>
-    <row r="42" spans="1:56" hidden="1">
+    <row r="42" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A42" s="24">
         <f>IF(B42="","",SUBTOTAL(3,$B$4:B42))</f>
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B42" s="25" t="s">
         <v>174</v>
@@ -25271,10 +25263,10 @@
       <c r="BC42" s="71"/>
       <c r="BD42" s="71"/>
     </row>
-    <row r="43" spans="1:56" hidden="1">
+    <row r="43" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A43" s="24">
         <f>IF(B43="","",SUBTOTAL(3,$B$4:B43))</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>174</v>
@@ -25385,10 +25377,10 @@
       <c r="BC43" s="71"/>
       <c r="BD43" s="71"/>
     </row>
-    <row r="44" spans="1:56" hidden="1">
+    <row r="44" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A44" s="24">
         <f>IF(B44="","",SUBTOTAL(3,$B$4:B44))</f>
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="B44" s="25" t="s">
         <v>174</v>
@@ -25499,10 +25491,10 @@
       <c r="BC44" s="71"/>
       <c r="BD44" s="71"/>
     </row>
-    <row r="45" spans="1:56" hidden="1">
+    <row r="45" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A45" s="24">
         <f>IF(B45="","",SUBTOTAL(3,$B$4:B45))</f>
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>174</v>
@@ -25613,10 +25605,10 @@
       <c r="BC45" s="71"/>
       <c r="BD45" s="71"/>
     </row>
-    <row r="46" spans="1:56" hidden="1">
+    <row r="46" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A46" s="24">
         <f>IF(B46="","",SUBTOTAL(3,$B$4:B46))</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>174</v>
@@ -25727,10 +25719,10 @@
       <c r="BC46" s="71"/>
       <c r="BD46" s="71"/>
     </row>
-    <row r="47" spans="1:56" hidden="1">
+    <row r="47" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A47" s="24">
         <f>IF(B47="","",SUBTOTAL(3,$B$4:B47))</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="B47" s="25" t="s">
         <v>174</v>
@@ -25841,10 +25833,10 @@
       <c r="BC47" s="71"/>
       <c r="BD47" s="71"/>
     </row>
-    <row r="48" spans="1:56" hidden="1">
+    <row r="48" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A48" s="24">
         <f>IF(B48="","",SUBTOTAL(3,$B$4:B48))</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B48" s="25" t="s">
         <v>174</v>
@@ -25955,10 +25947,10 @@
       <c r="BC48" s="71"/>
       <c r="BD48" s="71"/>
     </row>
-    <row r="49" spans="1:56" hidden="1">
+    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A49" s="24">
         <f>IF(B49="","",SUBTOTAL(3,$B$4:B49))</f>
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>174</v>
@@ -26069,10 +26061,10 @@
       <c r="BC49" s="71"/>
       <c r="BD49" s="71"/>
     </row>
-    <row r="50" spans="1:56" hidden="1">
+    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A50" s="24">
         <f>IF(B50="","",SUBTOTAL(3,$B$4:B50))</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>174</v>
@@ -26183,10 +26175,10 @@
       <c r="BC50" s="71"/>
       <c r="BD50" s="71"/>
     </row>
-    <row r="51" spans="1:56" hidden="1">
+    <row r="51" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A51" s="24">
         <f>IF(B51="","",SUBTOTAL(3,$B$4:B51))</f>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="B51" s="25" t="s">
         <v>174</v>
@@ -26297,10 +26289,10 @@
       <c r="BC51" s="71"/>
       <c r="BD51" s="71"/>
     </row>
-    <row r="52" spans="1:56" hidden="1">
+    <row r="52" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A52" s="24">
         <f>IF(B52="","",SUBTOTAL(3,$B$4:B52))</f>
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="B52" s="25" t="s">
         <v>174</v>
@@ -26411,10 +26403,10 @@
       <c r="BC52" s="71"/>
       <c r="BD52" s="71"/>
     </row>
-    <row r="53" spans="1:56" hidden="1">
+    <row r="53" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A53" s="24">
         <f>IF(B53="","",SUBTOTAL(3,$B$4:B53))</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B53" s="25" t="s">
         <v>174</v>
@@ -26525,10 +26517,10 @@
       <c r="BC53" s="71"/>
       <c r="BD53" s="71"/>
     </row>
-    <row r="54" spans="1:56" hidden="1">
+    <row r="54" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A54" s="24">
         <f>IF(B54="","",SUBTOTAL(3,$B$4:B54))</f>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="B54" s="25" t="s">
         <v>174</v>
@@ -26639,10 +26631,10 @@
       <c r="BC54" s="71"/>
       <c r="BD54" s="71"/>
     </row>
-    <row r="55" spans="1:56" hidden="1">
+    <row r="55" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A55" s="24">
         <f>IF(B55="","",SUBTOTAL(3,$B$4:B55))</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="B55" s="25" t="s">
         <v>174</v>
@@ -26753,10 +26745,10 @@
       <c r="BC55" s="71"/>
       <c r="BD55" s="71"/>
     </row>
-    <row r="56" spans="1:56" hidden="1">
+    <row r="56" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A56" s="24">
         <f>IF(B56="","",SUBTOTAL(3,$B$4:B56))</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="B56" s="25" t="s">
         <v>174</v>
@@ -26867,10 +26859,10 @@
       <c r="BC56" s="71"/>
       <c r="BD56" s="71"/>
     </row>
-    <row r="57" spans="1:56" hidden="1">
+    <row r="57" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A57" s="24">
         <f>IF(B57="","",SUBTOTAL(3,$B$4:B57))</f>
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="B57" s="25" t="s">
         <v>174</v>
@@ -26981,10 +26973,10 @@
       <c r="BC57" s="71"/>
       <c r="BD57" s="71"/>
     </row>
-    <row r="58" spans="1:56" hidden="1">
+    <row r="58" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A58" s="24">
         <f>IF(B58="","",SUBTOTAL(3,$B$4:B58))</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B58" s="25" t="s">
         <v>174</v>
@@ -27097,10 +27089,10 @@
       <c r="BC58" s="71"/>
       <c r="BD58" s="71"/>
     </row>
-    <row r="59" spans="1:56" hidden="1">
+    <row r="59" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A59" s="24">
         <f>IF(B59="","",SUBTOTAL(3,$B$4:B59))</f>
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="B59" s="25" t="s">
         <v>174</v>
@@ -27213,10 +27205,10 @@
       <c r="BC59" s="71"/>
       <c r="BD59" s="71"/>
     </row>
-    <row r="60" spans="1:56" hidden="1">
+    <row r="60" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A60" s="24">
         <f>IF(B60="","",SUBTOTAL(3,$B$4:B60))</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="B60" s="25" t="s">
         <v>174</v>
@@ -27329,10 +27321,10 @@
       <c r="BC60" s="71"/>
       <c r="BD60" s="71"/>
     </row>
-    <row r="61" spans="1:56" hidden="1">
+    <row r="61" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A61" s="24">
         <f>IF(B61="","",SUBTOTAL(3,$B$4:B61))</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="B61" s="25" t="s">
         <v>174</v>
@@ -27445,10 +27437,10 @@
       <c r="BC61" s="71"/>
       <c r="BD61" s="71"/>
     </row>
-    <row r="62" spans="1:56" hidden="1">
+    <row r="62" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A62" s="24">
         <f>IF(B62="","",SUBTOTAL(3,$B$4:B62))</f>
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>174</v>
@@ -27561,10 +27553,10 @@
       <c r="BC62" s="71"/>
       <c r="BD62" s="71"/>
     </row>
-    <row r="63" spans="1:56" hidden="1">
+    <row r="63" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A63" s="24">
         <f>IF(B63="","",SUBTOTAL(3,$B$4:B63))</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B63" s="25" t="s">
         <v>174</v>
@@ -27677,10 +27669,10 @@
       <c r="BC63" s="71"/>
       <c r="BD63" s="71"/>
     </row>
-    <row r="64" spans="1:56" hidden="1">
+    <row r="64" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A64" s="24">
         <f>IF(B64="","",SUBTOTAL(3,$B$4:B64))</f>
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="B64" s="25" t="s">
         <v>174</v>
@@ -27793,10 +27785,10 @@
       <c r="BC64" s="71"/>
       <c r="BD64" s="71"/>
     </row>
-    <row r="65" spans="1:56" hidden="1">
+    <row r="65" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A65" s="24">
         <f>IF(B65="","",SUBTOTAL(3,$B$4:B65))</f>
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="B65" s="25" t="s">
         <v>174</v>
@@ -27909,10 +27901,10 @@
       <c r="BC65" s="71"/>
       <c r="BD65" s="71"/>
     </row>
-    <row r="66" spans="1:56" hidden="1">
+    <row r="66" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A66" s="24">
         <f>IF(B66="","",SUBTOTAL(3,$B$4:B66))</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="B66" s="25" t="s">
         <v>174</v>
@@ -28025,10 +28017,10 @@
       <c r="BC66" s="71"/>
       <c r="BD66" s="71"/>
     </row>
-    <row r="67" spans="1:56" hidden="1">
+    <row r="67" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A67" s="24">
         <f>IF(B67="","",SUBTOTAL(3,$B$4:B67))</f>
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>174</v>
@@ -28141,10 +28133,10 @@
       <c r="BC67" s="71"/>
       <c r="BD67" s="71"/>
     </row>
-    <row r="68" spans="1:56" hidden="1">
+    <row r="68" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A68" s="24">
         <f>IF(B68="","",SUBTOTAL(3,$B$4:B68))</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="B68" s="25" t="s">
         <v>174</v>
@@ -28257,10 +28249,10 @@
       <c r="BC68" s="71"/>
       <c r="BD68" s="71"/>
     </row>
-    <row r="69" spans="1:56" hidden="1">
+    <row r="69" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A69" s="24">
         <f>IF(B69="","",SUBTOTAL(3,$B$4:B69))</f>
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="B69" s="25" t="s">
         <v>174</v>
@@ -28373,10 +28365,10 @@
       <c r="BC69" s="71"/>
       <c r="BD69" s="71"/>
     </row>
-    <row r="70" spans="1:56" hidden="1">
+    <row r="70" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A70" s="24">
         <f>IF(B70="","",SUBTOTAL(3,$B$4:B70))</f>
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="B70" s="25" t="s">
         <v>174</v>
@@ -28489,10 +28481,10 @@
       <c r="BC70" s="71"/>
       <c r="BD70" s="71"/>
     </row>
-    <row r="71" spans="1:56" hidden="1">
+    <row r="71" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A71" s="24">
         <f>IF(B71="","",SUBTOTAL(3,$B$4:B71))</f>
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="B71" s="25" t="s">
         <v>174</v>
@@ -28605,10 +28597,10 @@
       <c r="BC71" s="71"/>
       <c r="BD71" s="71"/>
     </row>
-    <row r="72" spans="1:56" hidden="1">
+    <row r="72" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A72" s="24">
         <f>IF(B72="","",SUBTOTAL(3,$B$4:B72))</f>
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="B72" s="25" t="s">
         <v>174</v>
@@ -28721,10 +28713,10 @@
       <c r="BC72" s="71"/>
       <c r="BD72" s="71"/>
     </row>
-    <row r="73" spans="1:56" hidden="1">
+    <row r="73" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A73" s="24">
         <f>IF(B73="","",SUBTOTAL(3,$B$4:B73))</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B73" s="25" t="s">
         <v>174</v>
@@ -28837,10 +28829,10 @@
       <c r="BC73" s="71"/>
       <c r="BD73" s="71"/>
     </row>
-    <row r="74" spans="1:56" hidden="1">
+    <row r="74" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A74" s="24">
         <f>IF(B74="","",SUBTOTAL(3,$B$4:B74))</f>
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="B74" s="25" t="s">
         <v>174</v>
@@ -28953,10 +28945,10 @@
       <c r="BC74" s="71"/>
       <c r="BD74" s="71"/>
     </row>
-    <row r="75" spans="1:56" hidden="1">
+    <row r="75" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A75" s="24">
         <f>IF(B75="","",SUBTOTAL(3,$B$4:B75))</f>
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="B75" s="25" t="s">
         <v>174</v>
@@ -29069,10 +29061,10 @@
       <c r="BC75" s="71"/>
       <c r="BD75" s="71"/>
     </row>
-    <row r="76" spans="1:56" hidden="1">
+    <row r="76" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A76" s="24">
         <f>IF(B76="","",SUBTOTAL(3,$B$4:B76))</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="B76" s="25" t="s">
         <v>174</v>
@@ -29185,10 +29177,10 @@
       <c r="BC76" s="71"/>
       <c r="BD76" s="71"/>
     </row>
-    <row r="77" spans="1:56" hidden="1">
+    <row r="77" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A77" s="24">
         <f>IF(B77="","",SUBTOTAL(3,$B$4:B77))</f>
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="B77" s="25" t="s">
         <v>174</v>
@@ -29301,10 +29293,10 @@
       <c r="BC77" s="71"/>
       <c r="BD77" s="71"/>
     </row>
-    <row r="78" spans="1:56" hidden="1">
+    <row r="78" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A78" s="24">
         <f>IF(B78="","",SUBTOTAL(3,$B$4:B78))</f>
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="B78" s="25" t="s">
         <v>174</v>
@@ -29417,10 +29409,10 @@
       <c r="BC78" s="71"/>
       <c r="BD78" s="71"/>
     </row>
-    <row r="79" spans="1:56" hidden="1">
+    <row r="79" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A79" s="24">
         <f>IF(B79="","",SUBTOTAL(3,$B$4:B79))</f>
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="B79" s="25" t="s">
         <v>174</v>
@@ -29533,10 +29525,10 @@
       <c r="BC79" s="71"/>
       <c r="BD79" s="71"/>
     </row>
-    <row r="80" spans="1:56" hidden="1">
+    <row r="80" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A80" s="24">
         <f>IF(B80="","",SUBTOTAL(3,$B$4:B80))</f>
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>174</v>
@@ -29649,10 +29641,10 @@
       <c r="BC80" s="71"/>
       <c r="BD80" s="71"/>
     </row>
-    <row r="81" spans="1:56" hidden="1">
+    <row r="81" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A81" s="24">
         <f>IF(B81="","",SUBTOTAL(3,$B$4:B81))</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="B81" s="25" t="s">
         <v>174</v>
@@ -29765,10 +29757,10 @@
       <c r="BC81" s="71"/>
       <c r="BD81" s="71"/>
     </row>
-    <row r="82" spans="1:56" hidden="1">
+    <row r="82" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A82" s="24">
         <f>IF(B82="","",SUBTOTAL(3,$B$4:B82))</f>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="B82" s="25" t="s">
         <v>174</v>
@@ -29881,10 +29873,10 @@
       <c r="BC82" s="71"/>
       <c r="BD82" s="71"/>
     </row>
-    <row r="83" spans="1:56" hidden="1">
+    <row r="83" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A83" s="24">
         <f>IF(B83="","",SUBTOTAL(3,$B$4:B83))</f>
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="B83" s="25" t="s">
         <v>174</v>
@@ -29997,10 +29989,10 @@
       <c r="BC83" s="71"/>
       <c r="BD83" s="71"/>
     </row>
-    <row r="84" spans="1:56" hidden="1">
+    <row r="84" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A84" s="24">
         <f>IF(B84="","",SUBTOTAL(3,$B$4:B84))</f>
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="B84" s="25" t="s">
         <v>174</v>
@@ -30113,10 +30105,10 @@
       <c r="BC84" s="71"/>
       <c r="BD84" s="71"/>
     </row>
-    <row r="85" spans="1:56" hidden="1">
+    <row r="85" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A85" s="24">
         <f>IF(B85="","",SUBTOTAL(3,$B$4:B85))</f>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="B85" s="25" t="s">
         <v>174</v>
@@ -30229,10 +30221,10 @@
       <c r="BC85" s="71"/>
       <c r="BD85" s="71"/>
     </row>
-    <row r="86" spans="1:56" hidden="1">
+    <row r="86" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A86" s="24">
         <f>IF(B86="","",SUBTOTAL(3,$B$4:B86))</f>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="B86" s="25" t="s">
         <v>174</v>
@@ -30345,10 +30337,10 @@
       <c r="BC86" s="71"/>
       <c r="BD86" s="71"/>
     </row>
-    <row r="87" spans="1:56" hidden="1">
+    <row r="87" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A87" s="24">
         <f>IF(B87="","",SUBTOTAL(3,$B$4:B87))</f>
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="B87" s="25" t="s">
         <v>174</v>
@@ -30461,10 +30453,10 @@
       <c r="BC87" s="71"/>
       <c r="BD87" s="71"/>
     </row>
-    <row r="88" spans="1:56" hidden="1">
+    <row r="88" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A88" s="24">
         <f>IF(B88="","",SUBTOTAL(3,$B$4:B88))</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="B88" s="25" t="s">
         <v>174</v>
@@ -30577,10 +30569,10 @@
       <c r="BC88" s="71"/>
       <c r="BD88" s="71"/>
     </row>
-    <row r="89" spans="1:56" hidden="1">
+    <row r="89" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A89" s="24">
         <f>IF(B89="","",SUBTOTAL(3,$B$4:B89))</f>
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="B89" s="25" t="s">
         <v>174</v>
@@ -30693,10 +30685,10 @@
       <c r="BC89" s="71"/>
       <c r="BD89" s="71"/>
     </row>
-    <row r="90" spans="1:56" hidden="1">
+    <row r="90" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A90" s="24">
         <f>IF(B90="","",SUBTOTAL(3,$B$4:B90))</f>
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="B90" s="25" t="s">
         <v>174</v>
@@ -30809,10 +30801,10 @@
       <c r="BC90" s="71"/>
       <c r="BD90" s="71"/>
     </row>
-    <row r="91" spans="1:56" hidden="1">
+    <row r="91" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A91" s="24">
         <f>IF(B91="","",SUBTOTAL(3,$B$4:B91))</f>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="B91" s="25" t="s">
         <v>174</v>
@@ -30925,10 +30917,10 @@
       <c r="BC91" s="71"/>
       <c r="BD91" s="71"/>
     </row>
-    <row r="92" spans="1:56" hidden="1">
+    <row r="92" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A92" s="24">
         <f>IF(B92="","",SUBTOTAL(3,$B$4:B92))</f>
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="B92" s="25" t="s">
         <v>174</v>
@@ -31039,10 +31031,10 @@
       <c r="BC92" s="71"/>
       <c r="BD92" s="71"/>
     </row>
-    <row r="93" spans="1:56" hidden="1">
+    <row r="93" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A93" s="24">
         <f>IF(B93="","",SUBTOTAL(3,$B$4:B93))</f>
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="B93" s="25" t="s">
         <v>174</v>
@@ -31153,10 +31145,10 @@
       <c r="BC93" s="71"/>
       <c r="BD93" s="71"/>
     </row>
-    <row r="94" spans="1:56" hidden="1">
+    <row r="94" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A94" s="24">
         <f>IF(B94="","",SUBTOTAL(3,$B$4:B94))</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B94" s="25" t="s">
         <v>174</v>
@@ -31267,10 +31259,10 @@
       <c r="BC94" s="71"/>
       <c r="BD94" s="71"/>
     </row>
-    <row r="95" spans="1:56" hidden="1">
+    <row r="95" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A95" s="24">
         <f>IF(B95="","",SUBTOTAL(3,$B$4:B95))</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="B95" s="25" t="s">
         <v>174</v>
@@ -31381,10 +31373,10 @@
       <c r="BC95" s="71"/>
       <c r="BD95" s="71"/>
     </row>
-    <row r="96" spans="1:56" hidden="1">
+    <row r="96" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A96" s="24">
         <f>IF(B96="","",SUBTOTAL(3,$B$4:B96))</f>
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="B96" s="25" t="s">
         <v>174</v>
@@ -31495,10 +31487,10 @@
       <c r="BC96" s="71"/>
       <c r="BD96" s="71"/>
     </row>
-    <row r="97" spans="1:56" hidden="1">
+    <row r="97" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A97" s="24">
         <f>IF(B97="","",SUBTOTAL(3,$B$4:B97))</f>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="B97" s="25" t="s">
         <v>174</v>
@@ -31609,10 +31601,10 @@
       <c r="BC97" s="71"/>
       <c r="BD97" s="71"/>
     </row>
-    <row r="98" spans="1:56" hidden="1">
+    <row r="98" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A98" s="24">
         <f>IF(B98="","",SUBTOTAL(3,$B$4:B98))</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="B98" s="25" t="s">
         <v>174</v>
@@ -31723,10 +31715,10 @@
       <c r="BC98" s="71"/>
       <c r="BD98" s="71"/>
     </row>
-    <row r="99" spans="1:56" hidden="1">
+    <row r="99" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A99" s="24">
         <f>IF(B99="","",SUBTOTAL(3,$B$4:B99))</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="B99" s="25" t="s">
         <v>174</v>
@@ -31837,10 +31829,10 @@
       <c r="BC99" s="71"/>
       <c r="BD99" s="71"/>
     </row>
-    <row r="100" spans="1:56" hidden="1">
+    <row r="100" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A100" s="24">
         <f>IF(B100="","",SUBTOTAL(3,$B$4:B100))</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="B100" s="25" t="s">
         <v>174</v>
@@ -31951,10 +31943,10 @@
       <c r="BC100" s="71"/>
       <c r="BD100" s="71"/>
     </row>
-    <row r="101" spans="1:56" hidden="1">
+    <row r="101" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A101" s="24">
         <f>IF(B101="","",SUBTOTAL(3,$B$4:B101))</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="B101" s="25" t="s">
         <v>174</v>
@@ -32065,10 +32057,10 @@
       <c r="BC101" s="71"/>
       <c r="BD101" s="71"/>
     </row>
-    <row r="102" spans="1:56" hidden="1">
+    <row r="102" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A102" s="24">
         <f>IF(B102="","",SUBTOTAL(3,$B$4:B102))</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>174</v>
@@ -32179,10 +32171,10 @@
       <c r="BC102" s="71"/>
       <c r="BD102" s="71"/>
     </row>
-    <row r="103" spans="1:56" hidden="1">
+    <row r="103" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A103" s="24">
         <f>IF(B103="","",SUBTOTAL(3,$B$4:B103))</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B103" s="25" t="s">
         <v>174</v>
@@ -32293,10 +32285,10 @@
       <c r="BC103" s="71"/>
       <c r="BD103" s="71"/>
     </row>
-    <row r="104" spans="1:56" hidden="1">
+    <row r="104" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A104" s="24">
         <f>IF(B104="","",SUBTOTAL(3,$B$4:B104))</f>
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="B104" s="25" t="s">
         <v>174</v>
@@ -32407,10 +32399,10 @@
       <c r="BC104" s="71"/>
       <c r="BD104" s="71"/>
     </row>
-    <row r="105" spans="1:56" hidden="1">
+    <row r="105" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A105" s="24">
         <f>IF(B105="","",SUBTOTAL(3,$B$4:B105))</f>
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B105" s="25" t="s">
         <v>174</v>
@@ -32521,10 +32513,10 @@
       <c r="BC105" s="71"/>
       <c r="BD105" s="71"/>
     </row>
-    <row r="106" spans="1:56" hidden="1">
+    <row r="106" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A106" s="24">
         <f>IF(B106="","",SUBTOTAL(3,$B$4:B106))</f>
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="B106" s="25" t="s">
         <v>174</v>
@@ -32635,10 +32627,10 @@
       <c r="BC106" s="71"/>
       <c r="BD106" s="71"/>
     </row>
-    <row r="107" spans="1:56" hidden="1">
+    <row r="107" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A107" s="24">
         <f>IF(B107="","",SUBTOTAL(3,$B$4:B107))</f>
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="B107" s="25" t="s">
         <v>174</v>
@@ -32751,10 +32743,10 @@
       <c r="BC107" s="71"/>
       <c r="BD107" s="71"/>
     </row>
-    <row r="108" spans="1:56" hidden="1">
+    <row r="108" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A108" s="24">
         <f>IF(B108="","",SUBTOTAL(3,$B$4:B108))</f>
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="B108" s="25" t="s">
         <v>174</v>
@@ -32867,10 +32859,10 @@
       <c r="BC108" s="71"/>
       <c r="BD108" s="71"/>
     </row>
-    <row r="109" spans="1:56" hidden="1">
+    <row r="109" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A109" s="24">
         <f>IF(B109="","",SUBTOTAL(3,$B$4:B109))</f>
-        <v>0</v>
+        <v>106</v>
       </c>
       <c r="B109" s="25" t="s">
         <v>174</v>
@@ -32983,10 +32975,10 @@
       <c r="BC109" s="71"/>
       <c r="BD109" s="71"/>
     </row>
-    <row r="110" spans="1:56" hidden="1">
+    <row r="110" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A110" s="24">
         <f>IF(B110="","",SUBTOTAL(3,$B$4:B110))</f>
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="B110" s="25" t="s">
         <v>174</v>
@@ -33099,10 +33091,10 @@
       <c r="BC110" s="71"/>
       <c r="BD110" s="71"/>
     </row>
-    <row r="111" spans="1:56" hidden="1">
+    <row r="111" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A111" s="24">
         <f>IF(B111="","",SUBTOTAL(3,$B$4:B111))</f>
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="B111" s="25" t="s">
         <v>174</v>
@@ -33215,10 +33207,10 @@
       <c r="BC111" s="71"/>
       <c r="BD111" s="71"/>
     </row>
-    <row r="112" spans="1:56" hidden="1">
+    <row r="112" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A112" s="24">
         <f>IF(B112="","",SUBTOTAL(3,$B$4:B112))</f>
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="B112" s="25" t="s">
         <v>174</v>
@@ -33331,10 +33323,10 @@
       <c r="BC112" s="71"/>
       <c r="BD112" s="71"/>
     </row>
-    <row r="113" spans="1:56" hidden="1">
+    <row r="113" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A113" s="24">
         <f>IF(B113="","",SUBTOTAL(3,$B$4:B113))</f>
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="B113" s="25" t="s">
         <v>174</v>
@@ -33447,10 +33439,10 @@
       <c r="BC113" s="71"/>
       <c r="BD113" s="71"/>
     </row>
-    <row r="114" spans="1:56" hidden="1">
+    <row r="114" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A114" s="24">
         <f>IF(B114="","",SUBTOTAL(3,$B$4:B114))</f>
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="B114" s="25" t="s">
         <v>174</v>
@@ -33563,10 +33555,10 @@
       <c r="BC114" s="71"/>
       <c r="BD114" s="71"/>
     </row>
-    <row r="115" spans="1:56" hidden="1">
+    <row r="115" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A115" s="24">
         <f>IF(B115="","",SUBTOTAL(3,$B$4:B115))</f>
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="B115" s="25" t="s">
         <v>174</v>
@@ -33679,10 +33671,10 @@
       <c r="BC115" s="71"/>
       <c r="BD115" s="71"/>
     </row>
-    <row r="116" spans="1:56" hidden="1">
+    <row r="116" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A116" s="24">
         <f>IF(B116="","",SUBTOTAL(3,$B$4:B116))</f>
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="B116" s="25" t="s">
         <v>174</v>
@@ -33795,10 +33787,10 @@
       <c r="BC116" s="71"/>
       <c r="BD116" s="71"/>
     </row>
-    <row r="117" spans="1:56" hidden="1">
+    <row r="117" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A117" s="24">
         <f>IF(B117="","",SUBTOTAL(3,$B$4:B117))</f>
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="B117" s="25" t="s">
         <v>174</v>
@@ -33911,10 +33903,10 @@
       <c r="BC117" s="71"/>
       <c r="BD117" s="71"/>
     </row>
-    <row r="118" spans="1:56" hidden="1">
+    <row r="118" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A118" s="24">
         <f>IF(B118="","",SUBTOTAL(3,$B$4:B118))</f>
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="B118" s="25" t="s">
         <v>174</v>
@@ -34027,10 +34019,10 @@
       <c r="BC118" s="71"/>
       <c r="BD118" s="71"/>
     </row>
-    <row r="119" spans="1:56" hidden="1">
+    <row r="119" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A119" s="24">
         <f>IF(B119="","",SUBTOTAL(3,$B$4:B119))</f>
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="B119" s="25" t="s">
         <v>174</v>
@@ -34143,10 +34135,10 @@
       <c r="BC119" s="71"/>
       <c r="BD119" s="71"/>
     </row>
-    <row r="120" spans="1:56" hidden="1">
+    <row r="120" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A120" s="24">
         <f>IF(B120="","",SUBTOTAL(3,$B$4:B120))</f>
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="B120" s="25" t="s">
         <v>174</v>
@@ -34259,10 +34251,10 @@
       <c r="BC120" s="71"/>
       <c r="BD120" s="71"/>
     </row>
-    <row r="121" spans="1:56" hidden="1">
+    <row r="121" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A121" s="24">
         <f>IF(B121="","",SUBTOTAL(3,$B$4:B121))</f>
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="B121" s="25" t="s">
         <v>174</v>
@@ -34375,10 +34367,10 @@
       <c r="BC121" s="71"/>
       <c r="BD121" s="71"/>
     </row>
-    <row r="122" spans="1:56" hidden="1">
+    <row r="122" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A122" s="24">
         <f>IF(B122="","",SUBTOTAL(3,$B$4:B122))</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="B122" s="25" t="s">
         <v>174</v>
@@ -34491,10 +34483,10 @@
       <c r="BC122" s="71"/>
       <c r="BD122" s="71"/>
     </row>
-    <row r="123" spans="1:56" hidden="1">
+    <row r="123" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A123" s="24">
         <f>IF(B123="","",SUBTOTAL(3,$B$4:B123))</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="B123" s="25" t="s">
         <v>174</v>
@@ -34607,10 +34599,10 @@
       <c r="BC123" s="71"/>
       <c r="BD123" s="71"/>
     </row>
-    <row r="124" spans="1:56" hidden="1">
+    <row r="124" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A124" s="24">
         <f>IF(B124="","",SUBTOTAL(3,$B$4:B124))</f>
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="B124" s="25" t="s">
         <v>174</v>
@@ -34723,10 +34715,10 @@
       <c r="BC124" s="71"/>
       <c r="BD124" s="71"/>
     </row>
-    <row r="125" spans="1:56" hidden="1">
+    <row r="125" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A125" s="24">
         <f>IF(B125="","",SUBTOTAL(3,$B$4:B125))</f>
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="B125" s="25" t="s">
         <v>174</v>
@@ -34839,10 +34831,10 @@
       <c r="BC125" s="71"/>
       <c r="BD125" s="71"/>
     </row>
-    <row r="126" spans="1:56" hidden="1">
+    <row r="126" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A126" s="24">
         <f>IF(B126="","",SUBTOTAL(3,$B$4:B126))</f>
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="B126" s="25" t="s">
         <v>174</v>
@@ -34955,10 +34947,10 @@
       <c r="BC126" s="71"/>
       <c r="BD126" s="71"/>
     </row>
-    <row r="127" spans="1:56" hidden="1">
+    <row r="127" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A127" s="24">
         <f>IF(B127="","",SUBTOTAL(3,$B$4:B127))</f>
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="B127" s="25" t="s">
         <v>174</v>
@@ -35071,10 +35063,10 @@
       <c r="BC127" s="71"/>
       <c r="BD127" s="71"/>
     </row>
-    <row r="128" spans="1:56" hidden="1">
+    <row r="128" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A128" s="24">
         <f>IF(B128="","",SUBTOTAL(3,$B$4:B128))</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="B128" s="25" t="s">
         <v>174</v>
@@ -35187,10 +35179,10 @@
       <c r="BC128" s="71"/>
       <c r="BD128" s="71"/>
     </row>
-    <row r="129" spans="1:56" hidden="1">
+    <row r="129" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A129" s="24">
         <f>IF(B129="","",SUBTOTAL(3,$B$4:B129))</f>
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="B129" s="25" t="s">
         <v>174</v>
@@ -35303,10 +35295,10 @@
       <c r="BC129" s="71"/>
       <c r="BD129" s="71"/>
     </row>
-    <row r="130" spans="1:56" hidden="1">
+    <row r="130" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A130" s="24">
         <f>IF(B130="","",SUBTOTAL(3,$B$4:B130))</f>
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="B130" s="25" t="s">
         <v>174</v>
@@ -35419,10 +35411,10 @@
       <c r="BC130" s="71"/>
       <c r="BD130" s="71"/>
     </row>
-    <row r="131" spans="1:56" hidden="1">
+    <row r="131" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A131" s="24">
         <f>IF(B131="","",SUBTOTAL(3,$B$4:B131))</f>
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B131" s="25" t="s">
         <v>174</v>
@@ -35535,10 +35527,10 @@
       <c r="BC131" s="71"/>
       <c r="BD131" s="71"/>
     </row>
-    <row r="132" spans="1:56" hidden="1">
+    <row r="132" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A132" s="24">
         <f>IF(B132="","",SUBTOTAL(3,$B$4:B132))</f>
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="B132" s="25" t="s">
         <v>174</v>
@@ -35651,10 +35643,10 @@
       <c r="BC132" s="71"/>
       <c r="BD132" s="71"/>
     </row>
-    <row r="133" spans="1:56" hidden="1">
+    <row r="133" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A133" s="24">
         <f>IF(B133="","",SUBTOTAL(3,$B$4:B133))</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="B133" s="25" t="s">
         <v>174</v>
@@ -35767,10 +35759,10 @@
       <c r="BC133" s="71"/>
       <c r="BD133" s="71"/>
     </row>
-    <row r="134" spans="1:56" hidden="1">
+    <row r="134" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A134" s="24">
         <f>IF(B134="","",SUBTOTAL(3,$B$4:B134))</f>
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="B134" s="25" t="s">
         <v>174</v>
@@ -35883,10 +35875,10 @@
       <c r="BC134" s="71"/>
       <c r="BD134" s="71"/>
     </row>
-    <row r="135" spans="1:56" hidden="1">
+    <row r="135" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A135" s="24">
         <f>IF(B135="","",SUBTOTAL(3,$B$4:B135))</f>
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="B135" s="25" t="s">
         <v>174</v>
@@ -35999,10 +35991,10 @@
       <c r="BC135" s="71"/>
       <c r="BD135" s="71"/>
     </row>
-    <row r="136" spans="1:56" hidden="1">
+    <row r="136" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A136" s="24">
         <f>IF(B136="","",SUBTOTAL(3,$B$4:B136))</f>
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="B136" s="25" t="s">
         <v>174</v>
@@ -36115,10 +36107,10 @@
       <c r="BC136" s="71"/>
       <c r="BD136" s="71"/>
     </row>
-    <row r="137" spans="1:56" hidden="1">
+    <row r="137" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A137" s="24">
         <f>IF(B137="","",SUBTOTAL(3,$B$4:B137))</f>
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="B137" s="25" t="s">
         <v>174</v>
@@ -36231,10 +36223,10 @@
       <c r="BC137" s="71"/>
       <c r="BD137" s="71"/>
     </row>
-    <row r="138" spans="1:56" hidden="1">
+    <row r="138" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A138" s="24">
         <f>IF(B138="","",SUBTOTAL(3,$B$4:B138))</f>
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B138" s="25" t="s">
         <v>174</v>
@@ -36347,10 +36339,10 @@
       <c r="BC138" s="71"/>
       <c r="BD138" s="71"/>
     </row>
-    <row r="139" spans="1:56" hidden="1">
+    <row r="139" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A139" s="24">
         <f>IF(B139="","",SUBTOTAL(3,$B$4:B139))</f>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="B139" s="25" t="s">
         <v>174</v>
@@ -36463,10 +36455,10 @@
       <c r="BC139" s="71"/>
       <c r="BD139" s="71"/>
     </row>
-    <row r="140" spans="1:56" hidden="1">
+    <row r="140" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A140" s="24">
         <f>IF(B140="","",SUBTOTAL(3,$B$4:B140))</f>
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="B140" s="25" t="s">
         <v>174</v>
@@ -36579,10 +36571,10 @@
       <c r="BC140" s="71"/>
       <c r="BD140" s="71"/>
     </row>
-    <row r="141" spans="1:56" hidden="1">
+    <row r="141" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A141" s="24">
         <f>IF(B141="","",SUBTOTAL(3,$B$4:B141))</f>
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="B141" s="25" t="s">
         <v>174</v>
@@ -36705,10 +36697,10 @@
       <c r="BC141" s="71"/>
       <c r="BD141" s="71"/>
     </row>
-    <row r="142" spans="1:56" hidden="1">
+    <row r="142" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A142" s="24">
         <f>IF(B142="","",SUBTOTAL(3,$B$4:B142))</f>
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="B142" s="25" t="s">
         <v>174</v>
@@ -36831,10 +36823,10 @@
       <c r="BC142" s="71"/>
       <c r="BD142" s="71"/>
     </row>
-    <row r="143" spans="1:56">
+    <row r="143" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A143" s="24">
         <f>IF(B143="","",SUBTOTAL(3,$B$4:B143))</f>
-        <v>1</v>
+        <v>140</v>
       </c>
       <c r="B143" s="25" t="s">
         <v>174</v>
@@ -36969,10 +36961,10 @@
       <c r="BC143" s="71"/>
       <c r="BD143" s="71"/>
     </row>
-    <row r="144" spans="1:56" hidden="1">
+    <row r="144" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A144" s="24">
         <f>IF(B144="","",SUBTOTAL(3,$B$4:B144))</f>
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="B144" s="25" t="s">
         <v>174</v>
@@ -37101,10 +37093,10 @@
       <c r="BC144" s="71"/>
       <c r="BD144" s="71"/>
     </row>
-    <row r="145" spans="1:56" hidden="1">
+    <row r="145" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A145" s="24">
         <f>IF(B145="","",SUBTOTAL(3,$B$4:B145))</f>
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="B145" s="25" t="s">
         <v>174</v>
@@ -37227,10 +37219,10 @@
       <c r="BC145" s="71"/>
       <c r="BD145" s="71"/>
     </row>
-    <row r="146" spans="1:56" hidden="1">
+    <row r="146" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A146" s="24">
         <f>IF(B146="","",SUBTOTAL(3,$B$4:B146))</f>
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="B146" s="25" t="s">
         <v>174</v>
@@ -37353,10 +37345,10 @@
       <c r="BC146" s="71"/>
       <c r="BD146" s="71"/>
     </row>
-    <row r="147" spans="1:56" hidden="1">
+    <row r="147" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A147" s="24">
         <f>IF(B147="","",SUBTOTAL(3,$B$4:B147))</f>
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="B147" s="25" t="s">
         <v>174</v>
@@ -37479,10 +37471,10 @@
       <c r="BC147" s="71"/>
       <c r="BD147" s="71"/>
     </row>
-    <row r="148" spans="1:56" hidden="1">
+    <row r="148" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A148" s="24">
         <f>IF(B148="","",SUBTOTAL(3,$B$4:B148))</f>
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="B148" s="25" t="s">
         <v>174</v>
@@ -37605,10 +37597,10 @@
       <c r="BC148" s="71"/>
       <c r="BD148" s="71"/>
     </row>
-    <row r="149" spans="1:56" hidden="1">
+    <row r="149" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A149" s="24">
         <f>IF(B149="","",SUBTOTAL(3,$B$4:B149))</f>
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="B149" s="25" t="s">
         <v>174</v>
@@ -37731,10 +37723,10 @@
       <c r="BC149" s="71"/>
       <c r="BD149" s="71"/>
     </row>
-    <row r="150" spans="1:56" hidden="1">
+    <row r="150" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A150" s="24">
         <f>IF(B150="","",SUBTOTAL(3,$B$4:B150))</f>
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="B150" s="25" t="s">
         <v>174</v>
@@ -37857,10 +37849,10 @@
       <c r="BC150" s="71"/>
       <c r="BD150" s="71"/>
     </row>
-    <row r="151" spans="1:56" hidden="1">
+    <row r="151" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A151" s="24">
         <f>IF(B151="","",SUBTOTAL(3,$B$4:B151))</f>
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="B151" s="25" t="s">
         <v>174</v>
@@ -37983,10 +37975,10 @@
       <c r="BC151" s="71"/>
       <c r="BD151" s="71"/>
     </row>
-    <row r="152" spans="1:56" hidden="1">
+    <row r="152" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A152" s="24">
         <f>IF(B152="","",SUBTOTAL(3,$B$4:B152))</f>
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="B152" s="25" t="s">
         <v>174</v>
@@ -38109,10 +38101,10 @@
       <c r="BC152" s="71"/>
       <c r="BD152" s="71"/>
     </row>
-    <row r="153" spans="1:56" hidden="1">
+    <row r="153" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A153" s="24">
         <f>IF(B153="","",SUBTOTAL(3,$B$4:B153))</f>
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="B153" s="25" t="s">
         <v>174</v>
@@ -38235,10 +38227,10 @@
       <c r="BC153" s="71"/>
       <c r="BD153" s="71"/>
     </row>
-    <row r="154" spans="1:56" hidden="1">
+    <row r="154" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A154" s="24">
         <f>IF(B154="","",SUBTOTAL(3,$B$4:B154))</f>
-        <v>1</v>
+        <v>151</v>
       </c>
       <c r="B154" s="25" t="s">
         <v>174</v>
@@ -38373,10 +38365,10 @@
       <c r="BC154" s="71"/>
       <c r="BD154" s="71"/>
     </row>
-    <row r="155" spans="1:56" hidden="1">
+    <row r="155" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A155" s="24">
         <f>IF(B155="","",SUBTOTAL(3,$B$4:B155))</f>
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="B155" s="25" t="s">
         <v>174</v>
@@ -38511,10 +38503,10 @@
       <c r="BC155" s="71"/>
       <c r="BD155" s="71"/>
     </row>
-    <row r="156" spans="1:56" hidden="1">
+    <row r="156" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A156" s="24">
         <f>IF(B156="","",SUBTOTAL(3,$B$4:B156))</f>
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="B156" s="25" t="s">
         <v>174</v>
@@ -38655,10 +38647,10 @@
       <c r="BC156" s="71"/>
       <c r="BD156" s="71"/>
     </row>
-    <row r="157" spans="1:56" hidden="1">
+    <row r="157" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A157" s="24">
         <f>IF(B157="","",SUBTOTAL(3,$B$4:B157))</f>
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="B157" s="25" t="s">
         <v>174</v>
@@ -38799,10 +38791,10 @@
       <c r="BC157" s="71"/>
       <c r="BD157" s="71"/>
     </row>
-    <row r="158" spans="1:56" hidden="1">
+    <row r="158" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A158" s="24">
         <f>IF(B158="","",SUBTOTAL(3,$B$4:B158))</f>
-        <v>1</v>
+        <v>155</v>
       </c>
       <c r="B158" s="25" t="s">
         <v>174</v>
@@ -38943,10 +38935,10 @@
       <c r="BC158" s="71"/>
       <c r="BD158" s="71"/>
     </row>
-    <row r="159" spans="1:56" hidden="1">
+    <row r="159" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A159" s="24">
         <f>IF(B159="","",SUBTOTAL(3,$B$4:B159))</f>
-        <v>1</v>
+        <v>156</v>
       </c>
       <c r="B159" s="25" t="s">
         <v>174</v>
@@ -39061,10 +39053,10 @@
       <c r="BC159" s="71"/>
       <c r="BD159" s="71"/>
     </row>
-    <row r="160" spans="1:56" hidden="1">
+    <row r="160" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A160" s="24">
         <f>IF(B160="","",SUBTOTAL(3,$B$4:B160))</f>
-        <v>1</v>
+        <v>157</v>
       </c>
       <c r="B160" s="25" t="s">
         <v>174</v>
@@ -39179,10 +39171,10 @@
       <c r="BC160" s="71"/>
       <c r="BD160" s="71"/>
     </row>
-    <row r="161" spans="1:56" hidden="1">
+    <row r="161" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A161" s="24">
         <f>IF(B161="","",SUBTOTAL(3,$B$4:B161))</f>
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="B161" s="25" t="s">
         <v>174</v>
@@ -39297,10 +39289,10 @@
       <c r="BC161" s="71"/>
       <c r="BD161" s="71"/>
     </row>
-    <row r="162" spans="1:56" hidden="1">
+    <row r="162" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A162" s="24">
         <f>IF(B162="","",SUBTOTAL(3,$B$4:B162))</f>
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="B162" s="25" t="s">
         <v>174</v>
@@ -39415,10 +39407,10 @@
       <c r="BC162" s="71"/>
       <c r="BD162" s="71"/>
     </row>
-    <row r="163" spans="1:56" hidden="1">
+    <row r="163" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A163" s="24">
         <f>IF(B163="","",SUBTOTAL(3,$B$4:B163))</f>
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="B163" s="25" t="s">
         <v>174</v>
@@ -39533,10 +39525,10 @@
       <c r="BC163" s="71"/>
       <c r="BD163" s="71"/>
     </row>
-    <row r="164" spans="1:56" hidden="1">
+    <row r="164" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A164" s="24">
         <f>IF(B164="","",SUBTOTAL(3,$B$4:B164))</f>
-        <v>1</v>
+        <v>161</v>
       </c>
       <c r="B164" s="25" t="s">
         <v>174</v>
@@ -39651,10 +39643,10 @@
       <c r="BC164" s="71"/>
       <c r="BD164" s="71"/>
     </row>
-    <row r="165" spans="1:56" hidden="1">
+    <row r="165" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A165" s="24">
         <f>IF(B165="","",SUBTOTAL(3,$B$4:B165))</f>
-        <v>1</v>
+        <v>162</v>
       </c>
       <c r="B165" s="25" t="s">
         <v>174</v>
@@ -39769,10 +39761,10 @@
       <c r="BC165" s="71"/>
       <c r="BD165" s="71"/>
     </row>
-    <row r="166" spans="1:56" hidden="1">
+    <row r="166" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A166" s="24">
         <f>IF(B166="","",SUBTOTAL(3,$B$4:B166))</f>
-        <v>1</v>
+        <v>163</v>
       </c>
       <c r="B166" s="25" t="s">
         <v>174</v>
@@ -39887,10 +39879,10 @@
       <c r="BC166" s="71"/>
       <c r="BD166" s="71"/>
     </row>
-    <row r="167" spans="1:56" hidden="1">
+    <row r="167" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A167" s="24">
         <f>IF(B167="","",SUBTOTAL(3,$B$4:B167))</f>
-        <v>1</v>
+        <v>164</v>
       </c>
       <c r="B167" s="25" t="s">
         <v>174</v>
@@ -40005,10 +39997,10 @@
       <c r="BC167" s="71"/>
       <c r="BD167" s="71"/>
     </row>
-    <row r="168" spans="1:56" hidden="1">
+    <row r="168" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A168" s="24">
         <f>IF(B168="","",SUBTOTAL(3,$B$4:B168))</f>
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="B168" s="25" t="s">
         <v>174</v>
@@ -40123,10 +40115,10 @@
       <c r="BC168" s="71"/>
       <c r="BD168" s="71"/>
     </row>
-    <row r="169" spans="1:56" hidden="1">
+    <row r="169" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A169" s="24">
         <f>IF(B169="","",SUBTOTAL(3,$B$4:B169))</f>
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="B169" s="25" t="s">
         <v>174</v>
@@ -40241,10 +40233,10 @@
       <c r="BC169" s="71"/>
       <c r="BD169" s="71"/>
     </row>
-    <row r="170" spans="1:56" hidden="1">
+    <row r="170" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A170" s="24">
         <f>IF(B170="","",SUBTOTAL(3,$B$4:B170))</f>
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="B170" s="25" t="s">
         <v>174</v>
@@ -40359,10 +40351,10 @@
       <c r="BC170" s="71"/>
       <c r="BD170" s="71"/>
     </row>
-    <row r="171" spans="1:56" hidden="1">
+    <row r="171" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A171" s="24">
         <f>IF(B171="","",SUBTOTAL(3,$B$4:B171))</f>
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="B171" s="25" t="s">
         <v>174</v>
@@ -40477,10 +40469,10 @@
       <c r="BC171" s="71"/>
       <c r="BD171" s="71"/>
     </row>
-    <row r="172" spans="1:56" hidden="1">
+    <row r="172" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A172" s="24">
         <f>IF(B172="","",SUBTOTAL(3,$B$4:B172))</f>
-        <v>1</v>
+        <v>169</v>
       </c>
       <c r="B172" s="25" t="s">
         <v>174</v>
@@ -40595,10 +40587,10 @@
       <c r="BC172" s="71"/>
       <c r="BD172" s="71"/>
     </row>
-    <row r="173" spans="1:56" hidden="1">
+    <row r="173" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A173" s="24">
         <f>IF(B173="","",SUBTOTAL(3,$B$4:B173))</f>
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="B173" s="25" t="s">
         <v>174</v>
@@ -40713,10 +40705,10 @@
       <c r="BC173" s="71"/>
       <c r="BD173" s="71"/>
     </row>
-    <row r="174" spans="1:56" hidden="1">
+    <row r="174" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A174" s="24">
         <f>IF(B174="","",SUBTOTAL(3,$B$4:B174))</f>
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="B174" s="25" t="s">
         <v>174</v>
@@ -40831,10 +40823,10 @@
       <c r="BC174" s="71"/>
       <c r="BD174" s="71"/>
     </row>
-    <row r="175" spans="1:56" hidden="1">
+    <row r="175" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A175" s="24">
         <f>IF(B175="","",SUBTOTAL(3,$B$4:B175))</f>
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="B175" s="25" t="s">
         <v>174</v>
@@ -40949,10 +40941,10 @@
       <c r="BC175" s="71"/>
       <c r="BD175" s="71"/>
     </row>
-    <row r="176" spans="1:56" hidden="1">
+    <row r="176" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A176" s="24">
         <f>IF(B176="","",SUBTOTAL(3,$B$4:B176))</f>
-        <v>1</v>
+        <v>173</v>
       </c>
       <c r="B176" s="25" t="s">
         <v>174</v>
@@ -41067,10 +41059,10 @@
       <c r="BC176" s="71"/>
       <c r="BD176" s="71"/>
     </row>
-    <row r="177" spans="1:56" hidden="1">
+    <row r="177" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A177" s="24">
         <f>IF(B177="","",SUBTOTAL(3,$B$4:B177))</f>
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="B177" s="25" t="s">
         <v>174</v>
@@ -41185,10 +41177,10 @@
       <c r="BC177" s="71"/>
       <c r="BD177" s="71"/>
     </row>
-    <row r="178" spans="1:56" hidden="1">
+    <row r="178" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A178" s="24">
         <f>IF(B178="","",SUBTOTAL(3,$B$4:B178))</f>
-        <v>1</v>
+        <v>175</v>
       </c>
       <c r="B178" s="25" t="s">
         <v>174</v>
@@ -41303,10 +41295,10 @@
       <c r="BC178" s="71"/>
       <c r="BD178" s="71"/>
     </row>
-    <row r="179" spans="1:56" hidden="1">
+    <row r="179" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A179" s="24">
         <f>IF(B179="","",SUBTOTAL(3,$B$4:B179))</f>
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="B179" s="25" t="s">
         <v>174</v>
@@ -41421,10 +41413,10 @@
       <c r="BC179" s="71"/>
       <c r="BD179" s="71"/>
     </row>
-    <row r="180" spans="1:56" hidden="1">
+    <row r="180" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A180" s="24">
         <f>IF(B180="","",SUBTOTAL(3,$B$4:B180))</f>
-        <v>1</v>
+        <v>177</v>
       </c>
       <c r="B180" s="25" t="s">
         <v>174</v>
@@ -41539,10 +41531,10 @@
       <c r="BC180" s="71"/>
       <c r="BD180" s="71"/>
     </row>
-    <row r="181" spans="1:56" hidden="1">
+    <row r="181" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A181" s="24">
         <f>IF(B181="","",SUBTOTAL(3,$B$4:B181))</f>
-        <v>1</v>
+        <v>178</v>
       </c>
       <c r="B181" s="25" t="s">
         <v>174</v>
@@ -41657,10 +41649,10 @@
       <c r="BC181" s="71"/>
       <c r="BD181" s="71"/>
     </row>
-    <row r="182" spans="1:56" hidden="1">
+    <row r="182" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A182" s="24">
         <f>IF(B182="","",SUBTOTAL(3,$B$4:B182))</f>
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="B182" s="25" t="s">
         <v>174</v>
@@ -41775,10 +41767,10 @@
       <c r="BC182" s="71"/>
       <c r="BD182" s="71"/>
     </row>
-    <row r="183" spans="1:56" hidden="1">
+    <row r="183" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A183" s="24">
         <f>IF(B183="","",SUBTOTAL(3,$B$4:B183))</f>
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="B183" s="25" t="s">
         <v>174</v>
@@ -41893,10 +41885,10 @@
       <c r="BC183" s="71"/>
       <c r="BD183" s="71"/>
     </row>
-    <row r="184" spans="1:56" hidden="1">
+    <row r="184" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A184" s="24">
         <f>IF(B184="","",SUBTOTAL(3,$B$4:B184))</f>
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="B184" s="25" t="s">
         <v>174</v>
@@ -42011,10 +42003,10 @@
       <c r="BC184" s="71"/>
       <c r="BD184" s="71"/>
     </row>
-    <row r="185" spans="1:56" hidden="1">
+    <row r="185" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A185" s="24">
         <f>IF(B185="","",SUBTOTAL(3,$B$4:B185))</f>
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="B185" s="25" t="s">
         <v>174</v>
@@ -42129,10 +42121,10 @@
       <c r="BC185" s="71"/>
       <c r="BD185" s="71"/>
     </row>
-    <row r="186" spans="1:56" hidden="1">
+    <row r="186" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A186" s="24">
         <f>IF(B186="","",SUBTOTAL(3,$B$4:B186))</f>
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="B186" s="25" t="s">
         <v>174</v>
@@ -42247,10 +42239,10 @@
       <c r="BC186" s="71"/>
       <c r="BD186" s="71"/>
     </row>
-    <row r="187" spans="1:56" hidden="1">
+    <row r="187" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A187" s="24">
         <f>IF(B187="","",SUBTOTAL(3,$B$4:B187))</f>
-        <v>1</v>
+        <v>184</v>
       </c>
       <c r="B187" s="25" t="s">
         <v>174</v>
@@ -42365,10 +42357,10 @@
       <c r="BC187" s="71"/>
       <c r="BD187" s="71"/>
     </row>
-    <row r="188" spans="1:56" hidden="1">
+    <row r="188" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A188" s="24">
         <f>IF(B188="","",SUBTOTAL(3,$B$4:B188))</f>
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="B188" s="25" t="s">
         <v>174</v>
@@ -42483,10 +42475,10 @@
       <c r="BC188" s="71"/>
       <c r="BD188" s="71"/>
     </row>
-    <row r="189" spans="1:56" hidden="1">
+    <row r="189" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A189" s="24">
         <f>IF(B189="","",SUBTOTAL(3,$B$4:B189))</f>
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="B189" s="25" t="s">
         <v>174</v>
@@ -42601,7 +42593,7 @@
       <c r="BC189" s="71"/>
       <c r="BD189" s="71"/>
     </row>
-    <row r="190" spans="1:56" hidden="1">
+    <row r="190" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A190" s="24" t="str">
         <f>IF(B190="","",SUBTOTAL(3,$B$4:B190))</f>
         <v/>
@@ -42689,7 +42681,7 @@
       <c r="BC190" s="71"/>
       <c r="BD190" s="71"/>
     </row>
-    <row r="191" spans="1:56" hidden="1">
+    <row r="191" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A191" s="24" t="str">
         <f>IF(B191="","",SUBTOTAL(3,$B$4:B191))</f>
         <v/>
@@ -42777,7 +42769,7 @@
       <c r="BC191" s="71"/>
       <c r="BD191" s="71"/>
     </row>
-    <row r="192" spans="1:56" hidden="1">
+    <row r="192" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A192" s="24" t="str">
         <f>IF(B192="","",SUBTOTAL(3,$B$4:B192))</f>
         <v/>
@@ -42865,7 +42857,7 @@
       <c r="BC192" s="71"/>
       <c r="BD192" s="71"/>
     </row>
-    <row r="193" spans="1:56" hidden="1">
+    <row r="193" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A193" s="24" t="str">
         <f>IF(B193="","",SUBTOTAL(3,$B$4:B193))</f>
         <v/>
@@ -42953,7 +42945,7 @@
       <c r="BC193" s="71"/>
       <c r="BD193" s="71"/>
     </row>
-    <row r="194" spans="1:56" hidden="1">
+    <row r="194" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A194" s="24" t="str">
         <f>IF(B194="","",SUBTOTAL(3,$B$4:B194))</f>
         <v/>
@@ -43041,7 +43033,7 @@
       <c r="BC194" s="71"/>
       <c r="BD194" s="71"/>
     </row>
-    <row r="195" spans="1:56" hidden="1">
+    <row r="195" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A195" s="24" t="str">
         <f>IF(B195="","",SUBTOTAL(3,$B$4:B195))</f>
         <v/>
@@ -43129,7 +43121,7 @@
       <c r="BC195" s="71"/>
       <c r="BD195" s="71"/>
     </row>
-    <row r="196" spans="1:56" hidden="1">
+    <row r="196" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A196" s="24" t="str">
         <f>IF(B196="","",SUBTOTAL(3,$B$4:B196))</f>
         <v/>
@@ -43217,7 +43209,7 @@
       <c r="BC196" s="71"/>
       <c r="BD196" s="71"/>
     </row>
-    <row r="197" spans="1:56" hidden="1">
+    <row r="197" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A197" s="24" t="str">
         <f>IF(B197="","",SUBTOTAL(3,$B$4:B197))</f>
         <v/>
@@ -43305,7 +43297,7 @@
       <c r="BC197" s="71"/>
       <c r="BD197" s="71"/>
     </row>
-    <row r="198" spans="1:56" hidden="1">
+    <row r="198" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A198" s="24" t="str">
         <f>IF(B198="","",SUBTOTAL(3,$B$4:B198))</f>
         <v/>
@@ -43393,7 +43385,7 @@
       <c r="BC198" s="71"/>
       <c r="BD198" s="71"/>
     </row>
-    <row r="199" spans="1:56" hidden="1">
+    <row r="199" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A199" s="24" t="str">
         <f>IF(B199="","",SUBTOTAL(3,$B$4:B199))</f>
         <v/>
@@ -43481,7 +43473,7 @@
       <c r="BC199" s="71"/>
       <c r="BD199" s="71"/>
     </row>
-    <row r="200" spans="1:56" hidden="1">
+    <row r="200" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A200" s="24" t="str">
         <f>IF(B200="","",SUBTOTAL(3,$B$4:B200))</f>
         <v/>
@@ -43569,7 +43561,7 @@
       <c r="BC200" s="71"/>
       <c r="BD200" s="71"/>
     </row>
-    <row r="201" spans="1:56" hidden="1">
+    <row r="201" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A201" s="24" t="str">
         <f>IF(B201="","",SUBTOTAL(3,$B$4:B201))</f>
         <v/>
@@ -43657,7 +43649,7 @@
       <c r="BC201" s="71"/>
       <c r="BD201" s="71"/>
     </row>
-    <row r="202" spans="1:56" hidden="1">
+    <row r="202" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A202" s="24" t="str">
         <f>IF(B202="","",SUBTOTAL(3,$B$4:B202))</f>
         <v/>
@@ -43745,7 +43737,7 @@
       <c r="BC202" s="71"/>
       <c r="BD202" s="71"/>
     </row>
-    <row r="203" spans="1:56" hidden="1">
+    <row r="203" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A203" s="24" t="str">
         <f>IF(B203="","",SUBTOTAL(3,$B$4:B203))</f>
         <v/>
@@ -43833,7 +43825,7 @@
       <c r="BC203" s="71"/>
       <c r="BD203" s="71"/>
     </row>
-    <row r="204" spans="1:56" hidden="1">
+    <row r="204" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A204" s="24" t="str">
         <f>IF(B204="","",SUBTOTAL(3,$B$4:B204))</f>
         <v/>
@@ -43921,7 +43913,7 @@
       <c r="BC204" s="71"/>
       <c r="BD204" s="71"/>
     </row>
-    <row r="205" spans="1:56" hidden="1">
+    <row r="205" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A205" s="24" t="str">
         <f>IF(B205="","",SUBTOTAL(3,$B$4:B205))</f>
         <v/>
@@ -44009,7 +44001,7 @@
       <c r="BC205" s="71"/>
       <c r="BD205" s="71"/>
     </row>
-    <row r="206" spans="1:56" hidden="1">
+    <row r="206" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A206" s="24" t="str">
         <f>IF(B206="","",SUBTOTAL(3,$B$4:B206))</f>
         <v/>
@@ -44097,7 +44089,7 @@
       <c r="BC206" s="71"/>
       <c r="BD206" s="71"/>
     </row>
-    <row r="207" spans="1:56" hidden="1">
+    <row r="207" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A207" s="24" t="str">
         <f>IF(B207="","",SUBTOTAL(3,$B$4:B207))</f>
         <v/>
@@ -44185,7 +44177,7 @@
       <c r="BC207" s="71"/>
       <c r="BD207" s="71"/>
     </row>
-    <row r="208" spans="1:56" hidden="1">
+    <row r="208" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A208" s="24" t="str">
         <f>IF(B208="","",SUBTOTAL(3,$B$4:B208))</f>
         <v/>
@@ -44273,7 +44265,7 @@
       <c r="BC208" s="71"/>
       <c r="BD208" s="71"/>
     </row>
-    <row r="209" spans="1:56" hidden="1">
+    <row r="209" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A209" s="24" t="str">
         <f>IF(B209="","",SUBTOTAL(3,$B$4:B209))</f>
         <v/>
@@ -44361,7 +44353,7 @@
       <c r="BC209" s="71"/>
       <c r="BD209" s="71"/>
     </row>
-    <row r="210" spans="1:56" hidden="1">
+    <row r="210" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A210" s="24" t="str">
         <f>IF(B210="","",SUBTOTAL(3,$B$4:B210))</f>
         <v/>
@@ -44449,7 +44441,7 @@
       <c r="BC210" s="71"/>
       <c r="BD210" s="71"/>
     </row>
-    <row r="211" spans="1:56" hidden="1">
+    <row r="211" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A211" s="24" t="str">
         <f>IF(B211="","",SUBTOTAL(3,$B$4:B211))</f>
         <v/>
@@ -44537,7 +44529,7 @@
       <c r="BC211" s="71"/>
       <c r="BD211" s="71"/>
     </row>
-    <row r="212" spans="1:56" hidden="1">
+    <row r="212" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A212" s="24" t="str">
         <f>IF(B212="","",SUBTOTAL(3,$B$4:B212))</f>
         <v/>
@@ -44625,7 +44617,7 @@
       <c r="BC212" s="71"/>
       <c r="BD212" s="71"/>
     </row>
-    <row r="213" spans="1:56" hidden="1">
+    <row r="213" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A213" s="24" t="str">
         <f>IF(B213="","",SUBTOTAL(3,$B$4:B213))</f>
         <v/>
@@ -44713,7 +44705,7 @@
       <c r="BC213" s="71"/>
       <c r="BD213" s="71"/>
     </row>
-    <row r="214" spans="1:56" hidden="1">
+    <row r="214" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A214" s="24" t="str">
         <f>IF(B214="","",SUBTOTAL(3,$B$4:B214))</f>
         <v/>
@@ -44801,7 +44793,7 @@
       <c r="BC214" s="71"/>
       <c r="BD214" s="71"/>
     </row>
-    <row r="215" spans="1:56" hidden="1">
+    <row r="215" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A215" s="24" t="str">
         <f>IF(B215="","",SUBTOTAL(3,$B$4:B215))</f>
         <v/>
@@ -44889,7 +44881,7 @@
       <c r="BC215" s="71"/>
       <c r="BD215" s="71"/>
     </row>
-    <row r="216" spans="1:56" hidden="1">
+    <row r="216" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A216" s="24" t="str">
         <f>IF(B216="","",SUBTOTAL(3,$B$4:B216))</f>
         <v/>
@@ -44977,7 +44969,7 @@
       <c r="BC216" s="71"/>
       <c r="BD216" s="71"/>
     </row>
-    <row r="217" spans="1:56" hidden="1">
+    <row r="217" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A217" s="24" t="str">
         <f>IF(B217="","",SUBTOTAL(3,$B$4:B217))</f>
         <v/>
@@ -45065,7 +45057,7 @@
       <c r="BC217" s="71"/>
       <c r="BD217" s="71"/>
     </row>
-    <row r="218" spans="1:56" hidden="1">
+    <row r="218" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A218" s="24" t="str">
         <f>IF(B218="","",SUBTOTAL(3,$B$4:B218))</f>
         <v/>
@@ -45153,7 +45145,7 @@
       <c r="BC218" s="71"/>
       <c r="BD218" s="71"/>
     </row>
-    <row r="219" spans="1:56" hidden="1">
+    <row r="219" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A219" s="24" t="str">
         <f>IF(B219="","",SUBTOTAL(3,$B$4:B219))</f>
         <v/>
@@ -45241,7 +45233,7 @@
       <c r="BC219" s="71"/>
       <c r="BD219" s="71"/>
     </row>
-    <row r="220" spans="1:56" hidden="1">
+    <row r="220" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A220" s="24" t="str">
         <f>IF(B220="","",SUBTOTAL(3,$B$4:B220))</f>
         <v/>
@@ -45329,7 +45321,7 @@
       <c r="BC220" s="71"/>
       <c r="BD220" s="71"/>
     </row>
-    <row r="221" spans="1:56" hidden="1">
+    <row r="221" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A221" s="24" t="str">
         <f>IF(B221="","",SUBTOTAL(3,$B$4:B221))</f>
         <v/>
@@ -45417,7 +45409,7 @@
       <c r="BC221" s="71"/>
       <c r="BD221" s="71"/>
     </row>
-    <row r="222" spans="1:56" hidden="1">
+    <row r="222" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A222" s="24" t="str">
         <f>IF(B222="","",SUBTOTAL(3,$B$4:B222))</f>
         <v/>
@@ -45505,7 +45497,7 @@
       <c r="BC222" s="71"/>
       <c r="BD222" s="71"/>
     </row>
-    <row r="223" spans="1:56" hidden="1">
+    <row r="223" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A223" s="24" t="str">
         <f>IF(B223="","",SUBTOTAL(3,$B$4:B223))</f>
         <v/>
@@ -45593,7 +45585,7 @@
       <c r="BC223" s="71"/>
       <c r="BD223" s="71"/>
     </row>
-    <row r="224" spans="1:56" hidden="1">
+    <row r="224" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A224" s="24" t="str">
         <f>IF(B224="","",SUBTOTAL(3,$B$4:B224))</f>
         <v/>
@@ -45681,7 +45673,7 @@
       <c r="BC224" s="71"/>
       <c r="BD224" s="71"/>
     </row>
-    <row r="225" spans="1:56" hidden="1">
+    <row r="225" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A225" s="24" t="str">
         <f>IF(B225="","",SUBTOTAL(3,$B$4:B225))</f>
         <v/>
@@ -45769,7 +45761,7 @@
       <c r="BC225" s="71"/>
       <c r="BD225" s="71"/>
     </row>
-    <row r="226" spans="1:56" hidden="1">
+    <row r="226" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A226" s="24" t="str">
         <f>IF(B226="","",SUBTOTAL(3,$B$4:B226))</f>
         <v/>
@@ -45857,7 +45849,7 @@
       <c r="BC226" s="71"/>
       <c r="BD226" s="71"/>
     </row>
-    <row r="227" spans="1:56" hidden="1">
+    <row r="227" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A227" s="24" t="str">
         <f>IF(B227="","",SUBTOTAL(3,$B$4:B227))</f>
         <v/>
@@ -45945,7 +45937,7 @@
       <c r="BC227" s="71"/>
       <c r="BD227" s="71"/>
     </row>
-    <row r="228" spans="1:56" hidden="1">
+    <row r="228" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A228" s="24" t="str">
         <f>IF(B228="","",SUBTOTAL(3,$B$4:B228))</f>
         <v/>
@@ -46033,7 +46025,7 @@
       <c r="BC228" s="71"/>
       <c r="BD228" s="71"/>
     </row>
-    <row r="229" spans="1:56" hidden="1">
+    <row r="229" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A229" s="24" t="str">
         <f>IF(B229="","",SUBTOTAL(3,$B$4:B229))</f>
         <v/>
@@ -46121,7 +46113,7 @@
       <c r="BC229" s="71"/>
       <c r="BD229" s="71"/>
     </row>
-    <row r="230" spans="1:56" hidden="1">
+    <row r="230" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A230" s="24" t="str">
         <f>IF(B230="","",SUBTOTAL(3,$B$4:B230))</f>
         <v/>
@@ -46209,7 +46201,7 @@
       <c r="BC230" s="71"/>
       <c r="BD230" s="71"/>
     </row>
-    <row r="231" spans="1:56" hidden="1">
+    <row r="231" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A231" s="24" t="str">
         <f>IF(B231="","",SUBTOTAL(3,$B$4:B231))</f>
         <v/>
@@ -46297,7 +46289,7 @@
       <c r="BC231" s="71"/>
       <c r="BD231" s="71"/>
     </row>
-    <row r="232" spans="1:56" hidden="1">
+    <row r="232" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A232" s="24" t="str">
         <f>IF(B232="","",SUBTOTAL(3,$B$4:B232))</f>
         <v/>
@@ -46385,7 +46377,7 @@
       <c r="BC232" s="71"/>
       <c r="BD232" s="71"/>
     </row>
-    <row r="233" spans="1:56" hidden="1">
+    <row r="233" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A233" s="24" t="str">
         <f>IF(B233="","",SUBTOTAL(3,$B$4:B233))</f>
         <v/>
@@ -46473,7 +46465,7 @@
       <c r="BC233" s="71"/>
       <c r="BD233" s="71"/>
     </row>
-    <row r="234" spans="1:56" hidden="1">
+    <row r="234" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A234" s="24" t="str">
         <f>IF(B234="","",SUBTOTAL(3,$B$4:B234))</f>
         <v/>
@@ -46561,7 +46553,7 @@
       <c r="BC234" s="71"/>
       <c r="BD234" s="71"/>
     </row>
-    <row r="235" spans="1:56" hidden="1">
+    <row r="235" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A235" s="24" t="str">
         <f>IF(B235="","",SUBTOTAL(3,$B$4:B235))</f>
         <v/>
@@ -46649,7 +46641,7 @@
       <c r="BC235" s="71"/>
       <c r="BD235" s="71"/>
     </row>
-    <row r="236" spans="1:56" hidden="1">
+    <row r="236" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A236" s="24" t="str">
         <f>IF(B236="","",SUBTOTAL(3,$B$4:B236))</f>
         <v/>
@@ -46737,7 +46729,7 @@
       <c r="BC236" s="71"/>
       <c r="BD236" s="71"/>
     </row>
-    <row r="237" spans="1:56" hidden="1">
+    <row r="237" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A237" s="24" t="str">
         <f>IF(B237="","",SUBTOTAL(3,$B$4:B237))</f>
         <v/>
@@ -46825,7 +46817,7 @@
       <c r="BC237" s="71"/>
       <c r="BD237" s="71"/>
     </row>
-    <row r="238" spans="1:56" hidden="1">
+    <row r="238" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A238" s="24" t="str">
         <f>IF(B238="","",SUBTOTAL(3,$B$4:B238))</f>
         <v/>
@@ -46913,7 +46905,7 @@
       <c r="BC238" s="71"/>
       <c r="BD238" s="71"/>
     </row>
-    <row r="239" spans="1:56" hidden="1">
+    <row r="239" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A239" s="24" t="str">
         <f>IF(B239="","",SUBTOTAL(3,$B$4:B239))</f>
         <v/>
@@ -47001,7 +46993,7 @@
       <c r="BC239" s="71"/>
       <c r="BD239" s="71"/>
     </row>
-    <row r="240" spans="1:56" hidden="1">
+    <row r="240" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A240" s="24" t="str">
         <f>IF(B240="","",SUBTOTAL(3,$B$4:B240))</f>
         <v/>
@@ -47089,7 +47081,7 @@
       <c r="BC240" s="71"/>
       <c r="BD240" s="71"/>
     </row>
-    <row r="241" spans="1:56" hidden="1">
+    <row r="241" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A241" s="24" t="str">
         <f>IF(B241="","",SUBTOTAL(3,$B$4:B241))</f>
         <v/>
@@ -47177,7 +47169,7 @@
       <c r="BC241" s="71"/>
       <c r="BD241" s="71"/>
     </row>
-    <row r="242" spans="1:56" hidden="1">
+    <row r="242" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A242" s="24" t="str">
         <f>IF(B242="","",SUBTOTAL(3,$B$4:B242))</f>
         <v/>
@@ -47265,7 +47257,7 @@
       <c r="BC242" s="71"/>
       <c r="BD242" s="71"/>
     </row>
-    <row r="243" spans="1:56" hidden="1">
+    <row r="243" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A243" s="24" t="str">
         <f>IF(B243="","",SUBTOTAL(3,$B$4:B243))</f>
         <v/>
@@ -47353,7 +47345,7 @@
       <c r="BC243" s="71"/>
       <c r="BD243" s="71"/>
     </row>
-    <row r="244" spans="1:56" hidden="1">
+    <row r="244" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A244" s="24" t="str">
         <f>IF(B244="","",SUBTOTAL(3,$B$4:B244))</f>
         <v/>
@@ -47441,7 +47433,7 @@
       <c r="BC244" s="71"/>
       <c r="BD244" s="71"/>
     </row>
-    <row r="245" spans="1:56" hidden="1">
+    <row r="245" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A245" s="24" t="str">
         <f>IF(B245="","",SUBTOTAL(3,$B$4:B245))</f>
         <v/>
@@ -47529,7 +47521,7 @@
       <c r="BC245" s="71"/>
       <c r="BD245" s="71"/>
     </row>
-    <row r="246" spans="1:56" hidden="1">
+    <row r="246" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A246" s="24" t="str">
         <f>IF(B246="","",SUBTOTAL(3,$B$4:B246))</f>
         <v/>
@@ -47617,7 +47609,7 @@
       <c r="BC246" s="71"/>
       <c r="BD246" s="71"/>
     </row>
-    <row r="247" spans="1:56" hidden="1">
+    <row r="247" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A247" s="24" t="str">
         <f>IF(B247="","",SUBTOTAL(3,$B$4:B247))</f>
         <v/>
@@ -47705,7 +47697,7 @@
       <c r="BC247" s="71"/>
       <c r="BD247" s="71"/>
     </row>
-    <row r="248" spans="1:56" hidden="1">
+    <row r="248" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A248" s="24" t="str">
         <f>IF(B248="","",SUBTOTAL(3,$B$4:B248))</f>
         <v/>
@@ -47793,7 +47785,7 @@
       <c r="BC248" s="71"/>
       <c r="BD248" s="71"/>
     </row>
-    <row r="249" spans="1:56" hidden="1">
+    <row r="249" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A249" s="24" t="str">
         <f>IF(B249="","",SUBTOTAL(3,$B$4:B249))</f>
         <v/>
@@ -47881,7 +47873,7 @@
       <c r="BC249" s="71"/>
       <c r="BD249" s="71"/>
     </row>
-    <row r="250" spans="1:56" hidden="1">
+    <row r="250" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A250" s="24" t="str">
         <f>IF(B250="","",SUBTOTAL(3,$B$4:B250))</f>
         <v/>
@@ -47969,7 +47961,7 @@
       <c r="BC250" s="71"/>
       <c r="BD250" s="71"/>
     </row>
-    <row r="251" spans="1:56" hidden="1">
+    <row r="251" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A251" s="24" t="str">
         <f>IF(B251="","",SUBTOTAL(3,$B$4:B251))</f>
         <v/>
@@ -48057,7 +48049,7 @@
       <c r="BC251" s="71"/>
       <c r="BD251" s="71"/>
     </row>
-    <row r="252" spans="1:56" hidden="1">
+    <row r="252" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A252" s="24" t="str">
         <f>IF(B252="","",SUBTOTAL(3,$B$4:B252))</f>
         <v/>
@@ -48145,7 +48137,7 @@
       <c r="BC252" s="71"/>
       <c r="BD252" s="71"/>
     </row>
-    <row r="253" spans="1:56" hidden="1">
+    <row r="253" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A253" s="24" t="str">
         <f>IF(B253="","",SUBTOTAL(3,$B$4:B253))</f>
         <v/>
@@ -48233,7 +48225,7 @@
       <c r="BC253" s="71"/>
       <c r="BD253" s="71"/>
     </row>
-    <row r="254" spans="1:56" hidden="1">
+    <row r="254" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A254" s="24" t="str">
         <f>IF(B254="","",SUBTOTAL(3,$B$4:B254))</f>
         <v/>
@@ -48321,7 +48313,7 @@
       <c r="BC254" s="71"/>
       <c r="BD254" s="71"/>
     </row>
-    <row r="255" spans="1:56" hidden="1">
+    <row r="255" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A255" s="24" t="str">
         <f>IF(B255="","",SUBTOTAL(3,$B$4:B255))</f>
         <v/>
@@ -48409,7 +48401,7 @@
       <c r="BC255" s="71"/>
       <c r="BD255" s="71"/>
     </row>
-    <row r="256" spans="1:56" hidden="1">
+    <row r="256" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A256" s="24" t="str">
         <f>IF(B256="","",SUBTOTAL(3,$B$4:B256))</f>
         <v/>
@@ -48497,7 +48489,7 @@
       <c r="BC256" s="71"/>
       <c r="BD256" s="71"/>
     </row>
-    <row r="257" spans="1:56" hidden="1">
+    <row r="257" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A257" s="24" t="str">
         <f>IF(B257="","",SUBTOTAL(3,$B$4:B257))</f>
         <v/>
@@ -48585,7 +48577,7 @@
       <c r="BC257" s="71"/>
       <c r="BD257" s="71"/>
     </row>
-    <row r="258" spans="1:56" hidden="1">
+    <row r="258" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A258" s="24" t="str">
         <f>IF(B258="","",SUBTOTAL(3,$B$4:B258))</f>
         <v/>
@@ -48673,7 +48665,7 @@
       <c r="BC258" s="71"/>
       <c r="BD258" s="71"/>
     </row>
-    <row r="259" spans="1:56" hidden="1">
+    <row r="259" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A259" s="24" t="str">
         <f>IF(B259="","",SUBTOTAL(3,$B$4:B259))</f>
         <v/>
@@ -48761,7 +48753,7 @@
       <c r="BC259" s="71"/>
       <c r="BD259" s="71"/>
     </row>
-    <row r="260" spans="1:56" hidden="1">
+    <row r="260" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A260" s="24" t="str">
         <f>IF(B260="","",SUBTOTAL(3,$B$4:B260))</f>
         <v/>
@@ -48849,7 +48841,7 @@
       <c r="BC260" s="71"/>
       <c r="BD260" s="71"/>
     </row>
-    <row r="261" spans="1:56" hidden="1">
+    <row r="261" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A261" s="24" t="str">
         <f>IF(B261="","",SUBTOTAL(3,$B$4:B261))</f>
         <v/>
@@ -48937,7 +48929,7 @@
       <c r="BC261" s="71"/>
       <c r="BD261" s="71"/>
     </row>
-    <row r="262" spans="1:56" hidden="1">
+    <row r="262" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A262" s="24" t="str">
         <f>IF(B262="","",SUBTOTAL(3,$B$4:B262))</f>
         <v/>
@@ -49025,7 +49017,7 @@
       <c r="BC262" s="71"/>
       <c r="BD262" s="71"/>
     </row>
-    <row r="263" spans="1:56" hidden="1">
+    <row r="263" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A263" s="24" t="str">
         <f>IF(B263="","",SUBTOTAL(3,$B$4:B263))</f>
         <v/>
@@ -49113,7 +49105,7 @@
       <c r="BC263" s="71"/>
       <c r="BD263" s="71"/>
     </row>
-    <row r="264" spans="1:56" hidden="1">
+    <row r="264" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A264" s="24" t="str">
         <f>IF(B264="","",SUBTOTAL(3,$B$4:B264))</f>
         <v/>
@@ -49201,7 +49193,7 @@
       <c r="BC264" s="71"/>
       <c r="BD264" s="71"/>
     </row>
-    <row r="265" spans="1:56" hidden="1">
+    <row r="265" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A265" s="24" t="str">
         <f>IF(B265="","",SUBTOTAL(3,$B$4:B265))</f>
         <v/>
@@ -49289,7 +49281,7 @@
       <c r="BC265" s="71"/>
       <c r="BD265" s="71"/>
     </row>
-    <row r="266" spans="1:56" hidden="1">
+    <row r="266" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A266" s="24" t="str">
         <f>IF(B266="","",SUBTOTAL(3,$B$4:B266))</f>
         <v/>
@@ -49377,7 +49369,7 @@
       <c r="BC266" s="71"/>
       <c r="BD266" s="71"/>
     </row>
-    <row r="267" spans="1:56" hidden="1">
+    <row r="267" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A267" s="24" t="str">
         <f>IF(B267="","",SUBTOTAL(3,$B$4:B267))</f>
         <v/>
@@ -49465,7 +49457,7 @@
       <c r="BC267" s="71"/>
       <c r="BD267" s="71"/>
     </row>
-    <row r="268" spans="1:56" hidden="1">
+    <row r="268" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A268" s="24" t="str">
         <f>IF(B268="","",SUBTOTAL(3,$B$4:B268))</f>
         <v/>
@@ -49553,7 +49545,7 @@
       <c r="BC268" s="71"/>
       <c r="BD268" s="71"/>
     </row>
-    <row r="269" spans="1:56" hidden="1">
+    <row r="269" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A269" s="24" t="str">
         <f>IF(B269="","",SUBTOTAL(3,$B$4:B269))</f>
         <v/>
@@ -49641,7 +49633,7 @@
       <c r="BC269" s="71"/>
       <c r="BD269" s="71"/>
     </row>
-    <row r="270" spans="1:56" hidden="1">
+    <row r="270" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A270" s="24" t="str">
         <f>IF(B270="","",SUBTOTAL(3,$B$4:B270))</f>
         <v/>
@@ -49729,7 +49721,7 @@
       <c r="BC270" s="71"/>
       <c r="BD270" s="71"/>
     </row>
-    <row r="271" spans="1:56" hidden="1">
+    <row r="271" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A271" s="24" t="str">
         <f>IF(B271="","",SUBTOTAL(3,$B$4:B271))</f>
         <v/>
@@ -49817,7 +49809,7 @@
       <c r="BC271" s="71"/>
       <c r="BD271" s="71"/>
     </row>
-    <row r="272" spans="1:56" hidden="1">
+    <row r="272" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A272" s="24" t="str">
         <f>IF(B272="","",SUBTOTAL(3,$B$4:B272))</f>
         <v/>
@@ -49905,7 +49897,7 @@
       <c r="BC272" s="71"/>
       <c r="BD272" s="71"/>
     </row>
-    <row r="273" spans="1:56" hidden="1">
+    <row r="273" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A273" s="24" t="str">
         <f>IF(B273="","",SUBTOTAL(3,$B$4:B273))</f>
         <v/>
@@ -49993,7 +49985,7 @@
       <c r="BC273" s="71"/>
       <c r="BD273" s="71"/>
     </row>
-    <row r="274" spans="1:56" hidden="1">
+    <row r="274" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A274" s="24" t="str">
         <f>IF(B274="","",SUBTOTAL(3,$B$4:B274))</f>
         <v/>
@@ -50081,7 +50073,7 @@
       <c r="BC274" s="71"/>
       <c r="BD274" s="71"/>
     </row>
-    <row r="275" spans="1:56" hidden="1">
+    <row r="275" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A275" s="24" t="str">
         <f>IF(B275="","",SUBTOTAL(3,$B$4:B275))</f>
         <v/>
@@ -50169,7 +50161,7 @@
       <c r="BC275" s="71"/>
       <c r="BD275" s="71"/>
     </row>
-    <row r="276" spans="1:56" hidden="1">
+    <row r="276" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A276" s="24" t="str">
         <f>IF(B276="","",SUBTOTAL(3,$B$4:B276))</f>
         <v/>
@@ -50257,7 +50249,7 @@
       <c r="BC276" s="71"/>
       <c r="BD276" s="71"/>
     </row>
-    <row r="277" spans="1:56" hidden="1">
+    <row r="277" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A277" s="24" t="str">
         <f>IF(B277="","",SUBTOTAL(3,$B$4:B277))</f>
         <v/>
@@ -50345,7 +50337,7 @@
       <c r="BC277" s="71"/>
       <c r="BD277" s="71"/>
     </row>
-    <row r="278" spans="1:56" hidden="1">
+    <row r="278" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A278" s="24" t="str">
         <f>IF(B278="","",SUBTOTAL(3,$B$4:B278))</f>
         <v/>
@@ -50433,7 +50425,7 @@
       <c r="BC278" s="71"/>
       <c r="BD278" s="71"/>
     </row>
-    <row r="279" spans="1:56" hidden="1">
+    <row r="279" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A279" s="24" t="str">
         <f>IF(B279="","",SUBTOTAL(3,$B$4:B279))</f>
         <v/>
@@ -50521,7 +50513,7 @@
       <c r="BC279" s="71"/>
       <c r="BD279" s="71"/>
     </row>
-    <row r="280" spans="1:56" hidden="1">
+    <row r="280" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A280" s="24" t="str">
         <f>IF(B280="","",SUBTOTAL(3,$B$4:B280))</f>
         <v/>
@@ -50609,7 +50601,7 @@
       <c r="BC280" s="71"/>
       <c r="BD280" s="71"/>
     </row>
-    <row r="281" spans="1:56" hidden="1">
+    <row r="281" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A281" s="24" t="str">
         <f>IF(B281="","",SUBTOTAL(3,$B$4:B281))</f>
         <v/>
@@ -50697,7 +50689,7 @@
       <c r="BC281" s="71"/>
       <c r="BD281" s="71"/>
     </row>
-    <row r="282" spans="1:56" hidden="1">
+    <row r="282" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A282" s="24" t="str">
         <f>IF(B282="","",SUBTOTAL(3,$B$4:B282))</f>
         <v/>
@@ -50785,7 +50777,7 @@
       <c r="BC282" s="71"/>
       <c r="BD282" s="71"/>
     </row>
-    <row r="283" spans="1:56" hidden="1">
+    <row r="283" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A283" s="24" t="str">
         <f>IF(B283="","",SUBTOTAL(3,$B$4:B283))</f>
         <v/>
@@ -50873,7 +50865,7 @@
       <c r="BC283" s="71"/>
       <c r="BD283" s="71"/>
     </row>
-    <row r="284" spans="1:56" hidden="1">
+    <row r="284" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A284" s="24" t="str">
         <f>IF(B284="","",SUBTOTAL(3,$B$4:B284))</f>
         <v/>
@@ -50961,7 +50953,7 @@
       <c r="BC284" s="71"/>
       <c r="BD284" s="71"/>
     </row>
-    <row r="285" spans="1:56" hidden="1">
+    <row r="285" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A285" s="24" t="str">
         <f>IF(B285="","",SUBTOTAL(3,$B$4:B285))</f>
         <v/>
@@ -51049,7 +51041,7 @@
       <c r="BC285" s="71"/>
       <c r="BD285" s="71"/>
     </row>
-    <row r="286" spans="1:56" hidden="1">
+    <row r="286" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A286" s="24" t="str">
         <f>IF(B286="","",SUBTOTAL(3,$B$4:B286))</f>
         <v/>
@@ -51137,7 +51129,7 @@
       <c r="BC286" s="71"/>
       <c r="BD286" s="71"/>
     </row>
-    <row r="287" spans="1:56" hidden="1">
+    <row r="287" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A287" s="24" t="str">
         <f>IF(B287="","",SUBTOTAL(3,$B$4:B287))</f>
         <v/>
@@ -51225,7 +51217,7 @@
       <c r="BC287" s="71"/>
       <c r="BD287" s="71"/>
     </row>
-    <row r="288" spans="1:56" hidden="1">
+    <row r="288" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A288" s="24" t="str">
         <f>IF(B288="","",SUBTOTAL(3,$B$4:B288))</f>
         <v/>
@@ -51313,7 +51305,7 @@
       <c r="BC288" s="71"/>
       <c r="BD288" s="71"/>
     </row>
-    <row r="289" spans="1:56" hidden="1">
+    <row r="289" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A289" s="24" t="str">
         <f>IF(B289="","",SUBTOTAL(3,$B$4:B289))</f>
         <v/>
@@ -51401,7 +51393,7 @@
       <c r="BC289" s="71"/>
       <c r="BD289" s="71"/>
     </row>
-    <row r="290" spans="1:56" hidden="1">
+    <row r="290" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A290" s="24" t="str">
         <f>IF(B290="","",SUBTOTAL(3,$B$4:B290))</f>
         <v/>
@@ -51489,7 +51481,7 @@
       <c r="BC290" s="71"/>
       <c r="BD290" s="71"/>
     </row>
-    <row r="291" spans="1:56" hidden="1">
+    <row r="291" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A291" s="24" t="str">
         <f>IF(B291="","",SUBTOTAL(3,$B$4:B291))</f>
         <v/>
@@ -51577,7 +51569,7 @@
       <c r="BC291" s="71"/>
       <c r="BD291" s="71"/>
     </row>
-    <row r="292" spans="1:56" hidden="1">
+    <row r="292" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A292" s="24" t="str">
         <f>IF(B292="","",SUBTOTAL(3,$B$4:B292))</f>
         <v/>
@@ -51665,7 +51657,7 @@
       <c r="BC292" s="71"/>
       <c r="BD292" s="71"/>
     </row>
-    <row r="293" spans="1:56" hidden="1">
+    <row r="293" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A293" s="24" t="str">
         <f>IF(B293="","",SUBTOTAL(3,$B$4:B293))</f>
         <v/>
@@ -51753,7 +51745,7 @@
       <c r="BC293" s="71"/>
       <c r="BD293" s="71"/>
     </row>
-    <row r="294" spans="1:56" hidden="1">
+    <row r="294" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A294" s="24" t="str">
         <f>IF(B294="","",SUBTOTAL(3,$B$4:B294))</f>
         <v/>
@@ -51841,7 +51833,7 @@
       <c r="BC294" s="71"/>
       <c r="BD294" s="71"/>
     </row>
-    <row r="295" spans="1:56" hidden="1">
+    <row r="295" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A295" s="24" t="str">
         <f>IF(B295="","",SUBTOTAL(3,$B$4:B295))</f>
         <v/>
@@ -51929,7 +51921,7 @@
       <c r="BC295" s="71"/>
       <c r="BD295" s="71"/>
     </row>
-    <row r="296" spans="1:56" hidden="1">
+    <row r="296" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A296" s="24" t="str">
         <f>IF(B296="","",SUBTOTAL(3,$B$4:B296))</f>
         <v/>
@@ -52017,7 +52009,7 @@
       <c r="BC296" s="71"/>
       <c r="BD296" s="71"/>
     </row>
-    <row r="297" spans="1:56" hidden="1">
+    <row r="297" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A297" s="24" t="str">
         <f>IF(B297="","",SUBTOTAL(3,$B$4:B297))</f>
         <v/>
@@ -52105,7 +52097,7 @@
       <c r="BC297" s="71"/>
       <c r="BD297" s="71"/>
     </row>
-    <row r="298" spans="1:56" hidden="1">
+    <row r="298" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A298" s="24" t="str">
         <f>IF(B298="","",SUBTOTAL(3,$B$4:B298))</f>
         <v/>
@@ -52193,7 +52185,7 @@
       <c r="BC298" s="71"/>
       <c r="BD298" s="71"/>
     </row>
-    <row r="299" spans="1:56" hidden="1">
+    <row r="299" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A299" s="24" t="str">
         <f>IF(B299="","",SUBTOTAL(3,$B$4:B299))</f>
         <v/>
@@ -52281,7 +52273,7 @@
       <c r="BC299" s="71"/>
       <c r="BD299" s="71"/>
     </row>
-    <row r="300" spans="1:56" hidden="1">
+    <row r="300" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A300" s="24" t="str">
         <f>IF(B300="","",SUBTOTAL(3,$B$4:B300))</f>
         <v/>
@@ -52369,7 +52361,7 @@
       <c r="BC300" s="71"/>
       <c r="BD300" s="71"/>
     </row>
-    <row r="301" spans="1:56" hidden="1">
+    <row r="301" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A301" s="24" t="str">
         <f>IF(B301="","",SUBTOTAL(3,$B$4:B301))</f>
         <v/>
@@ -52457,7 +52449,7 @@
       <c r="BC301" s="71"/>
       <c r="BD301" s="71"/>
     </row>
-    <row r="302" spans="1:56" hidden="1">
+    <row r="302" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A302" s="24" t="str">
         <f>IF(B302="","",SUBTOTAL(3,$B$4:B302))</f>
         <v/>
@@ -52545,7 +52537,7 @@
       <c r="BC302" s="71"/>
       <c r="BD302" s="71"/>
     </row>
-    <row r="303" spans="1:56" hidden="1">
+    <row r="303" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A303" s="24" t="str">
         <f>IF(B303="","",SUBTOTAL(3,$B$4:B303))</f>
         <v/>
@@ -52633,7 +52625,7 @@
       <c r="BC303" s="71"/>
       <c r="BD303" s="71"/>
     </row>
-    <row r="304" spans="1:56" hidden="1">
+    <row r="304" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A304" s="24" t="str">
         <f>IF(B304="","",SUBTOTAL(3,$B$4:B304))</f>
         <v/>
@@ -52721,7 +52713,7 @@
       <c r="BC304" s="71"/>
       <c r="BD304" s="71"/>
     </row>
-    <row r="305" spans="1:56" hidden="1">
+    <row r="305" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A305" s="24" t="str">
         <f>IF(B305="","",SUBTOTAL(3,$B$4:B305))</f>
         <v/>
@@ -52809,7 +52801,7 @@
       <c r="BC305" s="71"/>
       <c r="BD305" s="71"/>
     </row>
-    <row r="306" spans="1:56" hidden="1">
+    <row r="306" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A306" s="24" t="str">
         <f>IF(B306="","",SUBTOTAL(3,$B$4:B306))</f>
         <v/>
@@ -52897,7 +52889,7 @@
       <c r="BC306" s="71"/>
       <c r="BD306" s="71"/>
     </row>
-    <row r="307" spans="1:56" hidden="1">
+    <row r="307" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A307" s="24" t="str">
         <f>IF(B307="","",SUBTOTAL(3,$B$4:B307))</f>
         <v/>
@@ -52985,7 +52977,7 @@
       <c r="BC307" s="71"/>
       <c r="BD307" s="71"/>
     </row>
-    <row r="308" spans="1:56" hidden="1">
+    <row r="308" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A308" s="24" t="str">
         <f>IF(B308="","",SUBTOTAL(3,$B$4:B308))</f>
         <v/>
@@ -53073,7 +53065,7 @@
       <c r="BC308" s="71"/>
       <c r="BD308" s="71"/>
     </row>
-    <row r="309" spans="1:56" hidden="1">
+    <row r="309" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A309" s="24" t="str">
         <f>IF(B309="","",SUBTOTAL(3,$B$4:B309))</f>
         <v/>
@@ -53161,7 +53153,7 @@
       <c r="BC309" s="71"/>
       <c r="BD309" s="71"/>
     </row>
-    <row r="310" spans="1:56" hidden="1">
+    <row r="310" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A310" s="24" t="str">
         <f>IF(B310="","",SUBTOTAL(3,$B$4:B310))</f>
         <v/>
@@ -53249,7 +53241,7 @@
       <c r="BC310" s="71"/>
       <c r="BD310" s="71"/>
     </row>
-    <row r="311" spans="1:56" hidden="1">
+    <row r="311" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A311" s="24" t="str">
         <f>IF(B311="","",SUBTOTAL(3,$B$4:B311))</f>
         <v/>
@@ -53337,7 +53329,7 @@
       <c r="BC311" s="71"/>
       <c r="BD311" s="71"/>
     </row>
-    <row r="312" spans="1:56" hidden="1">
+    <row r="312" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A312" s="24" t="str">
         <f>IF(B312="","",SUBTOTAL(3,$B$4:B312))</f>
         <v/>
@@ -53425,7 +53417,7 @@
       <c r="BC312" s="71"/>
       <c r="BD312" s="71"/>
     </row>
-    <row r="313" spans="1:56" hidden="1">
+    <row r="313" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A313" s="24" t="str">
         <f>IF(B313="","",SUBTOTAL(3,$B$4:B313))</f>
         <v/>
@@ -53513,7 +53505,7 @@
       <c r="BC313" s="71"/>
       <c r="BD313" s="71"/>
     </row>
-    <row r="314" spans="1:56" hidden="1">
+    <row r="314" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A314" s="24" t="str">
         <f>IF(B314="","",SUBTOTAL(3,$B$4:B314))</f>
         <v/>
@@ -53601,7 +53593,7 @@
       <c r="BC314" s="71"/>
       <c r="BD314" s="71"/>
     </row>
-    <row r="315" spans="1:56" hidden="1">
+    <row r="315" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A315" s="24" t="str">
         <f>IF(B315="","",SUBTOTAL(3,$B$4:B315))</f>
         <v/>
@@ -53689,7 +53681,7 @@
       <c r="BC315" s="71"/>
       <c r="BD315" s="71"/>
     </row>
-    <row r="316" spans="1:56" hidden="1">
+    <row r="316" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A316" s="24" t="str">
         <f>IF(B316="","",SUBTOTAL(3,$B$4:B316))</f>
         <v/>
@@ -53777,7 +53769,7 @@
       <c r="BC316" s="71"/>
       <c r="BD316" s="71"/>
     </row>
-    <row r="317" spans="1:56" hidden="1">
+    <row r="317" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A317" s="24" t="str">
         <f>IF(B317="","",SUBTOTAL(3,$B$4:B317))</f>
         <v/>
@@ -53865,7 +53857,7 @@
       <c r="BC317" s="71"/>
       <c r="BD317" s="71"/>
     </row>
-    <row r="318" spans="1:56" hidden="1">
+    <row r="318" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A318" s="24" t="str">
         <f>IF(B318="","",SUBTOTAL(3,$B$4:B318))</f>
         <v/>
@@ -53953,7 +53945,7 @@
       <c r="BC318" s="71"/>
       <c r="BD318" s="71"/>
     </row>
-    <row r="319" spans="1:56" hidden="1">
+    <row r="319" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A319" s="24" t="str">
         <f>IF(B319="","",SUBTOTAL(3,$B$4:B319))</f>
         <v/>
@@ -54041,7 +54033,7 @@
       <c r="BC319" s="71"/>
       <c r="BD319" s="71"/>
     </row>
-    <row r="320" spans="1:56" hidden="1">
+    <row r="320" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A320" s="24" t="str">
         <f>IF(B320="","",SUBTOTAL(3,$B$4:B320))</f>
         <v/>
@@ -54129,7 +54121,7 @@
       <c r="BC320" s="71"/>
       <c r="BD320" s="71"/>
     </row>
-    <row r="321" spans="1:56" hidden="1">
+    <row r="321" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A321" s="24" t="str">
         <f>IF(B321="","",SUBTOTAL(3,$B$4:B321))</f>
         <v/>
@@ -54217,7 +54209,7 @@
       <c r="BC321" s="71"/>
       <c r="BD321" s="71"/>
     </row>
-    <row r="322" spans="1:56" hidden="1">
+    <row r="322" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A322" s="24" t="str">
         <f>IF(B322="","",SUBTOTAL(3,$B$4:B322))</f>
         <v/>
@@ -54305,7 +54297,7 @@
       <c r="BC322" s="71"/>
       <c r="BD322" s="71"/>
     </row>
-    <row r="323" spans="1:56" hidden="1">
+    <row r="323" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A323" s="24" t="str">
         <f>IF(B323="","",SUBTOTAL(3,$B$4:B323))</f>
         <v/>
@@ -54393,7 +54385,7 @@
       <c r="BC323" s="71"/>
       <c r="BD323" s="71"/>
     </row>
-    <row r="324" spans="1:56" hidden="1">
+    <row r="324" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A324" s="24" t="str">
         <f>IF(B324="","",SUBTOTAL(3,$B$4:B324))</f>
         <v/>
@@ -54481,7 +54473,7 @@
       <c r="BC324" s="71"/>
       <c r="BD324" s="71"/>
     </row>
-    <row r="325" spans="1:56" hidden="1">
+    <row r="325" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A325" s="24" t="str">
         <f>IF(B325="","",SUBTOTAL(3,$B$4:B325))</f>
         <v/>
@@ -54569,7 +54561,7 @@
       <c r="BC325" s="71"/>
       <c r="BD325" s="71"/>
     </row>
-    <row r="326" spans="1:56" ht="16.5" hidden="1" thickBot="1">
+    <row r="326" spans="1:56" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="38" t="str">
         <f>IF(B326="","",SUBTOTAL(3,$B$4:B326))</f>
         <v/>
@@ -54657,17 +54649,9 @@
       <c r="BC326" s="71"/>
       <c r="BD326" s="71"/>
     </row>
+    <row r="327" spans="1:56" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:BD326" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}">
-    <filterColumn colId="44">
-      <filters>
-        <filter val="A320-M4130-006"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="49">
-      <colorFilter dxfId="26"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:BD326" xr:uid="{334E9545-4D7F-4FF2-AE79-B0165FA68616}"/>
   <conditionalFormatting sqref="A4:AG326 AJ4:AL326">
     <cfRule type="expression" dxfId="15" priority="2">
       <formula>$AK4=$N4</formula>
